--- a/test_data.xlsx
+++ b/test_data.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1189" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1189" uniqueCount="368">
   <si>
     <t>publication_date_2025</t>
   </si>
@@ -144,9 +144,6 @@
     <t>structure_new_summaries</t>
   </si>
   <si>
-    <t>L</t>
-  </si>
-  <si>
     <t>at a glance section in both years</t>
   </si>
   <si>
@@ -156,9 +153,6 @@
     <t>structure_appendix_change</t>
   </si>
   <si>
-    <t>N</t>
-  </si>
-  <si>
     <t>use of appendix</t>
   </si>
   <si>
@@ -166,9 +160,6 @@
   </si>
   <si>
     <t>dma_methodology_update</t>
-  </si>
-  <si>
-    <t>P</t>
   </si>
   <si>
     <t>na</t>
@@ -192,13 +183,7 @@
     <t>dma_positive_impacts_removed</t>
   </si>
   <si>
-    <t>R</t>
-  </si>
-  <si>
     <t>dma_threshold_clarified</t>
-  </si>
-  <si>
-    <t>T</t>
   </si>
   <si>
     <t>p.50 - as in 2024</t>
@@ -221,9 +206,6 @@
     <t>1</t>
   </si>
   <si>
-    <t>V</t>
-  </si>
-  <si>
     <t>p.50 as 2024</t>
   </si>
   <si>
@@ -238,16 +220,10 @@
     <t>dma_topics_removed_count</t>
   </si>
   <si>
-    <t>X</t>
-  </si>
-  <si>
     <t>compare 19 (2024, p. 63) to 15 (2025, p. 66)</t>
   </si>
   <si>
     <t>dma_learning_reference</t>
-  </si>
-  <si>
-    <t>Z</t>
   </si>
   <si>
     <t>Regular reviews and updates of these targets
@@ -256,9 +232,6 @@
   </si>
   <si>
     <t>omnibus_explicit</t>
-  </si>
-  <si>
-    <t>AB</t>
   </si>
   <si>
     <t>p. 50: "n accordance with section 10.4 of ESRS 1 and the Omnibus quick-fix resolu-
@@ -278,9 +251,6 @@
   </si>
   <si>
     <t>restatement_e</t>
-  </si>
-  <si>
-    <t>AD</t>
   </si>
   <si>
     <t>p. 35. "In the 2025 reporting on sustainability topic E1 Cli-
@@ -308,9 +278,6 @@
     <t>restatement_s</t>
   </si>
   <si>
-    <t>AF</t>
-  </si>
-  <si>
     <t>63: "We have restated our 2024 S1 management
 distribution figures on page 119 to reflect
 enhanced data capture methodologies. 
@@ -322,265 +289,262 @@
     <t>restatement_g</t>
   </si>
   <si>
-    <t>AH</t>
-  </si>
-  <si>
-    <t>E11</t>
-  </si>
-  <si>
-    <t>E12</t>
-  </si>
-  <si>
-    <t>E13</t>
-  </si>
-  <si>
-    <t>E14</t>
-  </si>
-  <si>
-    <t>E15</t>
-  </si>
-  <si>
-    <t>E16</t>
-  </si>
-  <si>
-    <t>E17</t>
-  </si>
-  <si>
-    <t>E18</t>
-  </si>
-  <si>
-    <t>E19</t>
-  </si>
-  <si>
-    <t>E19_phase_in_disclosed</t>
-  </si>
-  <si>
-    <t>E21</t>
-  </si>
-  <si>
-    <t>E22</t>
-  </si>
-  <si>
-    <t>E23</t>
-  </si>
-  <si>
-    <t>E24</t>
-  </si>
-  <si>
-    <t>E25</t>
-  </si>
-  <si>
-    <t>E26</t>
-  </si>
-  <si>
-    <t>E26_phase_in_disclosed</t>
-  </si>
-  <si>
-    <t>E31</t>
-  </si>
-  <si>
-    <t>E32</t>
-  </si>
-  <si>
-    <t>E33</t>
-  </si>
-  <si>
-    <t>E34</t>
-  </si>
-  <si>
-    <t>E35</t>
-  </si>
-  <si>
-    <t>E35_phase_in_disclosed</t>
-  </si>
-  <si>
-    <t>E4fully_phased_in</t>
-  </si>
-  <si>
-    <t>E41</t>
-  </si>
-  <si>
-    <t>E42</t>
-  </si>
-  <si>
-    <t>E43</t>
-  </si>
-  <si>
-    <t>E44</t>
-  </si>
-  <si>
-    <t>E45</t>
-  </si>
-  <si>
-    <t>E46</t>
-  </si>
-  <si>
-    <t>E46_phase_in_disclosed</t>
-  </si>
-  <si>
-    <t>E51</t>
-  </si>
-  <si>
-    <t>E52</t>
-  </si>
-  <si>
-    <t>E53</t>
-  </si>
-  <si>
-    <t>E54</t>
-  </si>
-  <si>
-    <t>E55</t>
-  </si>
-  <si>
-    <t>E56</t>
-  </si>
-  <si>
-    <t>E56_phase_in_disclosed</t>
-  </si>
-  <si>
-    <t>S11</t>
-  </si>
-  <si>
-    <t>S12</t>
-  </si>
-  <si>
-    <t>S13</t>
-  </si>
-  <si>
-    <t>S14</t>
-  </si>
-  <si>
-    <t>S15</t>
-  </si>
-  <si>
-    <t>S16</t>
-  </si>
-  <si>
-    <t>S17</t>
-  </si>
-  <si>
-    <t>S17_phase_in_disclosed</t>
-  </si>
-  <si>
-    <t>S18</t>
-  </si>
-  <si>
-    <t>S18_phase_in_disclosed</t>
-  </si>
-  <si>
-    <t>S19</t>
-  </si>
-  <si>
-    <t>S110</t>
-  </si>
-  <si>
-    <t>S111</t>
-  </si>
-  <si>
-    <t>S111_phase_in_disclosed</t>
-  </si>
-  <si>
-    <t>S112</t>
-  </si>
-  <si>
-    <t>S112_phase_in_disclosed</t>
-  </si>
-  <si>
-    <t>S113</t>
-  </si>
-  <si>
-    <t>S113_phase_in_disclosed</t>
-  </si>
-  <si>
-    <t>S114</t>
-  </si>
-  <si>
-    <t>S114_phase_in_disclosed</t>
-  </si>
-  <si>
-    <t>S115</t>
-  </si>
-  <si>
-    <t>S115_phase_in_disclosed</t>
-  </si>
-  <si>
-    <t>S116</t>
-  </si>
-  <si>
-    <t>S117</t>
-  </si>
-  <si>
-    <t>S2fully_phased_in</t>
-  </si>
-  <si>
-    <t>S21</t>
-  </si>
-  <si>
-    <t>S22</t>
-  </si>
-  <si>
-    <t>S23</t>
-  </si>
-  <si>
-    <t>S24</t>
-  </si>
-  <si>
-    <t>S25</t>
-  </si>
-  <si>
-    <t>S3fully_phased_in</t>
-  </si>
-  <si>
-    <t>S31</t>
-  </si>
-  <si>
-    <t>S32</t>
-  </si>
-  <si>
-    <t>S33</t>
-  </si>
-  <si>
-    <t>S34</t>
-  </si>
-  <si>
-    <t>S35</t>
-  </si>
-  <si>
-    <t>S4fully_phased_in</t>
-  </si>
-  <si>
-    <t>S41</t>
-  </si>
-  <si>
-    <t>S42</t>
-  </si>
-  <si>
-    <t>S43</t>
-  </si>
-  <si>
-    <t>S44</t>
-  </si>
-  <si>
-    <t>S45</t>
-  </si>
-  <si>
-    <t>G11</t>
-  </si>
-  <si>
-    <t>G12</t>
-  </si>
-  <si>
-    <t>G13</t>
-  </si>
-  <si>
-    <t>G14</t>
-  </si>
-  <si>
-    <t>G15</t>
-  </si>
-  <si>
-    <t>G16</t>
+    <t>E1-1</t>
+  </si>
+  <si>
+    <t>E1-2</t>
+  </si>
+  <si>
+    <t>E1-3</t>
+  </si>
+  <si>
+    <t>E1-4</t>
+  </si>
+  <si>
+    <t>E1-5</t>
+  </si>
+  <si>
+    <t>E1-6</t>
+  </si>
+  <si>
+    <t>E1-7</t>
+  </si>
+  <si>
+    <t>E1-8</t>
+  </si>
+  <si>
+    <t>E1-9</t>
+  </si>
+  <si>
+    <t>E1-9_phase_in_disclosed</t>
+  </si>
+  <si>
+    <t>E2-1</t>
+  </si>
+  <si>
+    <t>E2-2</t>
+  </si>
+  <si>
+    <t>E2-3</t>
+  </si>
+  <si>
+    <t>E2-4</t>
+  </si>
+  <si>
+    <t>E2-5</t>
+  </si>
+  <si>
+    <t>E2-6</t>
+  </si>
+  <si>
+    <t>E2-6_phase_in_disclosed</t>
+  </si>
+  <si>
+    <t>E3-1</t>
+  </si>
+  <si>
+    <t>E3-2</t>
+  </si>
+  <si>
+    <t>E3-3</t>
+  </si>
+  <si>
+    <t>E3-4</t>
+  </si>
+  <si>
+    <t>E3-5</t>
+  </si>
+  <si>
+    <t>E3-5_phase_in_disclosed</t>
+  </si>
+  <si>
+    <t>E4-fully_phased_in</t>
+  </si>
+  <si>
+    <t>E4-1</t>
+  </si>
+  <si>
+    <t>E4-2</t>
+  </si>
+  <si>
+    <t>E4-3</t>
+  </si>
+  <si>
+    <t>E4-4</t>
+  </si>
+  <si>
+    <t>E4-5</t>
+  </si>
+  <si>
+    <t>E4-6</t>
+  </si>
+  <si>
+    <t>E4-6_phase_in_disclosed</t>
+  </si>
+  <si>
+    <t>E5-1</t>
+  </si>
+  <si>
+    <t>E5-2</t>
+  </si>
+  <si>
+    <t>E5-3</t>
+  </si>
+  <si>
+    <t>E5-4</t>
+  </si>
+  <si>
+    <t>E5-5</t>
+  </si>
+  <si>
+    <t>E5-6</t>
+  </si>
+  <si>
+    <t>E5-6_phase_in_disclosed</t>
+  </si>
+  <si>
+    <t>S1-1</t>
+  </si>
+  <si>
+    <t>S1-2</t>
+  </si>
+  <si>
+    <t>S1-3</t>
+  </si>
+  <si>
+    <t>S1-4</t>
+  </si>
+  <si>
+    <t>S1-5</t>
+  </si>
+  <si>
+    <t>S1-6</t>
+  </si>
+  <si>
+    <t>S1-7</t>
+  </si>
+  <si>
+    <t>S1-7_phase_in_disclosed</t>
+  </si>
+  <si>
+    <t>S1-8</t>
+  </si>
+  <si>
+    <t>S1-8_phase_in_disclosed</t>
+  </si>
+  <si>
+    <t>S1-9</t>
+  </si>
+  <si>
+    <t>S1-10</t>
+  </si>
+  <si>
+    <t>S1-11</t>
+  </si>
+  <si>
+    <t>S1-11_phase_in_disclosed</t>
+  </si>
+  <si>
+    <t>S1-12</t>
+  </si>
+  <si>
+    <t>S1-12_phase_in_disclosed</t>
+  </si>
+  <si>
+    <t>S1-13</t>
+  </si>
+  <si>
+    <t>S1-13_phase_in_disclosed</t>
+  </si>
+  <si>
+    <t>S1-14</t>
+  </si>
+  <si>
+    <t>S1-14_phase_in_disclosed</t>
+  </si>
+  <si>
+    <t>S1-15</t>
+  </si>
+  <si>
+    <t>S1-15_phase_in_disclosed</t>
+  </si>
+  <si>
+    <t>S1-16</t>
+  </si>
+  <si>
+    <t>S1-17</t>
+  </si>
+  <si>
+    <t>S2-fully_phased_in</t>
+  </si>
+  <si>
+    <t>S2-1</t>
+  </si>
+  <si>
+    <t>S2-2</t>
+  </si>
+  <si>
+    <t>S2-3</t>
+  </si>
+  <si>
+    <t>S2-4</t>
+  </si>
+  <si>
+    <t>S2-5</t>
+  </si>
+  <si>
+    <t>S3-fully_phased_in</t>
+  </si>
+  <si>
+    <t>S3-1</t>
+  </si>
+  <si>
+    <t>S3-2</t>
+  </si>
+  <si>
+    <t>S3-3</t>
+  </si>
+  <si>
+    <t>S3-4</t>
+  </si>
+  <si>
+    <t>S3-5</t>
+  </si>
+  <si>
+    <t>S4-fully_phased_in</t>
+  </si>
+  <si>
+    <t>S4-1</t>
+  </si>
+  <si>
+    <t>S4-2</t>
+  </si>
+  <si>
+    <t>S4-3</t>
+  </si>
+  <si>
+    <t>S4-4</t>
+  </si>
+  <si>
+    <t>S4-5</t>
+  </si>
+  <si>
+    <t>G1-1</t>
+  </si>
+  <si>
+    <t>G1-2</t>
+  </si>
+  <si>
+    <t>G1-3</t>
+  </si>
+  <si>
+    <t>G1-4</t>
+  </si>
+  <si>
+    <t>G1-5</t>
+  </si>
+  <si>
+    <t>G1-6</t>
   </si>
   <si>
     <t>year</t>
@@ -664,7 +628,7 @@
     <t>long_name</t>
   </si>
   <si>
-    <t>created_atx</t>
+    <t>created_at.x</t>
   </si>
   <si>
     <t>2025-05-20T01:11:43Z</t>
@@ -802,7 +766,7 @@
     <t>company</t>
   </si>
   <si>
-    <t>other_informationx</t>
+    <t>other_information.x</t>
   </si>
   <si>
     <t>NA</t>
@@ -835,7 +799,7 @@
     <t>1adb386d-63d5-435e-8646-3d6f526f78c4</t>
   </si>
   <si>
-    <t>created_aty</t>
+    <t>created_at.y</t>
   </si>
   <si>
     <t>2025-05-20T01:50:30Z</t>
@@ -919,7 +883,7 @@
     <t>en</t>
   </si>
   <si>
-    <t>other_informationy</t>
+    <t>other_information.y</t>
   </si>
   <si>
     <t>job_id</t>
@@ -973,7 +937,7 @@
     <t>A</t>
   </si>
   <si>
-    <t>item7210</t>
+    <t>ITEM7210</t>
   </si>
   <si>
     <t>3271396683</t>
@@ -1000,7 +964,7 @@
     <t>635430472.34</t>
   </si>
   <si>
-    <t>item6001</t>
+    <t>ITEM6001</t>
   </si>
   <si>
     <t>SPAR NORD BANK A/S</t>
@@ -1036,7 +1000,7 @@
     <t>Jahr</t>
   </si>
   <si>
-    <t>nontransposingcountry</t>
+    <t>non-transposing country?</t>
   </si>
   <si>
     <t>No</t>
@@ -1051,7 +1015,7 @@
     <t>Link_SR</t>
   </si>
   <si>
-    <t>AR_verifiziert</t>
+    <t>AR_verifiziert?</t>
   </si>
   <si>
     <t>Nein</t>
@@ -1081,7 +1045,7 @@
     <t>Datum_DR_Bearbeitung</t>
   </si>
   <si>
-    <t>IndexlisteSeitenzahl</t>
+    <t>Indexliste Seitenzahl</t>
   </si>
   <si>
     <t>110-111</t>
@@ -1275,514 +1239,514 @@
         <v>42</v>
       </c>
       <c r="L1" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="M1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N1" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="O1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="P1" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="Q1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="R1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S1" t="s">
+        <v>53</v>
+      </c>
+      <c r="T1" t="s">
+        <v>37</v>
+      </c>
+      <c r="U1" t="s">
         <v>56</v>
       </c>
-      <c r="S1" t="s">
-        <v>57</v>
-      </c>
-      <c r="T1" t="s">
-        <v>58</v>
-      </c>
-      <c r="U1" t="s">
-        <v>61</v>
-      </c>
       <c r="V1" t="s">
+        <v>37</v>
+      </c>
+      <c r="W1" t="s">
+        <v>62</v>
+      </c>
+      <c r="X1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y1" t="s">
         <v>64</v>
       </c>
-      <c r="W1" t="s">
-        <v>68</v>
-      </c>
-      <c r="X1" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC1" t="s">
         <v>71</v>
       </c>
-      <c r="Z1" t="s">
-        <v>72</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>74</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>75</v>
-      </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>76</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>78</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>79</v>
+      </c>
+      <c r="AJ1" t="s">
         <v>80</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AK1" t="s">
         <v>81</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AL1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>85</v>
+      </c>
+      <c r="AP1" t="s">
         <v>86</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AQ1" t="s">
         <v>87</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AR1" t="s">
+        <v>88</v>
+      </c>
+      <c r="AS1" t="s">
         <v>89</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AT1" t="s">
         <v>90</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AU1" t="s">
         <v>91</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AV1" t="s">
         <v>92</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AW1" t="s">
         <v>93</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AX1" t="s">
         <v>94</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AY1" t="s">
         <v>95</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AZ1" t="s">
         <v>96</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="BA1" t="s">
         <v>97</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="BB1" t="s">
         <v>98</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="BC1" t="s">
         <v>99</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="BD1" t="s">
         <v>100</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="BE1" t="s">
         <v>101</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="BF1" t="s">
         <v>102</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="BG1" t="s">
         <v>103</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="BH1" t="s">
         <v>104</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="BI1" t="s">
         <v>105</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="BJ1" t="s">
         <v>106</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="BK1" t="s">
         <v>107</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BL1" t="s">
         <v>108</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BM1" t="s">
         <v>109</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BN1" t="s">
         <v>110</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BO1" t="s">
         <v>111</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BP1" t="s">
         <v>112</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BQ1" t="s">
         <v>113</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BR1" t="s">
         <v>114</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BS1" t="s">
         <v>115</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BT1" t="s">
         <v>116</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BU1" t="s">
         <v>117</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BV1" t="s">
         <v>118</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BW1" t="s">
         <v>119</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BX1" t="s">
         <v>120</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BY1" t="s">
         <v>121</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BZ1" t="s">
         <v>122</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="CA1" t="s">
         <v>123</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="CB1" t="s">
         <v>124</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="CC1" t="s">
         <v>125</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="CD1" t="s">
         <v>126</v>
       </c>
-      <c r="BS1" t="s">
+      <c r="CE1" t="s">
         <v>127</v>
       </c>
-      <c r="BT1" t="s">
+      <c r="CF1" t="s">
         <v>128</v>
       </c>
-      <c r="BU1" t="s">
+      <c r="CG1" t="s">
         <v>129</v>
       </c>
-      <c r="BV1" t="s">
+      <c r="CH1" t="s">
         <v>130</v>
       </c>
-      <c r="BW1" t="s">
+      <c r="CI1" t="s">
         <v>131</v>
       </c>
-      <c r="BX1" t="s">
+      <c r="CJ1" t="s">
         <v>132</v>
       </c>
-      <c r="BY1" t="s">
+      <c r="CK1" t="s">
         <v>133</v>
       </c>
-      <c r="BZ1" t="s">
+      <c r="CL1" t="s">
         <v>134</v>
       </c>
-      <c r="CA1" t="s">
+      <c r="CM1" t="s">
         <v>135</v>
       </c>
-      <c r="CB1" t="s">
+      <c r="CN1" t="s">
         <v>136</v>
       </c>
-      <c r="CC1" t="s">
+      <c r="CO1" t="s">
         <v>137</v>
       </c>
-      <c r="CD1" t="s">
+      <c r="CP1" t="s">
         <v>138</v>
       </c>
-      <c r="CE1" t="s">
+      <c r="CQ1" t="s">
         <v>139</v>
       </c>
-      <c r="CF1" t="s">
+      <c r="CR1" t="s">
         <v>140</v>
       </c>
-      <c r="CG1" t="s">
+      <c r="CS1" t="s">
         <v>141</v>
       </c>
-      <c r="CH1" t="s">
+      <c r="CT1" t="s">
         <v>142</v>
       </c>
-      <c r="CI1" t="s">
+      <c r="CU1" t="s">
         <v>143</v>
       </c>
-      <c r="CJ1" t="s">
+      <c r="CV1" t="s">
         <v>144</v>
       </c>
-      <c r="CK1" t="s">
+      <c r="CW1" t="s">
         <v>145</v>
       </c>
-      <c r="CL1" t="s">
+      <c r="CX1" t="s">
         <v>146</v>
       </c>
-      <c r="CM1" t="s">
+      <c r="CY1" t="s">
         <v>147</v>
       </c>
-      <c r="CN1" t="s">
+      <c r="CZ1" t="s">
         <v>148</v>
       </c>
-      <c r="CO1" t="s">
+      <c r="DA1" t="s">
         <v>149</v>
       </c>
-      <c r="CP1" t="s">
+      <c r="DB1" t="s">
         <v>150</v>
       </c>
-      <c r="CQ1" t="s">
+      <c r="DC1" t="s">
         <v>151</v>
       </c>
-      <c r="CR1" t="s">
+      <c r="DD1" t="s">
         <v>152</v>
       </c>
-      <c r="CS1" t="s">
+      <c r="DE1" t="s">
         <v>153</v>
       </c>
-      <c r="CT1" t="s">
+      <c r="DF1" t="s">
         <v>154</v>
       </c>
-      <c r="CU1" t="s">
+      <c r="DG1" t="s">
         <v>155</v>
       </c>
-      <c r="CV1" t="s">
+      <c r="DH1" t="s">
         <v>156</v>
       </c>
-      <c r="CW1" t="s">
+      <c r="DI1" t="s">
         <v>157</v>
       </c>
-      <c r="CX1" t="s">
+      <c r="DJ1" t="s">
         <v>158</v>
       </c>
-      <c r="CY1" t="s">
+      <c r="DK1" t="s">
         <v>159</v>
       </c>
-      <c r="CZ1" t="s">
+      <c r="DL1" t="s">
         <v>160</v>
       </c>
-      <c r="DA1" t="s">
+      <c r="DM1" t="s">
         <v>161</v>
       </c>
-      <c r="DB1" t="s">
+      <c r="DN1" t="s">
         <v>162</v>
       </c>
-      <c r="DC1" t="s">
+      <c r="DO1" t="s">
         <v>163</v>
       </c>
-      <c r="DD1" t="s">
+      <c r="DP1" t="s">
         <v>164</v>
       </c>
-      <c r="DE1" t="s">
+      <c r="DQ1" t="s">
         <v>165</v>
       </c>
-      <c r="DF1" t="s">
+      <c r="DR1" t="s">
         <v>166</v>
       </c>
-      <c r="DG1" t="s">
+      <c r="DS1" t="s">
         <v>167</v>
       </c>
-      <c r="DH1" t="s">
+      <c r="DT1" t="s">
         <v>168</v>
       </c>
-      <c r="DI1" t="s">
+      <c r="DU1" t="s">
         <v>169</v>
       </c>
-      <c r="DJ1" t="s">
+      <c r="DV1" t="s">
         <v>170</v>
       </c>
-      <c r="DK1" t="s">
+      <c r="DW1" t="s">
         <v>171</v>
       </c>
-      <c r="DL1" t="s">
+      <c r="DX1" t="s">
         <v>172</v>
       </c>
-      <c r="DM1" t="s">
+      <c r="DY1" t="s">
         <v>173</v>
       </c>
-      <c r="DN1" t="s">
-        <v>174</v>
-      </c>
-      <c r="DO1" t="s">
-        <v>175</v>
-      </c>
-      <c r="DP1" t="s">
-        <v>176</v>
-      </c>
-      <c r="DQ1" t="s">
-        <v>177</v>
-      </c>
-      <c r="DR1" t="s">
-        <v>178</v>
-      </c>
-      <c r="DS1" t="s">
-        <v>179</v>
-      </c>
-      <c r="DT1" t="s">
-        <v>180</v>
-      </c>
-      <c r="DU1" t="s">
-        <v>181</v>
-      </c>
-      <c r="DV1" t="s">
+      <c r="DZ1" t="s">
         <v>182</v>
       </c>
-      <c r="DW1" t="s">
-        <v>183</v>
-      </c>
-      <c r="DX1" t="s">
-        <v>184</v>
-      </c>
-      <c r="DY1" t="s">
-        <v>185</v>
-      </c>
-      <c r="DZ1" t="s">
+      <c r="EA1" t="s">
+        <v>191</v>
+      </c>
+      <c r="EB1" t="s">
+        <v>192</v>
+      </c>
+      <c r="EC1" t="s">
         <v>194</v>
       </c>
-      <c r="EA1" t="s">
+      <c r="ED1" t="s">
+        <v>197</v>
+      </c>
+      <c r="EE1" t="s">
         <v>203</v>
       </c>
-      <c r="EB1" t="s">
-        <v>204</v>
-      </c>
-      <c r="EC1" t="s">
-        <v>206</v>
-      </c>
-      <c r="ED1" t="s">
-        <v>209</v>
-      </c>
-      <c r="EE1" t="s">
-        <v>215</v>
-      </c>
       <c r="EF1" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="EG1" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="EH1" t="s">
+        <v>228</v>
+      </c>
+      <c r="EI1" t="s">
+        <v>237</v>
+      </c>
+      <c r="EJ1" t="s">
+        <v>238</v>
+      </c>
+      <c r="EK1" t="s">
         <v>240</v>
       </c>
-      <c r="EI1" t="s">
+      <c r="EL1" t="s">
         <v>249</v>
       </c>
-      <c r="EJ1" t="s">
-        <v>250</v>
-      </c>
-      <c r="EK1" t="s">
-        <v>252</v>
-      </c>
-      <c r="EL1" t="s">
-        <v>261</v>
-      </c>
       <c r="EM1" t="s">
+        <v>251</v>
+      </c>
+      <c r="EN1" t="s">
+        <v>253</v>
+      </c>
+      <c r="EO1" t="s">
+        <v>258</v>
+      </c>
+      <c r="EP1" t="s">
+        <v>262</v>
+      </c>
+      <c r="EQ1" t="s">
         <v>263</v>
       </c>
-      <c r="EN1" t="s">
-        <v>265</v>
-      </c>
-      <c r="EO1" t="s">
-        <v>270</v>
-      </c>
-      <c r="EP1" t="s">
-        <v>274</v>
-      </c>
-      <c r="EQ1" t="s">
+      <c r="ER1" t="s">
+        <v>264</v>
+      </c>
+      <c r="ES1" t="s">
+        <v>273</v>
+      </c>
+      <c r="ET1" t="s">
         <v>275</v>
       </c>
-      <c r="ER1" t="s">
-        <v>276</v>
-      </c>
-      <c r="ES1" t="s">
-        <v>285</v>
-      </c>
-      <c r="ET1" t="s">
-        <v>287</v>
-      </c>
       <c r="EU1" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="EV1" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="EW1" t="s">
+        <v>279</v>
+      </c>
+      <c r="EX1" t="s">
+        <v>281</v>
+      </c>
+      <c r="EY1" t="s">
+        <v>282</v>
+      </c>
+      <c r="EZ1" t="s">
         <v>291</v>
       </c>
-      <c r="EX1" t="s">
+      <c r="FA1" t="s">
         <v>293</v>
       </c>
-      <c r="EY1" t="s">
-        <v>294</v>
-      </c>
-      <c r="EZ1" t="s">
-        <v>303</v>
-      </c>
-      <c r="FA1" t="s">
-        <v>305</v>
-      </c>
       <c r="FB1" t="s">
-        <v>307</v>
+        <v>295</v>
       </c>
       <c r="FC1" t="s">
+        <v>304</v>
+      </c>
+      <c r="FD1" t="s">
+        <v>313</v>
+      </c>
+      <c r="FE1" t="s">
+        <v>314</v>
+      </c>
+      <c r="FF1" t="s">
+        <v>315</v>
+      </c>
+      <c r="FG1" t="s">
         <v>316</v>
       </c>
-      <c r="FD1" t="s">
-        <v>325</v>
-      </c>
-      <c r="FE1" t="s">
+      <c r="FH1" t="s">
+        <v>319</v>
+      </c>
+      <c r="FI1" t="s">
+        <v>320</v>
+      </c>
+      <c r="FJ1" t="s">
+        <v>321</v>
+      </c>
+      <c r="FK1" t="s">
+        <v>323</v>
+      </c>
+      <c r="FL1" t="s">
         <v>326</v>
       </c>
-      <c r="FF1" t="s">
-        <v>327</v>
-      </c>
-      <c r="FG1" t="s">
-        <v>328</v>
-      </c>
-      <c r="FH1" t="s">
+      <c r="FM1" t="s">
+        <v>330</v>
+      </c>
+      <c r="FN1" t="s">
         <v>331</v>
       </c>
-      <c r="FI1" t="s">
-        <v>332</v>
-      </c>
-      <c r="FJ1" t="s">
-        <v>333</v>
-      </c>
-      <c r="FK1" t="s">
-        <v>335</v>
-      </c>
-      <c r="FL1" t="s">
-        <v>338</v>
-      </c>
-      <c r="FM1" t="s">
-        <v>342</v>
-      </c>
-      <c r="FN1" t="s">
-        <v>343</v>
-      </c>
       <c r="FO1" t="s">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="FP1" t="s">
+        <v>347</v>
+      </c>
+      <c r="FQ1" t="s">
+        <v>356</v>
+      </c>
+      <c r="FR1" t="s">
+        <v>358</v>
+      </c>
+      <c r="FS1" t="s">
         <v>359</v>
       </c>
-      <c r="FQ1" t="s">
-        <v>368</v>
-      </c>
-      <c r="FR1" t="s">
-        <v>370</v>
-      </c>
-      <c r="FS1" t="s">
-        <v>371</v>
-      </c>
       <c r="FT1" t="s">
-        <v>373</v>
+        <v>361</v>
       </c>
       <c r="FU1" t="s">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c r="FV1" t="s">
-        <v>375</v>
+        <v>363</v>
       </c>
       <c r="FW1" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="FX1" t="s">
-        <v>377</v>
+        <v>365</v>
       </c>
       <c r="FY1" t="s">
-        <v>379</v>
+        <v>367</v>
       </c>
     </row>
     <row r="2">
@@ -2109,55 +2073,55 @@
         <v>49</v>
       </c>
       <c r="DY2" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="DZ2" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="EA2" t="s">
         <v>17</v>
       </c>
       <c r="EB2" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="EC2" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="ED2" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="EE2" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="EF2" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="EG2" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="EH2" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="EI2" t="s">
         <v>17</v>
       </c>
       <c r="EJ2" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="EK2" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="EL2" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="EM2" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="EN2" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="EO2" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="EP2" s="2">
         <v>52</v>
@@ -2166,40 +2130,40 @@
         <v>111</v>
       </c>
       <c r="ER2" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="ES2" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="ET2" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="EU2" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="EV2" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="EW2" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="EX2" s="2">
         <v>60</v>
       </c>
       <c r="EY2" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="EZ2" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="FA2" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="FB2" t="s">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="FC2" t="s">
-        <v>317</v>
+        <v>305</v>
       </c>
       <c r="FD2" s="2">
         <v>315</v>
@@ -2211,56 +2175,56 @@
         <v>2024</v>
       </c>
       <c r="FG2" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="FH2" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="FI2" t="s">
         <v>2</v>
       </c>
       <c r="FJ2" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="FK2" t="s">
         <v>2</v>
       </c>
       <c r="FL2" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="FM2" s="1">
         <v>45840</v>
       </c>
       <c r="FN2" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="FO2" t="s">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="FP2" t="s">
+        <v>348</v>
+      </c>
+      <c r="FQ2" t="s">
+        <v>204</v>
+      </c>
+      <c r="FR2" t="s">
+        <v>183</v>
+      </c>
+      <c r="FS2" t="s">
         <v>360</v>
       </c>
-      <c r="FQ2" t="s">
-        <v>216</v>
-      </c>
-      <c r="FR2" t="s">
-        <v>195</v>
-      </c>
-      <c r="FS2" t="s">
-        <v>372</v>
-      </c>
       <c r="FT2" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="FU2" t="s">
         <v>17</v>
       </c>
       <c r="FV2" s="2"/>
       <c r="FW2" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="FX2" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="FY2" s="2">
         <v>1</v>
@@ -2328,7 +2292,7 @@
         <v>39</v>
       </c>
       <c r="U3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="V3" t="s">
         <v>39</v>
@@ -2355,7 +2319,7 @@
         <v>1</v>
       </c>
       <c r="AD3" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="AE3" s="2">
         <v>0</v>
@@ -3105,55 +3069,55 @@
         <v>46</v>
       </c>
       <c r="DY4" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="DZ4" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="EA4" t="s">
         <v>19</v>
       </c>
       <c r="EB4" t="s">
+        <v>193</v>
+      </c>
+      <c r="EC4" t="s">
+        <v>195</v>
+      </c>
+      <c r="ED4" t="s">
+        <v>199</v>
+      </c>
+      <c r="EE4" t="s">
         <v>205</v>
       </c>
-      <c r="EC4" t="s">
-        <v>207</v>
-      </c>
-      <c r="ED4" t="s">
-        <v>211</v>
-      </c>
-      <c r="EE4" t="s">
-        <v>217</v>
-      </c>
       <c r="EF4" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="EG4" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="EH4" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="EI4" t="s">
         <v>19</v>
       </c>
       <c r="EJ4" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="EK4" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="EL4" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="EM4" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="EN4" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="EO4" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="EP4" s="2">
         <v>42</v>
@@ -3162,40 +3126,40 @@
         <v>84</v>
       </c>
       <c r="ER4" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="ES4" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="ET4" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="EU4" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="EV4" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="EW4" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="EX4" s="2">
         <v>43</v>
       </c>
       <c r="EY4" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="EZ4" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="FA4" t="s">
+        <v>294</v>
+      </c>
+      <c r="FB4" t="s">
+        <v>297</v>
+      </c>
+      <c r="FC4" t="s">
         <v>306</v>
-      </c>
-      <c r="FB4" t="s">
-        <v>309</v>
-      </c>
-      <c r="FC4" t="s">
-        <v>318</v>
       </c>
       <c r="FD4" s="2">
         <v>254</v>
@@ -3207,56 +3171,56 @@
         <v>2024</v>
       </c>
       <c r="FG4" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="FH4" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="FI4" t="s">
         <v>2</v>
       </c>
       <c r="FJ4" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="FK4" t="s">
         <v>2</v>
       </c>
       <c r="FL4" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="FM4" s="1">
         <v>45840</v>
       </c>
       <c r="FN4" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="FO4" t="s">
         <v>18</v>
       </c>
       <c r="FP4" t="s">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="FQ4" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="FR4" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="FS4" t="s">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="FT4" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="FU4" t="s">
         <v>19</v>
       </c>
       <c r="FV4" s="2"/>
       <c r="FW4" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="FX4" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="FY4" s="2">
         <v>1</v>
@@ -3309,7 +3273,7 @@
         <v>0</v>
       </c>
       <c r="P5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="Q5" s="2">
         <v>0</v>
@@ -3321,19 +3285,19 @@
         <v>0</v>
       </c>
       <c r="T5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="U5" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="V5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="W5" s="2">
         <v>0</v>
       </c>
       <c r="X5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="Y5" s="2">
         <v>0</v>
@@ -3345,25 +3309,25 @@
         <v>1</v>
       </c>
       <c r="AB5" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="AC5" s="2">
         <v>1</v>
       </c>
       <c r="AD5" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="AE5" s="2">
         <v>1</v>
       </c>
       <c r="AF5" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="AG5" s="2">
         <v>0</v>
       </c>
       <c r="AH5" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="AI5" s="2">
         <v>1</v>
@@ -4101,55 +4065,55 @@
         <v>44</v>
       </c>
       <c r="DY6" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="DZ6" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="EA6" t="s">
         <v>20</v>
       </c>
       <c r="EB6" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="EC6" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="ED6" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="EE6" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="EF6" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="EG6" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="EH6" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="EI6" t="s">
         <v>20</v>
       </c>
       <c r="EJ6" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="EK6" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="EL6" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="EM6" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="EN6" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="EO6" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="EP6" s="2">
         <v>47</v>
@@ -4158,40 +4122,40 @@
         <v>101</v>
       </c>
       <c r="ER6" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="ES6" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="ET6" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="EU6" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="EV6" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="EW6" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="EX6" s="2">
         <v>55</v>
       </c>
       <c r="EY6" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="EZ6" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="FA6" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="FB6" t="s">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="FC6" t="s">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="FD6" s="2">
         <v>246</v>
@@ -4203,56 +4167,56 @@
         <v>2024</v>
       </c>
       <c r="FG6" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="FH6" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="FI6" t="s">
         <v>2</v>
       </c>
       <c r="FJ6" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="FK6" t="s">
         <v>2</v>
       </c>
       <c r="FL6" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="FM6" s="1">
         <v>45835</v>
       </c>
       <c r="FN6" t="s">
-        <v>346</v>
+        <v>334</v>
       </c>
       <c r="FO6" t="s">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="FP6" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
       <c r="FQ6" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="FR6" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="FS6" t="s">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="FT6" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="FU6" t="s">
         <v>20</v>
       </c>
       <c r="FV6" s="2"/>
       <c r="FW6" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="FX6" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="FY6" s="2">
         <v>1</v>
@@ -4299,7 +4263,7 @@
         <v>1</v>
       </c>
       <c r="N7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="O7" s="2">
         <v>0</v>
@@ -4317,19 +4281,19 @@
         <v>0</v>
       </c>
       <c r="T7" t="s">
+        <v>54</v>
+      </c>
+      <c r="U7" t="s">
+        <v>57</v>
+      </c>
+      <c r="V7" t="s">
         <v>59</v>
       </c>
-      <c r="U7" t="s">
-        <v>62</v>
-      </c>
-      <c r="V7" t="s">
-        <v>65</v>
-      </c>
       <c r="W7" s="2">
         <v>0</v>
       </c>
       <c r="X7" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="Y7" s="2">
         <v>0</v>
@@ -4341,7 +4305,7 @@
         <v>1</v>
       </c>
       <c r="AB7" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="AC7" s="2">
         <v>0</v>
@@ -4808,7 +4772,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M8" s="2">
         <v>0</v>
@@ -4820,7 +4784,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="Q8" s="2">
         <v>0</v>
@@ -4835,7 +4799,7 @@
         <v>39</v>
       </c>
       <c r="U8" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="V8" t="s">
         <v>39</v>
@@ -4856,13 +4820,13 @@
         <v>1</v>
       </c>
       <c r="AB8" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="AC8" s="2">
         <v>1</v>
       </c>
       <c r="AD8" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="AE8" s="2">
         <v>0</v>
@@ -5610,55 +5574,55 @@
         <v>56</v>
       </c>
       <c r="DY9" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="DZ9" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="EA9" t="s">
         <v>21</v>
       </c>
       <c r="EB9" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="EC9" t="s">
+        <v>195</v>
+      </c>
+      <c r="ED9" t="s">
+        <v>198</v>
+      </c>
+      <c r="EE9" t="s">
         <v>207</v>
       </c>
-      <c r="ED9" t="s">
-        <v>210</v>
-      </c>
-      <c r="EE9" t="s">
-        <v>219</v>
-      </c>
       <c r="EF9" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="EG9" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="EH9" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="EI9" t="s">
         <v>21</v>
       </c>
       <c r="EJ9" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="EK9" t="s">
+        <v>244</v>
+      </c>
+      <c r="EL9" t="s">
+        <v>250</v>
+      </c>
+      <c r="EM9" t="s">
+        <v>252</v>
+      </c>
+      <c r="EN9" t="s">
         <v>256</v>
       </c>
-      <c r="EL9" t="s">
-        <v>262</v>
-      </c>
-      <c r="EM9" t="s">
-        <v>264</v>
-      </c>
-      <c r="EN9" t="s">
-        <v>268</v>
-      </c>
       <c r="EO9" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="EP9" s="2">
         <v>53</v>
@@ -5667,40 +5631,40 @@
         <v>131</v>
       </c>
       <c r="ER9" t="s">
+        <v>268</v>
+      </c>
+      <c r="ES9" t="s">
+        <v>274</v>
+      </c>
+      <c r="ET9" t="s">
+        <v>276</v>
+      </c>
+      <c r="EU9" t="s">
+        <v>239</v>
+      </c>
+      <c r="EV9" t="s">
+        <v>239</v>
+      </c>
+      <c r="EW9" t="s">
         <v>280</v>
-      </c>
-      <c r="ES9" t="s">
-        <v>286</v>
-      </c>
-      <c r="ET9" t="s">
-        <v>288</v>
-      </c>
-      <c r="EU9" t="s">
-        <v>251</v>
-      </c>
-      <c r="EV9" t="s">
-        <v>251</v>
-      </c>
-      <c r="EW9" t="s">
-        <v>292</v>
       </c>
       <c r="EX9" s="2">
         <v>79</v>
       </c>
       <c r="EY9" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="EZ9" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="FA9" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="FB9" t="s">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="FC9" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="FD9" s="2">
         <v>387</v>
@@ -5712,56 +5676,56 @@
         <v>2024</v>
       </c>
       <c r="FG9" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="FH9" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="FI9" t="s">
         <v>2</v>
       </c>
       <c r="FJ9" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="FK9" t="s">
         <v>2</v>
       </c>
       <c r="FL9" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="FM9" s="1">
         <v>45840</v>
       </c>
       <c r="FN9" t="s">
-        <v>347</v>
+        <v>335</v>
       </c>
       <c r="FO9" t="s">
-        <v>354</v>
+        <v>342</v>
       </c>
       <c r="FP9" t="s">
-        <v>363</v>
+        <v>351</v>
       </c>
       <c r="FQ9" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="FR9" t="s">
+        <v>186</v>
+      </c>
+      <c r="FS9" t="s">
+        <v>360</v>
+      </c>
+      <c r="FT9" t="s">
         <v>198</v>
-      </c>
-      <c r="FS9" t="s">
-        <v>372</v>
-      </c>
-      <c r="FT9" t="s">
-        <v>210</v>
       </c>
       <c r="FU9" t="s">
         <v>21</v>
       </c>
       <c r="FV9" s="2"/>
       <c r="FW9" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="FX9" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="FY9" s="2">
         <v>1</v>
@@ -6091,55 +6055,55 @@
         <v>78</v>
       </c>
       <c r="DY10" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="DZ10" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="EA10" t="s">
         <v>22</v>
       </c>
       <c r="EB10" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="EC10" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="ED10" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="EE10" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="EF10" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="EG10" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="EH10" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="EI10" t="s">
         <v>22</v>
       </c>
       <c r="EJ10" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="EK10" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="EL10" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="EM10" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="EN10" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="EO10" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="EP10" s="2">
         <v>52</v>
@@ -6148,40 +6112,40 @@
         <v>117</v>
       </c>
       <c r="ER10" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="ES10" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="ET10" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="EU10" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="EV10" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="EW10" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="EX10" s="2">
         <v>66</v>
       </c>
       <c r="EY10" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="EZ10" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="FA10" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="FB10" t="s">
-        <v>312</v>
+        <v>300</v>
       </c>
       <c r="FC10" t="s">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="FD10" s="2">
         <v>375</v>
@@ -6193,56 +6157,56 @@
         <v>2024</v>
       </c>
       <c r="FG10" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="FH10" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="FI10" t="s">
         <v>2</v>
       </c>
       <c r="FJ10" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="FK10" t="s">
         <v>2</v>
       </c>
       <c r="FL10" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="FM10" s="1">
         <v>45840</v>
       </c>
       <c r="FN10" t="s">
-        <v>348</v>
+        <v>336</v>
       </c>
       <c r="FO10" t="s">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="FP10" t="s">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="FQ10" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="FR10" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="FS10" t="s">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="FT10" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="FU10" t="s">
         <v>22</v>
       </c>
       <c r="FV10" s="2"/>
       <c r="FW10" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="FX10" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="FY10" s="2">
         <v>1</v>
@@ -6295,7 +6259,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="Q11" s="2">
         <v>0</v>
@@ -6310,7 +6274,7 @@
         <v>39</v>
       </c>
       <c r="U11" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="V11" t="s">
         <v>2</v>
@@ -6337,7 +6301,7 @@
         <v>1</v>
       </c>
       <c r="AD11" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="AE11" s="2">
         <v>0</v>
@@ -6796,7 +6760,7 @@
       </c>
       <c r="K12" s="2"/>
       <c r="L12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M12" s="2">
         <v>0</v>
@@ -6820,10 +6784,10 @@
         <v>1</v>
       </c>
       <c r="T12" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="U12" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="V12" t="s">
         <v>2</v>
@@ -6832,7 +6796,7 @@
         <v>4</v>
       </c>
       <c r="X12" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="Y12" s="2">
         <v>0</v>
@@ -7600,55 +7564,55 @@
         <v>140</v>
       </c>
       <c r="DY13" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="DZ13" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="EA13" t="s">
         <v>24</v>
       </c>
       <c r="EB13" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="EC13" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="ED13" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="EE13" t="s">
+        <v>204</v>
+      </c>
+      <c r="EF13" t="s">
         <v>216</v>
       </c>
-      <c r="EF13" t="s">
-        <v>228</v>
-      </c>
       <c r="EG13" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="EH13" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="EI13" t="s">
         <v>24</v>
       </c>
       <c r="EJ13" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="EK13" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="EL13" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="EM13" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="EN13" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="EO13" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="EP13" s="2">
         <v>53</v>
@@ -7657,40 +7621,40 @@
         <v>151</v>
       </c>
       <c r="ER13" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="ES13" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="ET13" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="EU13" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="EV13" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="EW13" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="EX13" s="2">
         <v>99</v>
       </c>
       <c r="EY13" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="EZ13" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="FA13" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="FB13" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="FC13" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="FD13" s="2">
         <v>462</v>
@@ -7702,56 +7666,56 @@
         <v>2024</v>
       </c>
       <c r="FG13" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="FH13" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="FI13" t="s">
         <v>2</v>
       </c>
       <c r="FJ13" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="FK13" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="FL13" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="FM13" s="1">
         <v>45840</v>
       </c>
       <c r="FN13" t="s">
-        <v>349</v>
+        <v>337</v>
       </c>
       <c r="FO13" t="s">
-        <v>356</v>
+        <v>344</v>
       </c>
       <c r="FP13" t="s">
-        <v>365</v>
+        <v>353</v>
       </c>
       <c r="FQ13" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="FR13" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="FS13" t="s">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="FT13" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="FU13" t="s">
         <v>24</v>
       </c>
       <c r="FV13" s="2"/>
       <c r="FW13" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="FX13" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="FY13" s="2">
         <v>1</v>
@@ -7798,13 +7762,13 @@
         <v>1</v>
       </c>
       <c r="N14" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="O14" s="2">
         <v>0</v>
       </c>
       <c r="P14" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="Q14" s="2">
         <v>0</v>
@@ -7819,10 +7783,10 @@
         <v>39</v>
       </c>
       <c r="U14" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="V14" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="W14" s="2">
         <v>0</v>
@@ -7846,13 +7810,13 @@
         <v>1</v>
       </c>
       <c r="AD14" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AE14" s="2">
         <v>1</v>
       </c>
       <c r="AF14" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AG14" s="2">
         <v>0</v>
@@ -8596,55 +8560,55 @@
         <v>98</v>
       </c>
       <c r="DY15" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="DZ15" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="EA15" t="s">
         <v>25</v>
       </c>
       <c r="EB15" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="EC15" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="ED15" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="EE15" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="EF15" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="EG15" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="EH15" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="EI15" t="s">
         <v>25</v>
       </c>
       <c r="EJ15" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="EK15" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="EL15" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="EM15" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="EN15" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="EO15" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="EP15" s="2">
         <v>62</v>
@@ -8653,40 +8617,40 @@
         <v>154</v>
       </c>
       <c r="ER15" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="ES15" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="ET15" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="EU15" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="EV15" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="EW15" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="EX15" s="2">
         <v>93</v>
       </c>
       <c r="EY15" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="EZ15" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="FA15" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="FB15" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="FC15" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="FD15" s="2">
         <v>273</v>
@@ -8698,56 +8662,56 @@
         <v>2024</v>
       </c>
       <c r="FG15" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="FH15" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="FI15" t="s">
         <v>2</v>
       </c>
       <c r="FJ15" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="FK15" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="FL15" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="FM15" s="1">
         <v>45840</v>
       </c>
       <c r="FN15" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="FO15" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="FP15" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
       <c r="FQ15" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="FR15" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="FS15" t="s">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="FT15" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="FU15" t="s">
         <v>25</v>
       </c>
       <c r="FV15" s="2"/>
       <c r="FW15" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="FX15" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="FY15" s="2">
         <v>1</v>
@@ -8815,28 +8779,28 @@
         <v>39</v>
       </c>
       <c r="U16" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="V16" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="W16" s="2">
         <v>0</v>
       </c>
       <c r="X16" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="Y16" s="2">
         <v>1</v>
       </c>
       <c r="Z16" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="AA16" s="2">
         <v>1</v>
       </c>
       <c r="AB16" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="AC16" s="2">
         <v>0</v>
@@ -9592,55 +9556,55 @@
         <v>40</v>
       </c>
       <c r="DY17" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="DZ17" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="EA17" t="s">
         <v>26</v>
       </c>
       <c r="EB17" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="EC17" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="ED17" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="EE17" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="EF17" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="EG17" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="EH17" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="EI17" t="s">
         <v>26</v>
       </c>
       <c r="EJ17" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="EK17" t="s">
+        <v>248</v>
+      </c>
+      <c r="EL17" t="s">
+        <v>250</v>
+      </c>
+      <c r="EM17" t="s">
+        <v>252</v>
+      </c>
+      <c r="EN17" t="s">
+        <v>254</v>
+      </c>
+      <c r="EO17" t="s">
         <v>260</v>
-      </c>
-      <c r="EL17" t="s">
-        <v>262</v>
-      </c>
-      <c r="EM17" t="s">
-        <v>264</v>
-      </c>
-      <c r="EN17" t="s">
-        <v>266</v>
-      </c>
-      <c r="EO17" t="s">
-        <v>272</v>
       </c>
       <c r="EP17" s="2">
         <v>62</v>
@@ -9649,40 +9613,40 @@
         <v>100</v>
       </c>
       <c r="ER17" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="ES17" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="ET17" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="EU17" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="EV17" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="EW17" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="EX17" s="2">
         <v>39</v>
       </c>
       <c r="EY17" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="EZ17" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="FA17" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="FB17" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="FC17" t="s">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="FD17" s="2">
         <v>301</v>
@@ -9694,56 +9658,56 @@
         <v>2024</v>
       </c>
       <c r="FG17" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="FH17" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="FI17" t="s">
         <v>2</v>
       </c>
       <c r="FJ17" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="FK17" t="s">
         <v>2</v>
       </c>
       <c r="FL17" t="s">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="FM17" s="1">
         <v>45847</v>
       </c>
       <c r="FN17" t="s">
-        <v>350</v>
+        <v>338</v>
       </c>
       <c r="FO17" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="FP17" t="s">
-        <v>367</v>
+        <v>355</v>
       </c>
       <c r="FQ17" t="s">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="FR17" t="s">
+        <v>190</v>
+      </c>
+      <c r="FS17" t="s">
+        <v>360</v>
+      </c>
+      <c r="FT17" t="s">
         <v>202</v>
-      </c>
-      <c r="FS17" t="s">
-        <v>372</v>
-      </c>
-      <c r="FT17" t="s">
-        <v>214</v>
       </c>
       <c r="FU17" t="s">
         <v>26</v>
       </c>
       <c r="FV17" s="2"/>
       <c r="FW17" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="FX17" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="FY17" s="2">
         <v>1</v>

--- a/test_data.xlsx
+++ b/test_data.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1189" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="2378" uniqueCount="368">
   <si>
     <t>publication_date_2025</t>
   </si>
@@ -2594,87 +2594,107 @@
       <c r="DQ3" s="2">
         <v>2025</v>
       </c>
-      <c r="DR3" s="2"/>
-      <c r="DS3" s="2"/>
-      <c r="DT3" s="2"/>
-      <c r="DU3" s="2"/>
-      <c r="DV3" s="2"/>
-      <c r="DW3" s="2"/>
-      <c r="DX3" s="2"/>
+      <c r="DR3" s="2">
+        <v>315</v>
+      </c>
+      <c r="DS3" s="2">
+        <v>369</v>
+      </c>
+      <c r="DT3" s="2">
+        <v>37116</v>
+      </c>
+      <c r="DU3" s="2">
+        <v>22.288833618164063</v>
+      </c>
+      <c r="DV3" s="2">
+        <v>1140</v>
+      </c>
+      <c r="DW3" s="2">
+        <v>0.051753658801317215</v>
+      </c>
+      <c r="DX3" s="2">
+        <v>49</v>
+      </c>
       <c r="DY3" t="s">
-        <v>2</v>
+        <v>174</v>
       </c>
       <c r="DZ3" t="s">
-        <v>2</v>
+        <v>183</v>
       </c>
       <c r="EA3" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="EB3" t="s">
-        <v>2</v>
+        <v>193</v>
       </c>
       <c r="EC3" t="s">
-        <v>2</v>
+        <v>195</v>
       </c>
       <c r="ED3" t="s">
-        <v>2</v>
+        <v>198</v>
       </c>
       <c r="EE3" t="s">
-        <v>2</v>
+        <v>204</v>
       </c>
       <c r="EF3" t="s">
-        <v>2</v>
+        <v>211</v>
       </c>
       <c r="EG3" t="s">
-        <v>2</v>
+        <v>220</v>
       </c>
       <c r="EH3" t="s">
-        <v>2</v>
+        <v>229</v>
       </c>
       <c r="EI3" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="EJ3" t="s">
-        <v>2</v>
+        <v>239</v>
       </c>
       <c r="EK3" t="s">
-        <v>2</v>
+        <v>241</v>
       </c>
       <c r="EL3" t="s">
-        <v>2</v>
+        <v>250</v>
       </c>
       <c r="EM3" t="s">
-        <v>2</v>
+        <v>252</v>
       </c>
       <c r="EN3" t="s">
-        <v>2</v>
+        <v>254</v>
       </c>
       <c r="EO3" t="s">
-        <v>2</v>
-      </c>
-      <c r="EP3" s="2"/>
-      <c r="EQ3" s="2"/>
+        <v>259</v>
+      </c>
+      <c r="EP3" s="2">
+        <v>52</v>
+      </c>
+      <c r="EQ3" s="2">
+        <v>111</v>
+      </c>
       <c r="ER3" t="s">
-        <v>2</v>
+        <v>265</v>
       </c>
       <c r="ES3" t="s">
-        <v>2</v>
+        <v>274</v>
       </c>
       <c r="ET3" t="s">
-        <v>2</v>
+        <v>276</v>
       </c>
       <c r="EU3" t="s">
-        <v>2</v>
+        <v>239</v>
       </c>
       <c r="EV3" t="s">
-        <v>2</v>
+        <v>239</v>
       </c>
       <c r="EW3" t="s">
-        <v>2</v>
-      </c>
-      <c r="EX3" s="2"/>
+        <v>280</v>
+      </c>
+      <c r="EX3" s="2">
+        <v>60</v>
+      </c>
       <c r="EY3" t="s">
-        <v>2</v>
+        <v>283</v>
       </c>
       <c r="EZ3" t="s">
         <v>2</v>
@@ -3590,87 +3610,107 @@
       <c r="DQ5" s="2">
         <v>2025</v>
       </c>
-      <c r="DR5" s="2"/>
-      <c r="DS5" s="2"/>
-      <c r="DT5" s="2"/>
-      <c r="DU5" s="2"/>
-      <c r="DV5" s="2"/>
-      <c r="DW5" s="2"/>
-      <c r="DX5" s="2"/>
+      <c r="DR5" s="2">
+        <v>254</v>
+      </c>
+      <c r="DS5" s="2">
+        <v>357</v>
+      </c>
+      <c r="DT5" s="2">
+        <v>27483</v>
+      </c>
+      <c r="DU5" s="2">
+        <v>16.569766998291016</v>
+      </c>
+      <c r="DV5" s="2">
+        <v>1055</v>
+      </c>
+      <c r="DW5" s="2">
+        <v>0.048195261508226395</v>
+      </c>
+      <c r="DX5" s="2">
+        <v>46</v>
+      </c>
       <c r="DY5" t="s">
-        <v>2</v>
+        <v>175</v>
       </c>
       <c r="DZ5" t="s">
-        <v>2</v>
+        <v>184</v>
       </c>
       <c r="EA5" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="EB5" t="s">
-        <v>2</v>
+        <v>193</v>
       </c>
       <c r="EC5" t="s">
-        <v>2</v>
+        <v>195</v>
       </c>
       <c r="ED5" t="s">
-        <v>2</v>
+        <v>199</v>
       </c>
       <c r="EE5" t="s">
-        <v>2</v>
+        <v>205</v>
       </c>
       <c r="EF5" t="s">
-        <v>2</v>
+        <v>212</v>
       </c>
       <c r="EG5" t="s">
-        <v>2</v>
+        <v>221</v>
       </c>
       <c r="EH5" t="s">
-        <v>2</v>
+        <v>230</v>
       </c>
       <c r="EI5" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="EJ5" t="s">
-        <v>2</v>
+        <v>239</v>
       </c>
       <c r="EK5" t="s">
-        <v>2</v>
+        <v>242</v>
       </c>
       <c r="EL5" t="s">
-        <v>2</v>
+        <v>250</v>
       </c>
       <c r="EM5" t="s">
-        <v>2</v>
+        <v>252</v>
       </c>
       <c r="EN5" t="s">
-        <v>2</v>
+        <v>255</v>
       </c>
       <c r="EO5" t="s">
-        <v>2</v>
-      </c>
-      <c r="EP5" s="2"/>
-      <c r="EQ5" s="2"/>
+        <v>260</v>
+      </c>
+      <c r="EP5" s="2">
+        <v>42</v>
+      </c>
+      <c r="EQ5" s="2">
+        <v>84</v>
+      </c>
       <c r="ER5" t="s">
-        <v>2</v>
+        <v>266</v>
       </c>
       <c r="ES5" t="s">
-        <v>2</v>
+        <v>274</v>
       </c>
       <c r="ET5" t="s">
-        <v>2</v>
+        <v>276</v>
       </c>
       <c r="EU5" t="s">
-        <v>2</v>
+        <v>239</v>
       </c>
       <c r="EV5" t="s">
-        <v>2</v>
+        <v>239</v>
       </c>
       <c r="EW5" t="s">
-        <v>2</v>
-      </c>
-      <c r="EX5" s="2"/>
+        <v>280</v>
+      </c>
+      <c r="EX5" s="2">
+        <v>43</v>
+      </c>
       <c r="EY5" t="s">
-        <v>2</v>
+        <v>284</v>
       </c>
       <c r="EZ5" t="s">
         <v>2</v>
@@ -4586,87 +4626,107 @@
       <c r="DQ7" s="2">
         <v>2025</v>
       </c>
-      <c r="DR7" s="2"/>
-      <c r="DS7" s="2"/>
-      <c r="DT7" s="2"/>
-      <c r="DU7" s="2"/>
-      <c r="DV7" s="2"/>
-      <c r="DW7" s="2"/>
-      <c r="DX7" s="2"/>
+      <c r="DR7" s="2">
+        <v>246</v>
+      </c>
+      <c r="DS7" s="2">
+        <v>258</v>
+      </c>
+      <c r="DT7" s="2">
+        <v>22534</v>
+      </c>
+      <c r="DU7" s="2">
+        <v>30.837818145751953</v>
+      </c>
+      <c r="DV7" s="2">
+        <v>916</v>
+      </c>
+      <c r="DW7" s="2">
+        <v>0.12325027585029602</v>
+      </c>
+      <c r="DX7" s="2">
+        <v>44</v>
+      </c>
       <c r="DY7" t="s">
-        <v>2</v>
+        <v>176</v>
       </c>
       <c r="DZ7" t="s">
-        <v>2</v>
+        <v>185</v>
       </c>
       <c r="EA7" t="s">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="EB7" t="s">
-        <v>2</v>
+        <v>193</v>
       </c>
       <c r="EC7" t="s">
-        <v>2</v>
+        <v>195</v>
       </c>
       <c r="ED7" t="s">
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="EE7" t="s">
-        <v>2</v>
+        <v>206</v>
       </c>
       <c r="EF7" t="s">
-        <v>2</v>
+        <v>213</v>
       </c>
       <c r="EG7" t="s">
-        <v>2</v>
+        <v>222</v>
       </c>
       <c r="EH7" t="s">
-        <v>2</v>
+        <v>231</v>
       </c>
       <c r="EI7" t="s">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="EJ7" t="s">
-        <v>2</v>
+        <v>239</v>
       </c>
       <c r="EK7" t="s">
-        <v>2</v>
+        <v>243</v>
       </c>
       <c r="EL7" t="s">
-        <v>2</v>
+        <v>250</v>
       </c>
       <c r="EM7" t="s">
-        <v>2</v>
+        <v>252</v>
       </c>
       <c r="EN7" t="s">
-        <v>2</v>
+        <v>254</v>
       </c>
       <c r="EO7" t="s">
-        <v>2</v>
-      </c>
-      <c r="EP7" s="2"/>
-      <c r="EQ7" s="2"/>
+        <v>261</v>
+      </c>
+      <c r="EP7" s="2">
+        <v>47</v>
+      </c>
+      <c r="EQ7" s="2">
+        <v>101</v>
+      </c>
       <c r="ER7" t="s">
-        <v>2</v>
+        <v>267</v>
       </c>
       <c r="ES7" t="s">
-        <v>2</v>
+        <v>274</v>
       </c>
       <c r="ET7" t="s">
-        <v>2</v>
+        <v>276</v>
       </c>
       <c r="EU7" t="s">
-        <v>2</v>
+        <v>239</v>
       </c>
       <c r="EV7" t="s">
-        <v>2</v>
+        <v>239</v>
       </c>
       <c r="EW7" t="s">
-        <v>2</v>
-      </c>
-      <c r="EX7" s="2"/>
+        <v>280</v>
+      </c>
+      <c r="EX7" s="2">
+        <v>55</v>
+      </c>
       <c r="EY7" t="s">
-        <v>2</v>
+        <v>285</v>
       </c>
       <c r="EZ7" t="s">
         <v>2</v>
@@ -4738,11 +4798,9 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1">
-        <v>45680</v>
-      </c>
+      <c r="A8" s="1"/>
       <c r="B8" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C8" t="s">
         <v>11</v>
@@ -4750,93 +4808,65 @@
       <c r="D8" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="2">
-        <v>1</v>
-      </c>
+      <c r="E8" s="2"/>
       <c r="F8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G8" s="1">
-        <v>46055</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="G8" s="1"/>
       <c r="H8" t="s">
         <v>2</v>
       </c>
-      <c r="I8" s="2">
-        <v>1</v>
-      </c>
+      <c r="I8" s="2"/>
       <c r="J8" t="s">
-        <v>41</v>
-      </c>
-      <c r="K8" s="2">
-        <v>0</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="K8" s="2"/>
       <c r="L8" t="s">
-        <v>43</v>
-      </c>
-      <c r="M8" s="2">
-        <v>0</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M8" s="2"/>
       <c r="N8" t="s">
-        <v>39</v>
-      </c>
-      <c r="O8" s="2">
-        <v>0</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="O8" s="2"/>
       <c r="P8" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q8" s="2">
-        <v>0</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="Q8" s="2"/>
       <c r="R8" t="s">
-        <v>39</v>
-      </c>
-      <c r="S8" s="2">
-        <v>0</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="S8" s="2"/>
       <c r="T8" t="s">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="U8" t="s">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="V8" t="s">
-        <v>39</v>
-      </c>
-      <c r="W8" s="2">
-        <v>0</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="W8" s="2"/>
       <c r="X8" t="s">
-        <v>39</v>
-      </c>
-      <c r="Y8" s="2">
-        <v>0</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="Y8" s="2"/>
       <c r="Z8" t="s">
-        <v>39</v>
-      </c>
-      <c r="AA8" s="2">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AA8" s="2"/>
       <c r="AB8" t="s">
-        <v>69</v>
-      </c>
-      <c r="AC8" s="2">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AC8" s="2"/>
       <c r="AD8" t="s">
-        <v>74</v>
-      </c>
-      <c r="AE8" s="2">
-        <v>0</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AE8" s="2"/>
       <c r="AF8" t="s">
         <v>2</v>
       </c>
-      <c r="AG8" s="2">
-        <v>0</v>
-      </c>
+      <c r="AG8" s="2"/>
       <c r="AH8" t="s">
         <v>2</v>
       </c>
@@ -4867,9 +4897,7 @@
       <c r="AQ8" s="2">
         <v>0</v>
       </c>
-      <c r="AR8" s="2">
-        <v>1</v>
-      </c>
+      <c r="AR8" s="2"/>
       <c r="AS8" s="2">
         <v>0</v>
       </c>
@@ -4888,9 +4916,7 @@
       <c r="AX8" s="2">
         <v>0</v>
       </c>
-      <c r="AY8" s="2">
-        <v>0</v>
-      </c>
+      <c r="AY8" s="2"/>
       <c r="AZ8" s="2">
         <v>0</v>
       </c>
@@ -4906,12 +4932,8 @@
       <c r="BD8" s="2">
         <v>0</v>
       </c>
-      <c r="BE8" s="2">
-        <v>0</v>
-      </c>
-      <c r="BF8" s="2">
-        <v>0</v>
-      </c>
+      <c r="BE8" s="2"/>
+      <c r="BF8" s="2"/>
       <c r="BG8" s="2">
         <v>0</v>
       </c>
@@ -4930,9 +4952,7 @@
       <c r="BL8" s="2">
         <v>0</v>
       </c>
-      <c r="BM8" s="2">
-        <v>0</v>
-      </c>
+      <c r="BM8" s="2"/>
       <c r="BN8" s="2">
         <v>1</v>
       </c>
@@ -4946,14 +4966,12 @@
         <v>1</v>
       </c>
       <c r="BR8" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS8" s="2">
         <v>0</v>
       </c>
-      <c r="BT8" s="2">
-        <v>1</v>
-      </c>
+      <c r="BT8" s="2"/>
       <c r="BU8" s="2">
         <v>1</v>
       </c>
@@ -4975,15 +4993,11 @@
       <c r="CA8" s="2">
         <v>1</v>
       </c>
-      <c r="CB8" s="2">
-        <v>0</v>
-      </c>
+      <c r="CB8" s="2"/>
       <c r="CC8" s="2">
         <v>1</v>
       </c>
-      <c r="CD8" s="2">
-        <v>0</v>
-      </c>
+      <c r="CD8" s="2"/>
       <c r="CE8" s="2">
         <v>1</v>
       </c>
@@ -4993,27 +5007,19 @@
       <c r="CG8" s="2">
         <v>0</v>
       </c>
-      <c r="CH8" s="2">
-        <v>0</v>
-      </c>
+      <c r="CH8" s="2"/>
       <c r="CI8" s="2">
         <v>0</v>
       </c>
-      <c r="CJ8" s="2">
-        <v>0</v>
-      </c>
+      <c r="CJ8" s="2"/>
       <c r="CK8" s="2">
         <v>1</v>
       </c>
-      <c r="CL8" s="2">
-        <v>0</v>
-      </c>
+      <c r="CL8" s="2"/>
       <c r="CM8" s="2">
         <v>0</v>
       </c>
-      <c r="CN8" s="2">
-        <v>0</v>
-      </c>
+      <c r="CN8" s="2"/>
       <c r="CO8" s="2">
         <v>0</v>
       </c>
@@ -5024,9 +5030,7 @@
       <c r="CR8" s="2">
         <v>1</v>
       </c>
-      <c r="CS8" s="2">
-        <v>0</v>
-      </c>
+      <c r="CS8" s="2"/>
       <c r="CT8" s="2">
         <v>0</v>
       </c>
@@ -5042,9 +5046,7 @@
       <c r="CX8" s="2">
         <v>0</v>
       </c>
-      <c r="CY8" s="2">
-        <v>0</v>
-      </c>
+      <c r="CY8" s="2"/>
       <c r="CZ8" s="2">
         <v>0</v>
       </c>
@@ -5060,9 +5062,7 @@
       <c r="DD8" s="2">
         <v>0</v>
       </c>
-      <c r="DE8" s="2">
-        <v>0</v>
-      </c>
+      <c r="DE8" s="2"/>
       <c r="DF8" s="2">
         <v>1</v>
       </c>
@@ -5097,163 +5097,193 @@
         <v>0</v>
       </c>
       <c r="DQ8" s="2">
-        <v>2025</v>
-      </c>
-      <c r="DR8" s="2"/>
-      <c r="DS8" s="2"/>
-      <c r="DT8" s="2"/>
-      <c r="DU8" s="2"/>
-      <c r="DV8" s="2"/>
-      <c r="DW8" s="2"/>
-      <c r="DX8" s="2"/>
+        <v>2024</v>
+      </c>
+      <c r="DR8" s="2">
+        <v>387</v>
+      </c>
+      <c r="DS8" s="2">
+        <v>725</v>
+      </c>
+      <c r="DT8" s="2">
+        <v>36918</v>
+      </c>
+      <c r="DU8" s="2">
+        <v>20.384178161621094</v>
+      </c>
+      <c r="DV8" s="2">
+        <v>1182</v>
+      </c>
+      <c r="DW8" s="2">
+        <v>0.25176948308944702</v>
+      </c>
+      <c r="DX8" s="2">
+        <v>56</v>
+      </c>
       <c r="DY8" t="s">
-        <v>2</v>
+        <v>177</v>
       </c>
       <c r="DZ8" t="s">
-        <v>2</v>
+        <v>186</v>
       </c>
       <c r="EA8" t="s">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="EB8" t="s">
-        <v>2</v>
+        <v>193</v>
       </c>
       <c r="EC8" t="s">
-        <v>2</v>
+        <v>195</v>
       </c>
       <c r="ED8" t="s">
-        <v>2</v>
+        <v>198</v>
       </c>
       <c r="EE8" t="s">
-        <v>2</v>
+        <v>207</v>
       </c>
       <c r="EF8" t="s">
-        <v>2</v>
+        <v>214</v>
       </c>
       <c r="EG8" t="s">
-        <v>2</v>
+        <v>223</v>
       </c>
       <c r="EH8" t="s">
-        <v>2</v>
+        <v>232</v>
       </c>
       <c r="EI8" t="s">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="EJ8" t="s">
-        <v>2</v>
+        <v>239</v>
       </c>
       <c r="EK8" t="s">
-        <v>2</v>
+        <v>244</v>
       </c>
       <c r="EL8" t="s">
-        <v>2</v>
+        <v>250</v>
       </c>
       <c r="EM8" t="s">
-        <v>2</v>
+        <v>252</v>
       </c>
       <c r="EN8" t="s">
-        <v>2</v>
+        <v>256</v>
       </c>
       <c r="EO8" t="s">
-        <v>2</v>
-      </c>
-      <c r="EP8" s="2"/>
-      <c r="EQ8" s="2"/>
+        <v>260</v>
+      </c>
+      <c r="EP8" s="2">
+        <v>53</v>
+      </c>
+      <c r="EQ8" s="2">
+        <v>131</v>
+      </c>
       <c r="ER8" t="s">
-        <v>2</v>
+        <v>268</v>
       </c>
       <c r="ES8" t="s">
-        <v>2</v>
+        <v>274</v>
       </c>
       <c r="ET8" t="s">
-        <v>2</v>
+        <v>276</v>
       </c>
       <c r="EU8" t="s">
-        <v>2</v>
+        <v>239</v>
       </c>
       <c r="EV8" t="s">
-        <v>2</v>
+        <v>239</v>
       </c>
       <c r="EW8" t="s">
-        <v>2</v>
-      </c>
-      <c r="EX8" s="2"/>
+        <v>280</v>
+      </c>
+      <c r="EX8" s="2">
+        <v>79</v>
+      </c>
       <c r="EY8" t="s">
-        <v>2</v>
+        <v>286</v>
       </c>
       <c r="EZ8" t="s">
-        <v>2</v>
+        <v>292</v>
       </c>
       <c r="FA8" t="s">
-        <v>2</v>
+        <v>294</v>
       </c>
       <c r="FB8" t="s">
-        <v>2</v>
+        <v>299</v>
       </c>
       <c r="FC8" t="s">
-        <v>2</v>
-      </c>
-      <c r="FD8" s="2"/>
-      <c r="FE8" s="2"/>
-      <c r="FF8" s="2"/>
+        <v>308</v>
+      </c>
+      <c r="FD8" s="2">
+        <v>387</v>
+      </c>
+      <c r="FE8" s="2">
+        <v>725</v>
+      </c>
+      <c r="FF8" s="2">
+        <v>2024</v>
+      </c>
       <c r="FG8" t="s">
-        <v>2</v>
+        <v>317</v>
       </c>
       <c r="FH8" t="s">
-        <v>2</v>
+        <v>268</v>
       </c>
       <c r="FI8" t="s">
         <v>2</v>
       </c>
       <c r="FJ8" t="s">
-        <v>2</v>
+        <v>322</v>
       </c>
       <c r="FK8" t="s">
         <v>2</v>
       </c>
       <c r="FL8" t="s">
-        <v>2</v>
-      </c>
-      <c r="FM8" s="1"/>
+        <v>327</v>
+      </c>
+      <c r="FM8" s="1">
+        <v>45840</v>
+      </c>
       <c r="FN8" t="s">
-        <v>2</v>
+        <v>335</v>
       </c>
       <c r="FO8" t="s">
-        <v>2</v>
+        <v>342</v>
       </c>
       <c r="FP8" t="s">
-        <v>2</v>
+        <v>351</v>
       </c>
       <c r="FQ8" t="s">
-        <v>2</v>
+        <v>207</v>
       </c>
       <c r="FR8" t="s">
-        <v>2</v>
+        <v>186</v>
       </c>
       <c r="FS8" t="s">
-        <v>2</v>
+        <v>360</v>
       </c>
       <c r="FT8" t="s">
-        <v>2</v>
+        <v>198</v>
       </c>
       <c r="FU8" t="s">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="FV8" s="2"/>
       <c r="FW8" t="s">
-        <v>2</v>
+        <v>244</v>
       </c>
       <c r="FX8" t="s">
-        <v>2</v>
+        <v>366</v>
       </c>
       <c r="FY8" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1"/>
+      <c r="A9" s="1">
+        <v>45680</v>
+      </c>
       <c r="B9" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C9" t="s">
         <v>11</v>
@@ -5261,65 +5291,93 @@
       <c r="D9" t="s">
         <v>21</v>
       </c>
-      <c r="E9" s="2"/>
+      <c r="E9" s="2">
+        <v>1</v>
+      </c>
       <c r="F9" t="s">
-        <v>2</v>
-      </c>
-      <c r="G9" s="1"/>
+        <v>32</v>
+      </c>
+      <c r="G9" s="1">
+        <v>46055</v>
+      </c>
       <c r="H9" t="s">
         <v>2</v>
       </c>
-      <c r="I9" s="2"/>
+      <c r="I9" s="2">
+        <v>1</v>
+      </c>
       <c r="J9" t="s">
-        <v>2</v>
-      </c>
-      <c r="K9" s="2"/>
+        <v>41</v>
+      </c>
+      <c r="K9" s="2">
+        <v>0</v>
+      </c>
       <c r="L9" t="s">
-        <v>2</v>
-      </c>
-      <c r="M9" s="2"/>
+        <v>43</v>
+      </c>
+      <c r="M9" s="2">
+        <v>0</v>
+      </c>
       <c r="N9" t="s">
-        <v>2</v>
-      </c>
-      <c r="O9" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="O9" s="2">
+        <v>0</v>
+      </c>
       <c r="P9" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q9" s="2"/>
+        <v>50</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>0</v>
+      </c>
       <c r="R9" t="s">
-        <v>2</v>
-      </c>
-      <c r="S9" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="S9" s="2">
+        <v>0</v>
+      </c>
       <c r="T9" t="s">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="U9" t="s">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="V9" t="s">
-        <v>2</v>
-      </c>
-      <c r="W9" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="W9" s="2">
+        <v>0</v>
+      </c>
       <c r="X9" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y9" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="Y9" s="2">
+        <v>0</v>
+      </c>
       <c r="Z9" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA9" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="AA9" s="2">
+        <v>1</v>
+      </c>
       <c r="AB9" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC9" s="2"/>
+        <v>69</v>
+      </c>
+      <c r="AC9" s="2">
+        <v>1</v>
+      </c>
       <c r="AD9" t="s">
-        <v>2</v>
-      </c>
-      <c r="AE9" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="AE9" s="2">
+        <v>0</v>
+      </c>
       <c r="AF9" t="s">
         <v>2</v>
       </c>
-      <c r="AG9" s="2"/>
+      <c r="AG9" s="2">
+        <v>0</v>
+      </c>
       <c r="AH9" t="s">
         <v>2</v>
       </c>
@@ -5350,7 +5408,9 @@
       <c r="AQ9" s="2">
         <v>0</v>
       </c>
-      <c r="AR9" s="2"/>
+      <c r="AR9" s="2">
+        <v>1</v>
+      </c>
       <c r="AS9" s="2">
         <v>0</v>
       </c>
@@ -5369,7 +5429,9 @@
       <c r="AX9" s="2">
         <v>0</v>
       </c>
-      <c r="AY9" s="2"/>
+      <c r="AY9" s="2">
+        <v>0</v>
+      </c>
       <c r="AZ9" s="2">
         <v>0</v>
       </c>
@@ -5385,8 +5447,12 @@
       <c r="BD9" s="2">
         <v>0</v>
       </c>
-      <c r="BE9" s="2"/>
-      <c r="BF9" s="2"/>
+      <c r="BE9" s="2">
+        <v>0</v>
+      </c>
+      <c r="BF9" s="2">
+        <v>0</v>
+      </c>
       <c r="BG9" s="2">
         <v>0</v>
       </c>
@@ -5405,7 +5471,9 @@
       <c r="BL9" s="2">
         <v>0</v>
       </c>
-      <c r="BM9" s="2"/>
+      <c r="BM9" s="2">
+        <v>0</v>
+      </c>
       <c r="BN9" s="2">
         <v>1</v>
       </c>
@@ -5419,12 +5487,14 @@
         <v>1</v>
       </c>
       <c r="BR9" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BS9" s="2">
         <v>0</v>
       </c>
-      <c r="BT9" s="2"/>
+      <c r="BT9" s="2">
+        <v>1</v>
+      </c>
       <c r="BU9" s="2">
         <v>1</v>
       </c>
@@ -5446,11 +5516,15 @@
       <c r="CA9" s="2">
         <v>1</v>
       </c>
-      <c r="CB9" s="2"/>
+      <c r="CB9" s="2">
+        <v>0</v>
+      </c>
       <c r="CC9" s="2">
         <v>1</v>
       </c>
-      <c r="CD9" s="2"/>
+      <c r="CD9" s="2">
+        <v>0</v>
+      </c>
       <c r="CE9" s="2">
         <v>1</v>
       </c>
@@ -5460,19 +5534,27 @@
       <c r="CG9" s="2">
         <v>0</v>
       </c>
-      <c r="CH9" s="2"/>
+      <c r="CH9" s="2">
+        <v>0</v>
+      </c>
       <c r="CI9" s="2">
         <v>0</v>
       </c>
-      <c r="CJ9" s="2"/>
+      <c r="CJ9" s="2">
+        <v>0</v>
+      </c>
       <c r="CK9" s="2">
         <v>1</v>
       </c>
-      <c r="CL9" s="2"/>
+      <c r="CL9" s="2">
+        <v>0</v>
+      </c>
       <c r="CM9" s="2">
         <v>0</v>
       </c>
-      <c r="CN9" s="2"/>
+      <c r="CN9" s="2">
+        <v>0</v>
+      </c>
       <c r="CO9" s="2">
         <v>0</v>
       </c>
@@ -5483,7 +5565,9 @@
       <c r="CR9" s="2">
         <v>1</v>
       </c>
-      <c r="CS9" s="2"/>
+      <c r="CS9" s="2">
+        <v>0</v>
+      </c>
       <c r="CT9" s="2">
         <v>0</v>
       </c>
@@ -5499,7 +5583,9 @@
       <c r="CX9" s="2">
         <v>0</v>
       </c>
-      <c r="CY9" s="2"/>
+      <c r="CY9" s="2">
+        <v>0</v>
+      </c>
       <c r="CZ9" s="2">
         <v>0</v>
       </c>
@@ -5515,7 +5601,9 @@
       <c r="DD9" s="2">
         <v>0</v>
       </c>
-      <c r="DE9" s="2"/>
+      <c r="DE9" s="2">
+        <v>0</v>
+      </c>
       <c r="DF9" s="2">
         <v>1</v>
       </c>
@@ -5550,7 +5638,7 @@
         <v>0</v>
       </c>
       <c r="DQ9" s="2">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="DR9" s="2">
         <v>387</v>
@@ -5655,77 +5743,69 @@
         <v>286</v>
       </c>
       <c r="EZ9" t="s">
-        <v>292</v>
+        <v>2</v>
       </c>
       <c r="FA9" t="s">
-        <v>294</v>
+        <v>2</v>
       </c>
       <c r="FB9" t="s">
-        <v>299</v>
+        <v>2</v>
       </c>
       <c r="FC9" t="s">
-        <v>308</v>
-      </c>
-      <c r="FD9" s="2">
-        <v>387</v>
-      </c>
-      <c r="FE9" s="2">
-        <v>725</v>
-      </c>
-      <c r="FF9" s="2">
-        <v>2024</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="FD9" s="2"/>
+      <c r="FE9" s="2"/>
+      <c r="FF9" s="2"/>
       <c r="FG9" t="s">
-        <v>317</v>
+        <v>2</v>
       </c>
       <c r="FH9" t="s">
-        <v>268</v>
+        <v>2</v>
       </c>
       <c r="FI9" t="s">
         <v>2</v>
       </c>
       <c r="FJ9" t="s">
-        <v>322</v>
+        <v>2</v>
       </c>
       <c r="FK9" t="s">
         <v>2</v>
       </c>
       <c r="FL9" t="s">
-        <v>327</v>
-      </c>
-      <c r="FM9" s="1">
-        <v>45840</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="FM9" s="1"/>
       <c r="FN9" t="s">
-        <v>335</v>
+        <v>2</v>
       </c>
       <c r="FO9" t="s">
-        <v>342</v>
+        <v>2</v>
       </c>
       <c r="FP9" t="s">
-        <v>351</v>
+        <v>2</v>
       </c>
       <c r="FQ9" t="s">
-        <v>207</v>
+        <v>2</v>
       </c>
       <c r="FR9" t="s">
-        <v>186</v>
+        <v>2</v>
       </c>
       <c r="FS9" t="s">
-        <v>360</v>
+        <v>2</v>
       </c>
       <c r="FT9" t="s">
-        <v>198</v>
+        <v>2</v>
       </c>
       <c r="FU9" t="s">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="FV9" s="2"/>
       <c r="FW9" t="s">
-        <v>244</v>
+        <v>2</v>
       </c>
       <c r="FX9" t="s">
-        <v>366</v>
+        <v>2</v>
       </c>
       <c r="FY9" s="2">
         <v>1</v>
@@ -6576,87 +6656,107 @@
       <c r="DQ11" s="2">
         <v>2025</v>
       </c>
-      <c r="DR11" s="2"/>
-      <c r="DS11" s="2"/>
-      <c r="DT11" s="2"/>
-      <c r="DU11" s="2"/>
-      <c r="DV11" s="2"/>
-      <c r="DW11" s="2"/>
-      <c r="DX11" s="2"/>
+      <c r="DR11" s="2">
+        <v>375</v>
+      </c>
+      <c r="DS11" s="2">
+        <v>348</v>
+      </c>
+      <c r="DT11" s="2">
+        <v>28335</v>
+      </c>
+      <c r="DU11" s="2">
+        <v>29.764091491699219</v>
+      </c>
+      <c r="DV11" s="2">
+        <v>1250</v>
+      </c>
+      <c r="DW11" s="2">
+        <v>0.12238007038831711</v>
+      </c>
+      <c r="DX11" s="2">
+        <v>78</v>
+      </c>
       <c r="DY11" t="s">
-        <v>2</v>
+        <v>178</v>
       </c>
       <c r="DZ11" t="s">
-        <v>2</v>
+        <v>187</v>
       </c>
       <c r="EA11" t="s">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="EB11" t="s">
-        <v>2</v>
+        <v>193</v>
       </c>
       <c r="EC11" t="s">
-        <v>2</v>
+        <v>195</v>
       </c>
       <c r="ED11" t="s">
-        <v>2</v>
+        <v>201</v>
       </c>
       <c r="EE11" t="s">
-        <v>2</v>
+        <v>208</v>
       </c>
       <c r="EF11" t="s">
-        <v>2</v>
+        <v>215</v>
       </c>
       <c r="EG11" t="s">
-        <v>2</v>
+        <v>224</v>
       </c>
       <c r="EH11" t="s">
-        <v>2</v>
+        <v>233</v>
       </c>
       <c r="EI11" t="s">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="EJ11" t="s">
-        <v>2</v>
+        <v>239</v>
       </c>
       <c r="EK11" t="s">
-        <v>2</v>
+        <v>245</v>
       </c>
       <c r="EL11" t="s">
-        <v>2</v>
+        <v>250</v>
       </c>
       <c r="EM11" t="s">
-        <v>2</v>
+        <v>252</v>
       </c>
       <c r="EN11" t="s">
-        <v>2</v>
+        <v>254</v>
       </c>
       <c r="EO11" t="s">
-        <v>2</v>
-      </c>
-      <c r="EP11" s="2"/>
-      <c r="EQ11" s="2"/>
+        <v>260</v>
+      </c>
+      <c r="EP11" s="2">
+        <v>52</v>
+      </c>
+      <c r="EQ11" s="2">
+        <v>117</v>
+      </c>
       <c r="ER11" t="s">
-        <v>2</v>
+        <v>269</v>
       </c>
       <c r="ES11" t="s">
-        <v>2</v>
+        <v>274</v>
       </c>
       <c r="ET11" t="s">
-        <v>2</v>
+        <v>276</v>
       </c>
       <c r="EU11" t="s">
-        <v>2</v>
+        <v>239</v>
       </c>
       <c r="EV11" t="s">
-        <v>2</v>
+        <v>239</v>
       </c>
       <c r="EW11" t="s">
-        <v>2</v>
-      </c>
-      <c r="EX11" s="2"/>
+        <v>280</v>
+      </c>
+      <c r="EX11" s="2">
+        <v>66</v>
+      </c>
       <c r="EY11" t="s">
-        <v>2</v>
+        <v>287</v>
       </c>
       <c r="EZ11" t="s">
         <v>2</v>
@@ -6728,105 +6828,77 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1">
-        <v>45693</v>
-      </c>
+      <c r="A12" s="1"/>
       <c r="B12" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C12" t="s">
         <v>13</v>
       </c>
       <c r="D12" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" s="2">
-        <v>1</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="E12" s="2"/>
       <c r="F12" t="s">
-        <v>29</v>
-      </c>
-      <c r="G12" s="1">
-        <v>46057</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="G12" s="1"/>
       <c r="H12" t="s">
         <v>2</v>
       </c>
-      <c r="I12" s="2">
-        <v>0</v>
-      </c>
+      <c r="I12" s="2"/>
       <c r="J12" t="s">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="K12" s="2"/>
       <c r="L12" t="s">
-        <v>44</v>
-      </c>
-      <c r="M12" s="2">
-        <v>0</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M12" s="2"/>
       <c r="N12" t="s">
-        <v>39</v>
-      </c>
-      <c r="O12" s="2">
-        <v>0</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="O12" s="2"/>
       <c r="P12" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q12" s="2">
-        <v>0</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="Q12" s="2"/>
       <c r="R12" t="s">
-        <v>39</v>
-      </c>
-      <c r="S12" s="2">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="S12" s="2"/>
       <c r="T12" t="s">
-        <v>55</v>
+        <v>2</v>
       </c>
       <c r="U12" t="s">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="V12" t="s">
         <v>2</v>
       </c>
-      <c r="W12" s="2">
-        <v>4</v>
-      </c>
+      <c r="W12" s="2"/>
       <c r="X12" t="s">
-        <v>63</v>
-      </c>
-      <c r="Y12" s="2">
-        <v>0</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="Y12" s="2"/>
       <c r="Z12" t="s">
         <v>2</v>
       </c>
-      <c r="AA12" s="2">
-        <v>0</v>
-      </c>
+      <c r="AA12" s="2"/>
       <c r="AB12" t="s">
         <v>2</v>
       </c>
-      <c r="AC12" s="2">
-        <v>0</v>
-      </c>
+      <c r="AC12" s="2"/>
       <c r="AD12" t="s">
-        <v>39</v>
-      </c>
-      <c r="AE12" s="2">
-        <v>0</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AE12" s="2"/>
       <c r="AF12" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG12" s="2">
-        <v>0</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AG12" s="2"/>
       <c r="AH12" t="s">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="AI12" s="2">
         <v>1</v>
@@ -6855,9 +6927,7 @@
       <c r="AQ12" s="2">
         <v>0</v>
       </c>
-      <c r="AR12" s="2">
-        <v>1</v>
-      </c>
+      <c r="AR12" s="2"/>
       <c r="AS12" s="2">
         <v>0</v>
       </c>
@@ -6876,9 +6946,7 @@
       <c r="AX12" s="2">
         <v>0</v>
       </c>
-      <c r="AY12" s="2">
-        <v>0</v>
-      </c>
+      <c r="AY12" s="2"/>
       <c r="AZ12" s="2">
         <v>0</v>
       </c>
@@ -6894,12 +6962,8 @@
       <c r="BD12" s="2">
         <v>0</v>
       </c>
-      <c r="BE12" s="2">
-        <v>0</v>
-      </c>
-      <c r="BF12" s="2">
-        <v>0</v>
-      </c>
+      <c r="BE12" s="2"/>
+      <c r="BF12" s="2"/>
       <c r="BG12" s="2">
         <v>0</v>
       </c>
@@ -6918,9 +6982,7 @@
       <c r="BL12" s="2">
         <v>0</v>
       </c>
-      <c r="BM12" s="2">
-        <v>0</v>
-      </c>
+      <c r="BM12" s="2"/>
       <c r="BN12" s="2">
         <v>0</v>
       </c>
@@ -6939,9 +7001,7 @@
       <c r="BS12" s="2">
         <v>0</v>
       </c>
-      <c r="BT12" s="2">
-        <v>0</v>
-      </c>
+      <c r="BT12" s="2"/>
       <c r="BU12" s="2">
         <v>1</v>
       </c>
@@ -6963,15 +7023,11 @@
       <c r="CA12" s="2">
         <v>1</v>
       </c>
-      <c r="CB12" s="2">
-        <v>0</v>
-      </c>
+      <c r="CB12" s="2"/>
       <c r="CC12" s="2">
         <v>1</v>
       </c>
-      <c r="CD12" s="2">
-        <v>0</v>
-      </c>
+      <c r="CD12" s="2"/>
       <c r="CE12" s="2">
         <v>1</v>
       </c>
@@ -6981,42 +7037,30 @@
       <c r="CG12" s="2">
         <v>0</v>
       </c>
-      <c r="CH12" s="2">
-        <v>0</v>
-      </c>
+      <c r="CH12" s="2"/>
       <c r="CI12" s="2">
         <v>0</v>
       </c>
-      <c r="CJ12" s="2">
-        <v>0</v>
-      </c>
+      <c r="CJ12" s="2"/>
       <c r="CK12" s="2">
         <v>1</v>
       </c>
-      <c r="CL12" s="2">
-        <v>0</v>
-      </c>
+      <c r="CL12" s="2"/>
       <c r="CM12" s="2">
         <v>0</v>
       </c>
-      <c r="CN12" s="2">
-        <v>0</v>
-      </c>
+      <c r="CN12" s="2"/>
       <c r="CO12" s="2">
         <v>0</v>
       </c>
-      <c r="CP12" s="2">
-        <v>0</v>
-      </c>
+      <c r="CP12" s="2"/>
       <c r="CQ12" s="2">
         <v>1</v>
       </c>
       <c r="CR12" s="2">
         <v>1</v>
       </c>
-      <c r="CS12" s="2">
-        <v>0</v>
-      </c>
+      <c r="CS12" s="2"/>
       <c r="CT12" s="2">
         <v>0</v>
       </c>
@@ -7032,9 +7076,7 @@
       <c r="CX12" s="2">
         <v>0</v>
       </c>
-      <c r="CY12" s="2">
-        <v>0</v>
-      </c>
+      <c r="CY12" s="2"/>
       <c r="CZ12" s="2">
         <v>0</v>
       </c>
@@ -7050,9 +7092,7 @@
       <c r="DD12" s="2">
         <v>0</v>
       </c>
-      <c r="DE12" s="2">
-        <v>1</v>
-      </c>
+      <c r="DE12" s="2"/>
       <c r="DF12" s="2">
         <v>0</v>
       </c>
@@ -7087,231 +7127,287 @@
         <v>0</v>
       </c>
       <c r="DQ12" s="2">
-        <v>2025</v>
-      </c>
-      <c r="DR12" s="2"/>
-      <c r="DS12" s="2"/>
-      <c r="DT12" s="2"/>
-      <c r="DU12" s="2"/>
-      <c r="DV12" s="2"/>
-      <c r="DW12" s="2"/>
-      <c r="DX12" s="2"/>
+        <v>2024</v>
+      </c>
+      <c r="DR12" s="2">
+        <v>462</v>
+      </c>
+      <c r="DS12" s="2">
+        <v>417</v>
+      </c>
+      <c r="DT12" s="2">
+        <v>55359</v>
+      </c>
+      <c r="DU12" s="2">
+        <v>24.911413192749024</v>
+      </c>
+      <c r="DV12" s="2">
+        <v>10925</v>
+      </c>
+      <c r="DW12" s="2">
+        <v>0.009950634092092514</v>
+      </c>
+      <c r="DX12" s="2">
+        <v>140</v>
+      </c>
       <c r="DY12" t="s">
-        <v>2</v>
+        <v>179</v>
       </c>
       <c r="DZ12" t="s">
-        <v>2</v>
+        <v>188</v>
       </c>
       <c r="EA12" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="EB12" t="s">
-        <v>2</v>
+        <v>193</v>
       </c>
       <c r="EC12" t="s">
-        <v>2</v>
+        <v>195</v>
       </c>
       <c r="ED12" t="s">
-        <v>2</v>
+        <v>198</v>
       </c>
       <c r="EE12" t="s">
-        <v>2</v>
+        <v>204</v>
       </c>
       <c r="EF12" t="s">
-        <v>2</v>
+        <v>216</v>
       </c>
       <c r="EG12" t="s">
-        <v>2</v>
+        <v>225</v>
       </c>
       <c r="EH12" t="s">
-        <v>2</v>
+        <v>234</v>
       </c>
       <c r="EI12" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="EJ12" t="s">
-        <v>2</v>
+        <v>239</v>
       </c>
       <c r="EK12" t="s">
-        <v>2</v>
+        <v>246</v>
       </c>
       <c r="EL12" t="s">
-        <v>2</v>
+        <v>250</v>
       </c>
       <c r="EM12" t="s">
-        <v>2</v>
+        <v>252</v>
       </c>
       <c r="EN12" t="s">
-        <v>2</v>
+        <v>254</v>
       </c>
       <c r="EO12" t="s">
-        <v>2</v>
-      </c>
-      <c r="EP12" s="2"/>
-      <c r="EQ12" s="2"/>
+        <v>260</v>
+      </c>
+      <c r="EP12" s="2">
+        <v>53</v>
+      </c>
+      <c r="EQ12" s="2">
+        <v>151</v>
+      </c>
       <c r="ER12" t="s">
-        <v>2</v>
+        <v>270</v>
       </c>
       <c r="ES12" t="s">
-        <v>2</v>
+        <v>274</v>
       </c>
       <c r="ET12" t="s">
-        <v>2</v>
+        <v>276</v>
       </c>
       <c r="EU12" t="s">
-        <v>2</v>
+        <v>239</v>
       </c>
       <c r="EV12" t="s">
-        <v>2</v>
+        <v>239</v>
       </c>
       <c r="EW12" t="s">
-        <v>2</v>
-      </c>
-      <c r="EX12" s="2"/>
+        <v>280</v>
+      </c>
+      <c r="EX12" s="2">
+        <v>99</v>
+      </c>
       <c r="EY12" t="s">
-        <v>2</v>
+        <v>288</v>
       </c>
       <c r="EZ12" t="s">
-        <v>2</v>
+        <v>292</v>
       </c>
       <c r="FA12" t="s">
-        <v>2</v>
+        <v>294</v>
       </c>
       <c r="FB12" t="s">
-        <v>2</v>
+        <v>301</v>
       </c>
       <c r="FC12" t="s">
-        <v>2</v>
-      </c>
-      <c r="FD12" s="2"/>
-      <c r="FE12" s="2"/>
-      <c r="FF12" s="2"/>
+        <v>310</v>
+      </c>
+      <c r="FD12" s="2">
+        <v>462</v>
+      </c>
+      <c r="FE12" s="2">
+        <v>417</v>
+      </c>
+      <c r="FF12" s="2">
+        <v>2024</v>
+      </c>
       <c r="FG12" t="s">
-        <v>2</v>
+        <v>317</v>
       </c>
       <c r="FH12" t="s">
-        <v>2</v>
+        <v>270</v>
       </c>
       <c r="FI12" t="s">
         <v>2</v>
       </c>
       <c r="FJ12" t="s">
-        <v>2</v>
+        <v>322</v>
       </c>
       <c r="FK12" t="s">
-        <v>2</v>
+        <v>324</v>
       </c>
       <c r="FL12" t="s">
-        <v>2</v>
-      </c>
-      <c r="FM12" s="1"/>
+        <v>327</v>
+      </c>
+      <c r="FM12" s="1">
+        <v>45840</v>
+      </c>
       <c r="FN12" t="s">
-        <v>2</v>
+        <v>337</v>
       </c>
       <c r="FO12" t="s">
-        <v>2</v>
+        <v>344</v>
       </c>
       <c r="FP12" t="s">
-        <v>2</v>
+        <v>353</v>
       </c>
       <c r="FQ12" t="s">
-        <v>2</v>
+        <v>204</v>
       </c>
       <c r="FR12" t="s">
-        <v>2</v>
+        <v>188</v>
       </c>
       <c r="FS12" t="s">
-        <v>2</v>
+        <v>360</v>
       </c>
       <c r="FT12" t="s">
-        <v>2</v>
+        <v>198</v>
       </c>
       <c r="FU12" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="FV12" s="2"/>
       <c r="FW12" t="s">
-        <v>2</v>
+        <v>246</v>
       </c>
       <c r="FX12" t="s">
-        <v>2</v>
+        <v>366</v>
       </c>
       <c r="FY12" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1"/>
+      <c r="A13" s="1">
+        <v>45693</v>
+      </c>
       <c r="B13" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13" t="s">
         <v>13</v>
       </c>
       <c r="D13" t="s">
-        <v>24</v>
-      </c>
-      <c r="E13" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="E13" s="2">
+        <v>1</v>
+      </c>
       <c r="F13" t="s">
-        <v>2</v>
-      </c>
-      <c r="G13" s="1"/>
+        <v>29</v>
+      </c>
+      <c r="G13" s="1">
+        <v>46057</v>
+      </c>
       <c r="H13" t="s">
         <v>2</v>
       </c>
-      <c r="I13" s="2"/>
+      <c r="I13" s="2">
+        <v>0</v>
+      </c>
       <c r="J13" t="s">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="K13" s="2"/>
       <c r="L13" t="s">
-        <v>2</v>
-      </c>
-      <c r="M13" s="2"/>
+        <v>44</v>
+      </c>
+      <c r="M13" s="2">
+        <v>0</v>
+      </c>
       <c r="N13" t="s">
-        <v>2</v>
-      </c>
-      <c r="O13" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="O13" s="2">
+        <v>0</v>
+      </c>
       <c r="P13" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q13" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="Q13" s="2">
+        <v>0</v>
+      </c>
       <c r="R13" t="s">
-        <v>2</v>
-      </c>
-      <c r="S13" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="S13" s="2">
+        <v>1</v>
+      </c>
       <c r="T13" t="s">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="U13" t="s">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="V13" t="s">
         <v>2</v>
       </c>
-      <c r="W13" s="2"/>
+      <c r="W13" s="2">
+        <v>4</v>
+      </c>
       <c r="X13" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y13" s="2"/>
+        <v>63</v>
+      </c>
+      <c r="Y13" s="2">
+        <v>0</v>
+      </c>
       <c r="Z13" t="s">
         <v>2</v>
       </c>
-      <c r="AA13" s="2"/>
+      <c r="AA13" s="2">
+        <v>0</v>
+      </c>
       <c r="AB13" t="s">
         <v>2</v>
       </c>
-      <c r="AC13" s="2"/>
+      <c r="AC13" s="2">
+        <v>0</v>
+      </c>
       <c r="AD13" t="s">
-        <v>2</v>
-      </c>
-      <c r="AE13" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="AE13" s="2">
+        <v>0</v>
+      </c>
       <c r="AF13" t="s">
-        <v>2</v>
-      </c>
-      <c r="AG13" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="AG13" s="2">
+        <v>0</v>
+      </c>
       <c r="AH13" t="s">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="AI13" s="2">
         <v>1</v>
@@ -7340,7 +7436,9 @@
       <c r="AQ13" s="2">
         <v>0</v>
       </c>
-      <c r="AR13" s="2"/>
+      <c r="AR13" s="2">
+        <v>1</v>
+      </c>
       <c r="AS13" s="2">
         <v>0</v>
       </c>
@@ -7359,7 +7457,9 @@
       <c r="AX13" s="2">
         <v>0</v>
       </c>
-      <c r="AY13" s="2"/>
+      <c r="AY13" s="2">
+        <v>0</v>
+      </c>
       <c r="AZ13" s="2">
         <v>0</v>
       </c>
@@ -7375,8 +7475,12 @@
       <c r="BD13" s="2">
         <v>0</v>
       </c>
-      <c r="BE13" s="2"/>
-      <c r="BF13" s="2"/>
+      <c r="BE13" s="2">
+        <v>0</v>
+      </c>
+      <c r="BF13" s="2">
+        <v>0</v>
+      </c>
       <c r="BG13" s="2">
         <v>0</v>
       </c>
@@ -7395,7 +7499,9 @@
       <c r="BL13" s="2">
         <v>0</v>
       </c>
-      <c r="BM13" s="2"/>
+      <c r="BM13" s="2">
+        <v>0</v>
+      </c>
       <c r="BN13" s="2">
         <v>0</v>
       </c>
@@ -7414,7 +7520,9 @@
       <c r="BS13" s="2">
         <v>0</v>
       </c>
-      <c r="BT13" s="2"/>
+      <c r="BT13" s="2">
+        <v>0</v>
+      </c>
       <c r="BU13" s="2">
         <v>1</v>
       </c>
@@ -7436,11 +7544,15 @@
       <c r="CA13" s="2">
         <v>1</v>
       </c>
-      <c r="CB13" s="2"/>
+      <c r="CB13" s="2">
+        <v>0</v>
+      </c>
       <c r="CC13" s="2">
         <v>1</v>
       </c>
-      <c r="CD13" s="2"/>
+      <c r="CD13" s="2">
+        <v>0</v>
+      </c>
       <c r="CE13" s="2">
         <v>1</v>
       </c>
@@ -7450,30 +7562,42 @@
       <c r="CG13" s="2">
         <v>0</v>
       </c>
-      <c r="CH13" s="2"/>
+      <c r="CH13" s="2">
+        <v>0</v>
+      </c>
       <c r="CI13" s="2">
         <v>0</v>
       </c>
-      <c r="CJ13" s="2"/>
+      <c r="CJ13" s="2">
+        <v>0</v>
+      </c>
       <c r="CK13" s="2">
         <v>1</v>
       </c>
-      <c r="CL13" s="2"/>
+      <c r="CL13" s="2">
+        <v>0</v>
+      </c>
       <c r="CM13" s="2">
         <v>0</v>
       </c>
-      <c r="CN13" s="2"/>
+      <c r="CN13" s="2">
+        <v>0</v>
+      </c>
       <c r="CO13" s="2">
         <v>0</v>
       </c>
-      <c r="CP13" s="2"/>
+      <c r="CP13" s="2">
+        <v>0</v>
+      </c>
       <c r="CQ13" s="2">
         <v>1</v>
       </c>
       <c r="CR13" s="2">
         <v>1</v>
       </c>
-      <c r="CS13" s="2"/>
+      <c r="CS13" s="2">
+        <v>0</v>
+      </c>
       <c r="CT13" s="2">
         <v>0</v>
       </c>
@@ -7489,7 +7613,9 @@
       <c r="CX13" s="2">
         <v>0</v>
       </c>
-      <c r="CY13" s="2"/>
+      <c r="CY13" s="2">
+        <v>0</v>
+      </c>
       <c r="CZ13" s="2">
         <v>0</v>
       </c>
@@ -7505,7 +7631,9 @@
       <c r="DD13" s="2">
         <v>0</v>
       </c>
-      <c r="DE13" s="2"/>
+      <c r="DE13" s="2">
+        <v>1</v>
+      </c>
       <c r="DF13" s="2">
         <v>0</v>
       </c>
@@ -7540,7 +7668,7 @@
         <v>0</v>
       </c>
       <c r="DQ13" s="2">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="DR13" s="2">
         <v>462</v>
@@ -7645,88 +7773,78 @@
         <v>288</v>
       </c>
       <c r="EZ13" t="s">
-        <v>292</v>
+        <v>2</v>
       </c>
       <c r="FA13" t="s">
-        <v>294</v>
+        <v>2</v>
       </c>
       <c r="FB13" t="s">
-        <v>301</v>
+        <v>2</v>
       </c>
       <c r="FC13" t="s">
-        <v>310</v>
-      </c>
-      <c r="FD13" s="2">
-        <v>462</v>
-      </c>
-      <c r="FE13" s="2">
-        <v>417</v>
-      </c>
-      <c r="FF13" s="2">
-        <v>2024</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="FD13" s="2"/>
+      <c r="FE13" s="2"/>
+      <c r="FF13" s="2"/>
       <c r="FG13" t="s">
-        <v>317</v>
+        <v>2</v>
       </c>
       <c r="FH13" t="s">
-        <v>270</v>
+        <v>2</v>
       </c>
       <c r="FI13" t="s">
         <v>2</v>
       </c>
       <c r="FJ13" t="s">
-        <v>322</v>
+        <v>2</v>
       </c>
       <c r="FK13" t="s">
-        <v>324</v>
+        <v>2</v>
       </c>
       <c r="FL13" t="s">
-        <v>327</v>
-      </c>
-      <c r="FM13" s="1">
-        <v>45840</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="FM13" s="1"/>
       <c r="FN13" t="s">
-        <v>337</v>
+        <v>2</v>
       </c>
       <c r="FO13" t="s">
-        <v>344</v>
+        <v>2</v>
       </c>
       <c r="FP13" t="s">
-        <v>353</v>
+        <v>2</v>
       </c>
       <c r="FQ13" t="s">
-        <v>204</v>
+        <v>2</v>
       </c>
       <c r="FR13" t="s">
-        <v>188</v>
+        <v>2</v>
       </c>
       <c r="FS13" t="s">
-        <v>360</v>
+        <v>2</v>
       </c>
       <c r="FT13" t="s">
-        <v>198</v>
+        <v>2</v>
       </c>
       <c r="FU13" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="FV13" s="2"/>
       <c r="FW13" t="s">
-        <v>246</v>
+        <v>2</v>
       </c>
       <c r="FX13" t="s">
-        <v>366</v>
+        <v>2</v>
       </c>
       <c r="FY13" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1">
-        <v>45686</v>
-      </c>
+      <c r="A14" s="1"/>
       <c r="B14" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C14" t="s">
         <v>14</v>
@@ -7734,93 +7852,65 @@
       <c r="D14" t="s">
         <v>25</v>
       </c>
-      <c r="E14" s="2">
-        <v>1</v>
-      </c>
+      <c r="E14" s="2"/>
       <c r="F14" t="s">
-        <v>32</v>
-      </c>
-      <c r="G14" s="1">
-        <v>46056</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="G14" s="1"/>
       <c r="H14" t="s">
         <v>2</v>
       </c>
-      <c r="I14" s="2">
-        <v>0</v>
-      </c>
+      <c r="I14" s="2"/>
       <c r="J14" t="s">
-        <v>39</v>
-      </c>
-      <c r="K14" s="2">
-        <v>0</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="K14" s="2"/>
       <c r="L14" t="s">
-        <v>39</v>
-      </c>
-      <c r="M14" s="2">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M14" s="2"/>
       <c r="N14" t="s">
-        <v>47</v>
-      </c>
-      <c r="O14" s="2">
-        <v>0</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="O14" s="2"/>
       <c r="P14" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q14" s="2">
-        <v>0</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="Q14" s="2"/>
       <c r="R14" t="s">
-        <v>39</v>
-      </c>
-      <c r="S14" s="2">
-        <v>0</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="S14" s="2"/>
       <c r="T14" t="s">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="U14" t="s">
-        <v>58</v>
+        <v>2</v>
       </c>
       <c r="V14" t="s">
-        <v>60</v>
-      </c>
-      <c r="W14" s="2">
-        <v>0</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="W14" s="2"/>
       <c r="X14" t="s">
-        <v>39</v>
-      </c>
-      <c r="Y14" s="2">
-        <v>0</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="Y14" s="2"/>
       <c r="Z14" t="s">
-        <v>39</v>
-      </c>
-      <c r="AA14" s="2">
-        <v>0</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AA14" s="2"/>
       <c r="AB14" t="s">
-        <v>39</v>
-      </c>
-      <c r="AC14" s="2">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AC14" s="2"/>
       <c r="AD14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AE14" s="2">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AE14" s="2"/>
       <c r="AF14" t="s">
-        <v>77</v>
-      </c>
-      <c r="AG14" s="2">
-        <v>0</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AG14" s="2"/>
       <c r="AH14" t="s">
         <v>2</v>
       </c>
@@ -7851,9 +7941,7 @@
       <c r="AQ14" s="2">
         <v>0</v>
       </c>
-      <c r="AR14" s="2">
-        <v>1</v>
-      </c>
+      <c r="AR14" s="2"/>
       <c r="AS14" s="2">
         <v>0</v>
       </c>
@@ -7872,9 +7960,7 @@
       <c r="AX14" s="2">
         <v>0</v>
       </c>
-      <c r="AY14" s="2">
-        <v>0</v>
-      </c>
+      <c r="AY14" s="2"/>
       <c r="AZ14" s="2">
         <v>1</v>
       </c>
@@ -7890,12 +7976,8 @@
       <c r="BD14" s="2">
         <v>0</v>
       </c>
-      <c r="BE14" s="2">
-        <v>1</v>
-      </c>
-      <c r="BF14" s="2">
-        <v>0</v>
-      </c>
+      <c r="BE14" s="2"/>
+      <c r="BF14" s="2"/>
       <c r="BG14" s="2">
         <v>0</v>
       </c>
@@ -7914,9 +7996,7 @@
       <c r="BL14" s="2">
         <v>0</v>
       </c>
-      <c r="BM14" s="2">
-        <v>0</v>
-      </c>
+      <c r="BM14" s="2"/>
       <c r="BN14" s="2">
         <v>1</v>
       </c>
@@ -7935,9 +8015,7 @@
       <c r="BS14" s="2">
         <v>0</v>
       </c>
-      <c r="BT14" s="2">
-        <v>1</v>
-      </c>
+      <c r="BT14" s="2"/>
       <c r="BU14" s="2">
         <v>1</v>
       </c>
@@ -7959,15 +8037,11 @@
       <c r="CA14" s="2">
         <v>1</v>
       </c>
-      <c r="CB14" s="2">
-        <v>0</v>
-      </c>
+      <c r="CB14" s="2"/>
       <c r="CC14" s="2">
         <v>1</v>
       </c>
-      <c r="CD14" s="2">
-        <v>0</v>
-      </c>
+      <c r="CD14" s="2"/>
       <c r="CE14" s="2">
         <v>1</v>
       </c>
@@ -7977,42 +8051,30 @@
       <c r="CG14" s="2">
         <v>1</v>
       </c>
-      <c r="CH14" s="2">
-        <v>0</v>
-      </c>
+      <c r="CH14" s="2"/>
       <c r="CI14" s="2">
-        <v>0</v>
-      </c>
-      <c r="CJ14" s="2">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="CJ14" s="2"/>
       <c r="CK14" s="2">
-        <v>0</v>
-      </c>
-      <c r="CL14" s="2">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="CL14" s="2"/>
       <c r="CM14" s="2">
         <v>1</v>
       </c>
-      <c r="CN14" s="2">
-        <v>0</v>
-      </c>
+      <c r="CN14" s="2"/>
       <c r="CO14" s="2">
         <v>1</v>
       </c>
-      <c r="CP14" s="2">
-        <v>0</v>
-      </c>
+      <c r="CP14" s="2"/>
       <c r="CQ14" s="2">
         <v>1</v>
       </c>
       <c r="CR14" s="2">
         <v>1</v>
       </c>
-      <c r="CS14" s="2">
-        <v>1</v>
-      </c>
+      <c r="CS14" s="2"/>
       <c r="CT14" s="2">
         <v>0</v>
       </c>
@@ -8028,9 +8090,7 @@
       <c r="CX14" s="2">
         <v>0</v>
       </c>
-      <c r="CY14" s="2">
-        <v>0</v>
-      </c>
+      <c r="CY14" s="2"/>
       <c r="CZ14" s="2">
         <v>0</v>
       </c>
@@ -8046,9 +8106,7 @@
       <c r="DD14" s="2">
         <v>0</v>
       </c>
-      <c r="DE14" s="2">
-        <v>0</v>
-      </c>
+      <c r="DE14" s="2"/>
       <c r="DF14" s="2">
         <v>1</v>
       </c>
@@ -8077,169 +8135,199 @@
         <v>1</v>
       </c>
       <c r="DO14" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DP14" s="2">
         <v>1</v>
       </c>
       <c r="DQ14" s="2">
-        <v>2025</v>
-      </c>
-      <c r="DR14" s="2"/>
-      <c r="DS14" s="2"/>
-      <c r="DT14" s="2"/>
-      <c r="DU14" s="2"/>
-      <c r="DV14" s="2"/>
-      <c r="DW14" s="2"/>
-      <c r="DX14" s="2"/>
+        <v>2024</v>
+      </c>
+      <c r="DR14" s="2">
+        <v>273</v>
+      </c>
+      <c r="DS14" s="2">
+        <v>594</v>
+      </c>
+      <c r="DT14" s="2">
+        <v>35853</v>
+      </c>
+      <c r="DU14" s="2">
+        <v>29.621505737304688</v>
+      </c>
+      <c r="DV14" s="2">
+        <v>1173</v>
+      </c>
+      <c r="DW14" s="2">
+        <v>0.1259913295507431</v>
+      </c>
+      <c r="DX14" s="2">
+        <v>98</v>
+      </c>
       <c r="DY14" t="s">
-        <v>2</v>
+        <v>180</v>
       </c>
       <c r="DZ14" t="s">
-        <v>2</v>
+        <v>189</v>
       </c>
       <c r="EA14" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="EB14" t="s">
-        <v>2</v>
+        <v>193</v>
       </c>
       <c r="EC14" t="s">
-        <v>2</v>
+        <v>195</v>
       </c>
       <c r="ED14" t="s">
-        <v>2</v>
+        <v>202</v>
       </c>
       <c r="EE14" t="s">
-        <v>2</v>
+        <v>209</v>
       </c>
       <c r="EF14" t="s">
-        <v>2</v>
+        <v>217</v>
       </c>
       <c r="EG14" t="s">
-        <v>2</v>
+        <v>226</v>
       </c>
       <c r="EH14" t="s">
-        <v>2</v>
+        <v>235</v>
       </c>
       <c r="EI14" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="EJ14" t="s">
-        <v>2</v>
+        <v>239</v>
       </c>
       <c r="EK14" t="s">
-        <v>2</v>
+        <v>247</v>
       </c>
       <c r="EL14" t="s">
-        <v>2</v>
+        <v>250</v>
       </c>
       <c r="EM14" t="s">
-        <v>2</v>
+        <v>252</v>
       </c>
       <c r="EN14" t="s">
-        <v>2</v>
+        <v>257</v>
       </c>
       <c r="EO14" t="s">
-        <v>2</v>
-      </c>
-      <c r="EP14" s="2"/>
-      <c r="EQ14" s="2"/>
+        <v>261</v>
+      </c>
+      <c r="EP14" s="2">
+        <v>62</v>
+      </c>
+      <c r="EQ14" s="2">
+        <v>154</v>
+      </c>
       <c r="ER14" t="s">
-        <v>2</v>
+        <v>271</v>
       </c>
       <c r="ES14" t="s">
-        <v>2</v>
+        <v>274</v>
       </c>
       <c r="ET14" t="s">
-        <v>2</v>
+        <v>276</v>
       </c>
       <c r="EU14" t="s">
-        <v>2</v>
+        <v>239</v>
       </c>
       <c r="EV14" t="s">
-        <v>2</v>
+        <v>239</v>
       </c>
       <c r="EW14" t="s">
-        <v>2</v>
-      </c>
-      <c r="EX14" s="2"/>
+        <v>280</v>
+      </c>
+      <c r="EX14" s="2">
+        <v>93</v>
+      </c>
       <c r="EY14" t="s">
-        <v>2</v>
+        <v>289</v>
       </c>
       <c r="EZ14" t="s">
-        <v>2</v>
+        <v>292</v>
       </c>
       <c r="FA14" t="s">
-        <v>2</v>
+        <v>294</v>
       </c>
       <c r="FB14" t="s">
-        <v>2</v>
+        <v>302</v>
       </c>
       <c r="FC14" t="s">
-        <v>2</v>
-      </c>
-      <c r="FD14" s="2"/>
-      <c r="FE14" s="2"/>
-      <c r="FF14" s="2"/>
+        <v>311</v>
+      </c>
+      <c r="FD14" s="2">
+        <v>273</v>
+      </c>
+      <c r="FE14" s="2">
+        <v>594</v>
+      </c>
+      <c r="FF14" s="2">
+        <v>2024</v>
+      </c>
       <c r="FG14" t="s">
-        <v>2</v>
+        <v>317</v>
       </c>
       <c r="FH14" t="s">
-        <v>2</v>
+        <v>271</v>
       </c>
       <c r="FI14" t="s">
         <v>2</v>
       </c>
       <c r="FJ14" t="s">
-        <v>2</v>
+        <v>322</v>
       </c>
       <c r="FK14" t="s">
-        <v>2</v>
+        <v>325</v>
       </c>
       <c r="FL14" t="s">
-        <v>2</v>
-      </c>
-      <c r="FM14" s="1"/>
+        <v>327</v>
+      </c>
+      <c r="FM14" s="1">
+        <v>45840</v>
+      </c>
       <c r="FN14" t="s">
-        <v>2</v>
+        <v>181</v>
       </c>
       <c r="FO14" t="s">
-        <v>2</v>
+        <v>345</v>
       </c>
       <c r="FP14" t="s">
-        <v>2</v>
+        <v>354</v>
       </c>
       <c r="FQ14" t="s">
-        <v>2</v>
+        <v>209</v>
       </c>
       <c r="FR14" t="s">
-        <v>2</v>
+        <v>189</v>
       </c>
       <c r="FS14" t="s">
-        <v>2</v>
+        <v>360</v>
       </c>
       <c r="FT14" t="s">
-        <v>2</v>
+        <v>202</v>
       </c>
       <c r="FU14" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="FV14" s="2"/>
       <c r="FW14" t="s">
-        <v>2</v>
+        <v>247</v>
       </c>
       <c r="FX14" t="s">
-        <v>2</v>
+        <v>366</v>
       </c>
       <c r="FY14" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1"/>
+      <c r="A15" s="1">
+        <v>45686</v>
+      </c>
       <c r="B15" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C15" t="s">
         <v>14</v>
@@ -8247,65 +8335,93 @@
       <c r="D15" t="s">
         <v>25</v>
       </c>
-      <c r="E15" s="2"/>
+      <c r="E15" s="2">
+        <v>1</v>
+      </c>
       <c r="F15" t="s">
-        <v>2</v>
-      </c>
-      <c r="G15" s="1"/>
+        <v>32</v>
+      </c>
+      <c r="G15" s="1">
+        <v>46056</v>
+      </c>
       <c r="H15" t="s">
         <v>2</v>
       </c>
-      <c r="I15" s="2"/>
+      <c r="I15" s="2">
+        <v>0</v>
+      </c>
       <c r="J15" t="s">
-        <v>2</v>
-      </c>
-      <c r="K15" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="K15" s="2">
+        <v>0</v>
+      </c>
       <c r="L15" t="s">
-        <v>2</v>
-      </c>
-      <c r="M15" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="M15" s="2">
+        <v>1</v>
+      </c>
       <c r="N15" t="s">
-        <v>2</v>
-      </c>
-      <c r="O15" s="2"/>
+        <v>47</v>
+      </c>
+      <c r="O15" s="2">
+        <v>0</v>
+      </c>
       <c r="P15" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q15" s="2"/>
+        <v>50</v>
+      </c>
+      <c r="Q15" s="2">
+        <v>0</v>
+      </c>
       <c r="R15" t="s">
-        <v>2</v>
-      </c>
-      <c r="S15" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="S15" s="2">
+        <v>0</v>
+      </c>
       <c r="T15" t="s">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="U15" t="s">
-        <v>2</v>
+        <v>58</v>
       </c>
       <c r="V15" t="s">
-        <v>2</v>
-      </c>
-      <c r="W15" s="2"/>
+        <v>60</v>
+      </c>
+      <c r="W15" s="2">
+        <v>0</v>
+      </c>
       <c r="X15" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y15" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="Y15" s="2">
+        <v>0</v>
+      </c>
       <c r="Z15" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA15" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="AA15" s="2">
+        <v>0</v>
+      </c>
       <c r="AB15" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC15" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="AC15" s="2">
+        <v>1</v>
+      </c>
       <c r="AD15" t="s">
-        <v>2</v>
-      </c>
-      <c r="AE15" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="AE15" s="2">
+        <v>1</v>
+      </c>
       <c r="AF15" t="s">
-        <v>2</v>
-      </c>
-      <c r="AG15" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="AG15" s="2">
+        <v>0</v>
+      </c>
       <c r="AH15" t="s">
         <v>2</v>
       </c>
@@ -8336,7 +8452,9 @@
       <c r="AQ15" s="2">
         <v>0</v>
       </c>
-      <c r="AR15" s="2"/>
+      <c r="AR15" s="2">
+        <v>1</v>
+      </c>
       <c r="AS15" s="2">
         <v>0</v>
       </c>
@@ -8355,7 +8473,9 @@
       <c r="AX15" s="2">
         <v>0</v>
       </c>
-      <c r="AY15" s="2"/>
+      <c r="AY15" s="2">
+        <v>0</v>
+      </c>
       <c r="AZ15" s="2">
         <v>1</v>
       </c>
@@ -8371,8 +8491,12 @@
       <c r="BD15" s="2">
         <v>0</v>
       </c>
-      <c r="BE15" s="2"/>
-      <c r="BF15" s="2"/>
+      <c r="BE15" s="2">
+        <v>1</v>
+      </c>
+      <c r="BF15" s="2">
+        <v>0</v>
+      </c>
       <c r="BG15" s="2">
         <v>0</v>
       </c>
@@ -8391,7 +8515,9 @@
       <c r="BL15" s="2">
         <v>0</v>
       </c>
-      <c r="BM15" s="2"/>
+      <c r="BM15" s="2">
+        <v>0</v>
+      </c>
       <c r="BN15" s="2">
         <v>1</v>
       </c>
@@ -8410,7 +8536,9 @@
       <c r="BS15" s="2">
         <v>0</v>
       </c>
-      <c r="BT15" s="2"/>
+      <c r="BT15" s="2">
+        <v>1</v>
+      </c>
       <c r="BU15" s="2">
         <v>1</v>
       </c>
@@ -8432,11 +8560,15 @@
       <c r="CA15" s="2">
         <v>1</v>
       </c>
-      <c r="CB15" s="2"/>
+      <c r="CB15" s="2">
+        <v>0</v>
+      </c>
       <c r="CC15" s="2">
         <v>1</v>
       </c>
-      <c r="CD15" s="2"/>
+      <c r="CD15" s="2">
+        <v>0</v>
+      </c>
       <c r="CE15" s="2">
         <v>1</v>
       </c>
@@ -8446,30 +8578,42 @@
       <c r="CG15" s="2">
         <v>1</v>
       </c>
-      <c r="CH15" s="2"/>
+      <c r="CH15" s="2">
+        <v>0</v>
+      </c>
       <c r="CI15" s="2">
-        <v>1</v>
-      </c>
-      <c r="CJ15" s="2"/>
+        <v>0</v>
+      </c>
+      <c r="CJ15" s="2">
+        <v>0</v>
+      </c>
       <c r="CK15" s="2">
-        <v>1</v>
-      </c>
-      <c r="CL15" s="2"/>
+        <v>0</v>
+      </c>
+      <c r="CL15" s="2">
+        <v>0</v>
+      </c>
       <c r="CM15" s="2">
         <v>1</v>
       </c>
-      <c r="CN15" s="2"/>
+      <c r="CN15" s="2">
+        <v>0</v>
+      </c>
       <c r="CO15" s="2">
         <v>1</v>
       </c>
-      <c r="CP15" s="2"/>
+      <c r="CP15" s="2">
+        <v>0</v>
+      </c>
       <c r="CQ15" s="2">
         <v>1</v>
       </c>
       <c r="CR15" s="2">
         <v>1</v>
       </c>
-      <c r="CS15" s="2"/>
+      <c r="CS15" s="2">
+        <v>1</v>
+      </c>
       <c r="CT15" s="2">
         <v>0</v>
       </c>
@@ -8485,7 +8629,9 @@
       <c r="CX15" s="2">
         <v>0</v>
       </c>
-      <c r="CY15" s="2"/>
+      <c r="CY15" s="2">
+        <v>0</v>
+      </c>
       <c r="CZ15" s="2">
         <v>0</v>
       </c>
@@ -8501,7 +8647,9 @@
       <c r="DD15" s="2">
         <v>0</v>
       </c>
-      <c r="DE15" s="2"/>
+      <c r="DE15" s="2">
+        <v>0</v>
+      </c>
       <c r="DF15" s="2">
         <v>1</v>
       </c>
@@ -8530,13 +8678,13 @@
         <v>1</v>
       </c>
       <c r="DO15" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DP15" s="2">
         <v>1</v>
       </c>
       <c r="DQ15" s="2">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="DR15" s="2">
         <v>273</v>
@@ -8641,88 +8789,78 @@
         <v>289</v>
       </c>
       <c r="EZ15" t="s">
-        <v>292</v>
+        <v>2</v>
       </c>
       <c r="FA15" t="s">
-        <v>294</v>
+        <v>2</v>
       </c>
       <c r="FB15" t="s">
-        <v>302</v>
+        <v>2</v>
       </c>
       <c r="FC15" t="s">
-        <v>311</v>
-      </c>
-      <c r="FD15" s="2">
-        <v>273</v>
-      </c>
-      <c r="FE15" s="2">
-        <v>594</v>
-      </c>
-      <c r="FF15" s="2">
-        <v>2024</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="FD15" s="2"/>
+      <c r="FE15" s="2"/>
+      <c r="FF15" s="2"/>
       <c r="FG15" t="s">
-        <v>317</v>
+        <v>2</v>
       </c>
       <c r="FH15" t="s">
-        <v>271</v>
+        <v>2</v>
       </c>
       <c r="FI15" t="s">
         <v>2</v>
       </c>
       <c r="FJ15" t="s">
-        <v>322</v>
+        <v>2</v>
       </c>
       <c r="FK15" t="s">
-        <v>325</v>
+        <v>2</v>
       </c>
       <c r="FL15" t="s">
-        <v>327</v>
-      </c>
-      <c r="FM15" s="1">
-        <v>45840</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="FM15" s="1"/>
       <c r="FN15" t="s">
-        <v>181</v>
+        <v>2</v>
       </c>
       <c r="FO15" t="s">
-        <v>345</v>
+        <v>2</v>
       </c>
       <c r="FP15" t="s">
-        <v>354</v>
+        <v>2</v>
       </c>
       <c r="FQ15" t="s">
-        <v>209</v>
+        <v>2</v>
       </c>
       <c r="FR15" t="s">
-        <v>189</v>
+        <v>2</v>
       </c>
       <c r="FS15" t="s">
-        <v>360</v>
+        <v>2</v>
       </c>
       <c r="FT15" t="s">
-        <v>202</v>
+        <v>2</v>
       </c>
       <c r="FU15" t="s">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="FV15" s="2"/>
       <c r="FW15" t="s">
-        <v>247</v>
+        <v>2</v>
       </c>
       <c r="FX15" t="s">
-        <v>366</v>
+        <v>2</v>
       </c>
       <c r="FY15" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1">
-        <v>45693</v>
-      </c>
+      <c r="A16" s="1"/>
       <c r="B16" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="s">
         <v>15</v>
@@ -8730,512 +8868,482 @@
       <c r="D16" t="s">
         <v>26</v>
       </c>
-      <c r="E16" s="2">
-        <v>1</v>
-      </c>
+      <c r="E16" s="2"/>
       <c r="F16" t="s">
-        <v>31</v>
-      </c>
-      <c r="G16" s="1">
-        <v>46057</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="G16" s="1"/>
       <c r="H16" t="s">
         <v>2</v>
       </c>
-      <c r="I16" s="2">
-        <v>0</v>
-      </c>
+      <c r="I16" s="2"/>
       <c r="J16" t="s">
+        <v>2</v>
+      </c>
+      <c r="K16" s="2"/>
+      <c r="L16" t="s">
+        <v>2</v>
+      </c>
+      <c r="M16" s="2"/>
+      <c r="N16" t="s">
+        <v>2</v>
+      </c>
+      <c r="O16" s="2"/>
+      <c r="P16" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q16" s="2"/>
+      <c r="R16" t="s">
+        <v>2</v>
+      </c>
+      <c r="S16" s="2"/>
+      <c r="T16" t="s">
+        <v>2</v>
+      </c>
+      <c r="U16" t="s">
+        <v>2</v>
+      </c>
+      <c r="V16" t="s">
+        <v>2</v>
+      </c>
+      <c r="W16" s="2"/>
+      <c r="X16" t="s">
+        <v>2</v>
+      </c>
+      <c r="Y16" s="2"/>
+      <c r="Z16" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA16" s="2"/>
+      <c r="AB16" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC16" s="2"/>
+      <c r="AD16" t="s">
+        <v>2</v>
+      </c>
+      <c r="AE16" s="2"/>
+      <c r="AF16" t="s">
+        <v>2</v>
+      </c>
+      <c r="AG16" s="2"/>
+      <c r="AH16" t="s">
+        <v>2</v>
+      </c>
+      <c r="AI16" s="2">
+        <v>1</v>
+      </c>
+      <c r="AJ16" s="2">
+        <v>1</v>
+      </c>
+      <c r="AK16" s="2">
+        <v>1</v>
+      </c>
+      <c r="AL16" s="2">
+        <v>1</v>
+      </c>
+      <c r="AM16" s="2">
+        <v>1</v>
+      </c>
+      <c r="AN16" s="2">
+        <v>1</v>
+      </c>
+      <c r="AO16" s="2">
+        <v>0</v>
+      </c>
+      <c r="AP16" s="2">
+        <v>0</v>
+      </c>
+      <c r="AQ16" s="2">
+        <v>0</v>
+      </c>
+      <c r="AR16" s="2"/>
+      <c r="AS16" s="2">
+        <v>0</v>
+      </c>
+      <c r="AT16" s="2">
+        <v>0</v>
+      </c>
+      <c r="AU16" s="2">
+        <v>0</v>
+      </c>
+      <c r="AV16" s="2">
+        <v>0</v>
+      </c>
+      <c r="AW16" s="2">
+        <v>0</v>
+      </c>
+      <c r="AX16" s="2">
+        <v>0</v>
+      </c>
+      <c r="AY16" s="2"/>
+      <c r="AZ16" s="2">
+        <v>0</v>
+      </c>
+      <c r="BA16" s="2">
+        <v>0</v>
+      </c>
+      <c r="BB16" s="2">
+        <v>0</v>
+      </c>
+      <c r="BC16" s="2">
+        <v>0</v>
+      </c>
+      <c r="BD16" s="2">
+        <v>0</v>
+      </c>
+      <c r="BE16" s="2"/>
+      <c r="BF16" s="2"/>
+      <c r="BG16" s="2">
+        <v>0</v>
+      </c>
+      <c r="BH16" s="2">
+        <v>0</v>
+      </c>
+      <c r="BI16" s="2">
+        <v>0</v>
+      </c>
+      <c r="BJ16" s="2">
+        <v>0</v>
+      </c>
+      <c r="BK16" s="2">
+        <v>0</v>
+      </c>
+      <c r="BL16" s="2">
+        <v>0</v>
+      </c>
+      <c r="BM16" s="2"/>
+      <c r="BN16" s="2">
+        <v>0</v>
+      </c>
+      <c r="BO16" s="2">
+        <v>0</v>
+      </c>
+      <c r="BP16" s="2">
+        <v>0</v>
+      </c>
+      <c r="BQ16" s="2">
+        <v>0</v>
+      </c>
+      <c r="BR16" s="2">
+        <v>0</v>
+      </c>
+      <c r="BS16" s="2">
+        <v>0</v>
+      </c>
+      <c r="BT16" s="2"/>
+      <c r="BU16" s="2">
+        <v>1</v>
+      </c>
+      <c r="BV16" s="2">
+        <v>1</v>
+      </c>
+      <c r="BW16" s="2">
+        <v>1</v>
+      </c>
+      <c r="BX16" s="2">
+        <v>1</v>
+      </c>
+      <c r="BY16" s="2">
+        <v>1</v>
+      </c>
+      <c r="BZ16" s="2">
+        <v>1</v>
+      </c>
+      <c r="CA16" s="2">
+        <v>1</v>
+      </c>
+      <c r="CB16" s="2"/>
+      <c r="CC16" s="2">
+        <v>0</v>
+      </c>
+      <c r="CD16" s="2"/>
+      <c r="CE16" s="2">
+        <v>1</v>
+      </c>
+      <c r="CF16" s="2">
+        <v>0</v>
+      </c>
+      <c r="CG16" s="2">
+        <v>0</v>
+      </c>
+      <c r="CH16" s="2"/>
+      <c r="CI16" s="2">
+        <v>0</v>
+      </c>
+      <c r="CJ16" s="2"/>
+      <c r="CK16" s="2">
+        <v>1</v>
+      </c>
+      <c r="CL16" s="2"/>
+      <c r="CM16" s="2">
+        <v>0</v>
+      </c>
+      <c r="CN16" s="2"/>
+      <c r="CO16" s="2">
+        <v>1</v>
+      </c>
+      <c r="CP16" s="2"/>
+      <c r="CQ16" s="2">
+        <v>1</v>
+      </c>
+      <c r="CR16" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS16" s="2"/>
+      <c r="CT16" s="2">
+        <v>0</v>
+      </c>
+      <c r="CU16" s="2">
+        <v>0</v>
+      </c>
+      <c r="CV16" s="2">
+        <v>0</v>
+      </c>
+      <c r="CW16" s="2">
+        <v>0</v>
+      </c>
+      <c r="CX16" s="2">
+        <v>0</v>
+      </c>
+      <c r="CY16" s="2"/>
+      <c r="CZ16" s="2">
+        <v>0</v>
+      </c>
+      <c r="DA16" s="2">
+        <v>0</v>
+      </c>
+      <c r="DB16" s="2">
+        <v>0</v>
+      </c>
+      <c r="DC16" s="2">
+        <v>0</v>
+      </c>
+      <c r="DD16" s="2">
+        <v>0</v>
+      </c>
+      <c r="DE16" s="2"/>
+      <c r="DF16" s="2">
+        <v>0</v>
+      </c>
+      <c r="DG16" s="2">
+        <v>0</v>
+      </c>
+      <c r="DH16" s="2">
+        <v>0</v>
+      </c>
+      <c r="DI16" s="2">
+        <v>0</v>
+      </c>
+      <c r="DJ16" s="2">
+        <v>0</v>
+      </c>
+      <c r="DK16" s="2">
+        <v>1</v>
+      </c>
+      <c r="DL16" s="2">
+        <v>0</v>
+      </c>
+      <c r="DM16" s="2">
+        <v>0</v>
+      </c>
+      <c r="DN16" s="2">
+        <v>0</v>
+      </c>
+      <c r="DO16" s="2">
+        <v>0</v>
+      </c>
+      <c r="DP16" s="2">
+        <v>0</v>
+      </c>
+      <c r="DQ16" s="2">
+        <v>2024</v>
+      </c>
+      <c r="DR16" s="2">
+        <v>301</v>
+      </c>
+      <c r="DS16" s="2">
+        <v>216</v>
+      </c>
+      <c r="DT16" s="2">
+        <v>21648</v>
+      </c>
+      <c r="DU16" s="2">
+        <v>19.887435913085938</v>
+      </c>
+      <c r="DV16" s="2">
+        <v>881</v>
+      </c>
+      <c r="DW16" s="2">
+        <v>0.033100180327892303</v>
+      </c>
+      <c r="DX16" s="2">
+        <v>40</v>
+      </c>
+      <c r="DY16" t="s">
+        <v>181</v>
+      </c>
+      <c r="DZ16" t="s">
+        <v>190</v>
+      </c>
+      <c r="EA16" t="s">
+        <v>26</v>
+      </c>
+      <c r="EB16" t="s">
+        <v>193</v>
+      </c>
+      <c r="EC16" t="s">
+        <v>196</v>
+      </c>
+      <c r="ED16" t="s">
+        <v>202</v>
+      </c>
+      <c r="EE16" t="s">
+        <v>209</v>
+      </c>
+      <c r="EF16" t="s">
+        <v>218</v>
+      </c>
+      <c r="EG16" t="s">
+        <v>227</v>
+      </c>
+      <c r="EH16" t="s">
+        <v>236</v>
+      </c>
+      <c r="EI16" t="s">
+        <v>26</v>
+      </c>
+      <c r="EJ16" t="s">
+        <v>239</v>
+      </c>
+      <c r="EK16" t="s">
+        <v>248</v>
+      </c>
+      <c r="EL16" t="s">
+        <v>250</v>
+      </c>
+      <c r="EM16" t="s">
+        <v>252</v>
+      </c>
+      <c r="EN16" t="s">
+        <v>254</v>
+      </c>
+      <c r="EO16" t="s">
+        <v>260</v>
+      </c>
+      <c r="EP16" s="2">
+        <v>62</v>
+      </c>
+      <c r="EQ16" s="2">
+        <v>100</v>
+      </c>
+      <c r="ER16" t="s">
+        <v>272</v>
+      </c>
+      <c r="ES16" t="s">
+        <v>274</v>
+      </c>
+      <c r="ET16" t="s">
+        <v>276</v>
+      </c>
+      <c r="EU16" t="s">
+        <v>239</v>
+      </c>
+      <c r="EV16" t="s">
+        <v>239</v>
+      </c>
+      <c r="EW16" t="s">
+        <v>280</v>
+      </c>
+      <c r="EX16" s="2">
         <v>39</v>
       </c>
-      <c r="K16" s="2">
-        <v>0</v>
-      </c>
-      <c r="L16" t="s">
-        <v>39</v>
-      </c>
-      <c r="M16" s="2">
-        <v>0</v>
-      </c>
-      <c r="N16" t="s">
-        <v>39</v>
-      </c>
-      <c r="O16" s="2">
-        <v>0</v>
-      </c>
-      <c r="P16" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q16" s="2">
-        <v>0</v>
-      </c>
-      <c r="R16" t="s">
-        <v>39</v>
-      </c>
-      <c r="S16" s="2">
-        <v>0</v>
-      </c>
-      <c r="T16" t="s">
-        <v>39</v>
-      </c>
-      <c r="U16" t="s">
-        <v>57</v>
-      </c>
-      <c r="V16" t="s">
-        <v>61</v>
-      </c>
-      <c r="W16" s="2">
-        <v>0</v>
-      </c>
-      <c r="X16" t="s">
-        <v>61</v>
-      </c>
-      <c r="Y16" s="2">
-        <v>1</v>
-      </c>
-      <c r="Z16" t="s">
-        <v>65</v>
-      </c>
-      <c r="AA16" s="2">
-        <v>1</v>
-      </c>
-      <c r="AB16" t="s">
-        <v>70</v>
-      </c>
-      <c r="AC16" s="2">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="s">
-        <v>39</v>
-      </c>
-      <c r="AE16" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="s">
-        <v>39</v>
-      </c>
-      <c r="AG16" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="s">
-        <v>39</v>
-      </c>
-      <c r="AI16" s="2">
-        <v>1</v>
-      </c>
-      <c r="AJ16" s="2">
-        <v>1</v>
-      </c>
-      <c r="AK16" s="2">
-        <v>1</v>
-      </c>
-      <c r="AL16" s="2">
-        <v>1</v>
-      </c>
-      <c r="AM16" s="2">
-        <v>1</v>
-      </c>
-      <c r="AN16" s="2">
-        <v>1</v>
-      </c>
-      <c r="AO16" s="2">
-        <v>0</v>
-      </c>
-      <c r="AP16" s="2">
-        <v>0</v>
-      </c>
-      <c r="AQ16" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR16" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS16" s="2">
-        <v>0</v>
-      </c>
-      <c r="AT16" s="2">
-        <v>0</v>
-      </c>
-      <c r="AU16" s="2">
-        <v>0</v>
-      </c>
-      <c r="AV16" s="2">
-        <v>0</v>
-      </c>
-      <c r="AW16" s="2">
-        <v>0</v>
-      </c>
-      <c r="AX16" s="2">
-        <v>0</v>
-      </c>
-      <c r="AY16" s="2">
-        <v>0</v>
-      </c>
-      <c r="AZ16" s="2">
-        <v>0</v>
-      </c>
-      <c r="BA16" s="2">
-        <v>0</v>
-      </c>
-      <c r="BB16" s="2">
-        <v>0</v>
-      </c>
-      <c r="BC16" s="2">
-        <v>0</v>
-      </c>
-      <c r="BD16" s="2">
-        <v>0</v>
-      </c>
-      <c r="BE16" s="2">
-        <v>0</v>
-      </c>
-      <c r="BF16" s="2">
-        <v>0</v>
-      </c>
-      <c r="BG16" s="2">
-        <v>0</v>
-      </c>
-      <c r="BH16" s="2">
-        <v>0</v>
-      </c>
-      <c r="BI16" s="2">
-        <v>0</v>
-      </c>
-      <c r="BJ16" s="2">
-        <v>0</v>
-      </c>
-      <c r="BK16" s="2">
-        <v>0</v>
-      </c>
-      <c r="BL16" s="2">
-        <v>0</v>
-      </c>
-      <c r="BM16" s="2">
-        <v>0</v>
-      </c>
-      <c r="BN16" s="2">
-        <v>0</v>
-      </c>
-      <c r="BO16" s="2">
-        <v>0</v>
-      </c>
-      <c r="BP16" s="2">
-        <v>0</v>
-      </c>
-      <c r="BQ16" s="2">
-        <v>0</v>
-      </c>
-      <c r="BR16" s="2">
-        <v>0</v>
-      </c>
-      <c r="BS16" s="2">
-        <v>0</v>
-      </c>
-      <c r="BT16" s="2">
-        <v>0</v>
-      </c>
-      <c r="BU16" s="2">
-        <v>1</v>
-      </c>
-      <c r="BV16" s="2">
-        <v>1</v>
-      </c>
-      <c r="BW16" s="2">
-        <v>1</v>
-      </c>
-      <c r="BX16" s="2">
-        <v>1</v>
-      </c>
-      <c r="BY16" s="2">
-        <v>1</v>
-      </c>
-      <c r="BZ16" s="2">
-        <v>1</v>
-      </c>
-      <c r="CA16" s="2">
-        <v>1</v>
-      </c>
-      <c r="CB16" s="2">
-        <v>0</v>
-      </c>
-      <c r="CC16" s="2">
-        <v>0</v>
-      </c>
-      <c r="CD16" s="2">
-        <v>0</v>
-      </c>
-      <c r="CE16" s="2">
-        <v>1</v>
-      </c>
-      <c r="CF16" s="2">
-        <v>0</v>
-      </c>
-      <c r="CG16" s="2">
-        <v>0</v>
-      </c>
-      <c r="CH16" s="2">
-        <v>0</v>
-      </c>
-      <c r="CI16" s="2">
-        <v>0</v>
-      </c>
-      <c r="CJ16" s="2">
-        <v>0</v>
-      </c>
-      <c r="CK16" s="2">
-        <v>0</v>
-      </c>
-      <c r="CL16" s="2">
-        <v>1</v>
-      </c>
-      <c r="CM16" s="2">
-        <v>0</v>
-      </c>
-      <c r="CN16" s="2">
-        <v>0</v>
-      </c>
-      <c r="CO16" s="2">
-        <v>1</v>
-      </c>
-      <c r="CP16" s="2">
-        <v>0</v>
-      </c>
-      <c r="CQ16" s="2">
-        <v>1</v>
-      </c>
-      <c r="CR16" s="2">
-        <v>0</v>
-      </c>
-      <c r="CS16" s="2">
-        <v>0</v>
-      </c>
-      <c r="CT16" s="2">
-        <v>0</v>
-      </c>
-      <c r="CU16" s="2">
-        <v>0</v>
-      </c>
-      <c r="CV16" s="2">
-        <v>0</v>
-      </c>
-      <c r="CW16" s="2">
-        <v>0</v>
-      </c>
-      <c r="CX16" s="2">
-        <v>0</v>
-      </c>
-      <c r="CY16" s="2">
-        <v>0</v>
-      </c>
-      <c r="CZ16" s="2">
-        <v>0</v>
-      </c>
-      <c r="DA16" s="2">
-        <v>0</v>
-      </c>
-      <c r="DB16" s="2">
-        <v>0</v>
-      </c>
-      <c r="DC16" s="2">
-        <v>0</v>
-      </c>
-      <c r="DD16" s="2">
-        <v>0</v>
-      </c>
-      <c r="DE16" s="2">
-        <v>0</v>
-      </c>
-      <c r="DF16" s="2">
-        <v>0</v>
-      </c>
-      <c r="DG16" s="2">
-        <v>0</v>
-      </c>
-      <c r="DH16" s="2">
-        <v>0</v>
-      </c>
-      <c r="DI16" s="2">
-        <v>0</v>
-      </c>
-      <c r="DJ16" s="2">
-        <v>0</v>
-      </c>
-      <c r="DK16" s="2">
-        <v>1</v>
-      </c>
-      <c r="DL16" s="2">
-        <v>0</v>
-      </c>
-      <c r="DM16" s="2">
-        <v>0</v>
-      </c>
-      <c r="DN16" s="2">
-        <v>0</v>
-      </c>
-      <c r="DO16" s="2">
-        <v>0</v>
-      </c>
-      <c r="DP16" s="2">
-        <v>0</v>
-      </c>
-      <c r="DQ16" s="2">
-        <v>2025</v>
-      </c>
-      <c r="DR16" s="2"/>
-      <c r="DS16" s="2"/>
-      <c r="DT16" s="2"/>
-      <c r="DU16" s="2"/>
-      <c r="DV16" s="2"/>
-      <c r="DW16" s="2"/>
-      <c r="DX16" s="2"/>
-      <c r="DY16" t="s">
-        <v>2</v>
-      </c>
-      <c r="DZ16" t="s">
-        <v>2</v>
-      </c>
-      <c r="EA16" t="s">
-        <v>2</v>
-      </c>
-      <c r="EB16" t="s">
-        <v>2</v>
-      </c>
-      <c r="EC16" t="s">
-        <v>2</v>
-      </c>
-      <c r="ED16" t="s">
-        <v>2</v>
-      </c>
-      <c r="EE16" t="s">
-        <v>2</v>
-      </c>
-      <c r="EF16" t="s">
-        <v>2</v>
-      </c>
-      <c r="EG16" t="s">
-        <v>2</v>
-      </c>
-      <c r="EH16" t="s">
-        <v>2</v>
-      </c>
-      <c r="EI16" t="s">
-        <v>2</v>
-      </c>
-      <c r="EJ16" t="s">
-        <v>2</v>
-      </c>
-      <c r="EK16" t="s">
-        <v>2</v>
-      </c>
-      <c r="EL16" t="s">
-        <v>2</v>
-      </c>
-      <c r="EM16" t="s">
-        <v>2</v>
-      </c>
-      <c r="EN16" t="s">
-        <v>2</v>
-      </c>
-      <c r="EO16" t="s">
-        <v>2</v>
-      </c>
-      <c r="EP16" s="2"/>
-      <c r="EQ16" s="2"/>
-      <c r="ER16" t="s">
-        <v>2</v>
-      </c>
-      <c r="ES16" t="s">
-        <v>2</v>
-      </c>
-      <c r="ET16" t="s">
-        <v>2</v>
-      </c>
-      <c r="EU16" t="s">
-        <v>2</v>
-      </c>
-      <c r="EV16" t="s">
-        <v>2</v>
-      </c>
-      <c r="EW16" t="s">
-        <v>2</v>
-      </c>
-      <c r="EX16" s="2"/>
       <c r="EY16" t="s">
-        <v>2</v>
+        <v>290</v>
       </c>
       <c r="EZ16" t="s">
-        <v>2</v>
+        <v>292</v>
       </c>
       <c r="FA16" t="s">
-        <v>2</v>
+        <v>294</v>
       </c>
       <c r="FB16" t="s">
-        <v>2</v>
+        <v>303</v>
       </c>
       <c r="FC16" t="s">
-        <v>2</v>
-      </c>
-      <c r="FD16" s="2"/>
-      <c r="FE16" s="2"/>
-      <c r="FF16" s="2"/>
+        <v>312</v>
+      </c>
+      <c r="FD16" s="2">
+        <v>301</v>
+      </c>
+      <c r="FE16" s="2">
+        <v>216</v>
+      </c>
+      <c r="FF16" s="2">
+        <v>2024</v>
+      </c>
       <c r="FG16" t="s">
-        <v>2</v>
+        <v>318</v>
       </c>
       <c r="FH16" t="s">
-        <v>2</v>
+        <v>272</v>
       </c>
       <c r="FI16" t="s">
         <v>2</v>
       </c>
       <c r="FJ16" t="s">
-        <v>2</v>
+        <v>322</v>
       </c>
       <c r="FK16" t="s">
         <v>2</v>
       </c>
       <c r="FL16" t="s">
-        <v>2</v>
-      </c>
-      <c r="FM16" s="1"/>
+        <v>329</v>
+      </c>
+      <c r="FM16" s="1">
+        <v>45847</v>
+      </c>
       <c r="FN16" t="s">
-        <v>2</v>
+        <v>338</v>
       </c>
       <c r="FO16" t="s">
-        <v>2</v>
+        <v>346</v>
       </c>
       <c r="FP16" t="s">
-        <v>2</v>
+        <v>355</v>
       </c>
       <c r="FQ16" t="s">
-        <v>2</v>
+        <v>357</v>
       </c>
       <c r="FR16" t="s">
-        <v>2</v>
+        <v>190</v>
       </c>
       <c r="FS16" t="s">
-        <v>2</v>
+        <v>360</v>
       </c>
       <c r="FT16" t="s">
-        <v>2</v>
+        <v>202</v>
       </c>
       <c r="FU16" t="s">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="FV16" s="2"/>
       <c r="FW16" t="s">
-        <v>2</v>
+        <v>248</v>
       </c>
       <c r="FX16" t="s">
-        <v>2</v>
+        <v>366</v>
       </c>
       <c r="FY16" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1"/>
+      <c r="A17" s="1">
+        <v>45693</v>
+      </c>
       <c r="B17" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="s">
         <v>15</v>
@@ -9243,67 +9351,95 @@
       <c r="D17" t="s">
         <v>26</v>
       </c>
-      <c r="E17" s="2"/>
+      <c r="E17" s="2">
+        <v>1</v>
+      </c>
       <c r="F17" t="s">
-        <v>2</v>
-      </c>
-      <c r="G17" s="1"/>
+        <v>31</v>
+      </c>
+      <c r="G17" s="1">
+        <v>46057</v>
+      </c>
       <c r="H17" t="s">
         <v>2</v>
       </c>
-      <c r="I17" s="2"/>
+      <c r="I17" s="2">
+        <v>0</v>
+      </c>
       <c r="J17" t="s">
-        <v>2</v>
-      </c>
-      <c r="K17" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="K17" s="2">
+        <v>0</v>
+      </c>
       <c r="L17" t="s">
-        <v>2</v>
-      </c>
-      <c r="M17" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="M17" s="2">
+        <v>0</v>
+      </c>
       <c r="N17" t="s">
-        <v>2</v>
-      </c>
-      <c r="O17" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="O17" s="2">
+        <v>0</v>
+      </c>
       <c r="P17" t="s">
-        <v>2</v>
-      </c>
-      <c r="Q17" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="Q17" s="2">
+        <v>0</v>
+      </c>
       <c r="R17" t="s">
-        <v>2</v>
-      </c>
-      <c r="S17" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="S17" s="2">
+        <v>0</v>
+      </c>
       <c r="T17" t="s">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="U17" t="s">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="V17" t="s">
-        <v>2</v>
-      </c>
-      <c r="W17" s="2"/>
+        <v>61</v>
+      </c>
+      <c r="W17" s="2">
+        <v>0</v>
+      </c>
       <c r="X17" t="s">
-        <v>2</v>
-      </c>
-      <c r="Y17" s="2"/>
+        <v>61</v>
+      </c>
+      <c r="Y17" s="2">
+        <v>1</v>
+      </c>
       <c r="Z17" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA17" s="2"/>
+        <v>65</v>
+      </c>
+      <c r="AA17" s="2">
+        <v>1</v>
+      </c>
       <c r="AB17" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC17" s="2"/>
+        <v>70</v>
+      </c>
+      <c r="AC17" s="2">
+        <v>0</v>
+      </c>
       <c r="AD17" t="s">
-        <v>2</v>
-      </c>
-      <c r="AE17" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="AE17" s="2">
+        <v>0</v>
+      </c>
       <c r="AF17" t="s">
-        <v>2</v>
-      </c>
-      <c r="AG17" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="AG17" s="2">
+        <v>0</v>
+      </c>
       <c r="AH17" t="s">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="AI17" s="2">
         <v>1</v>
@@ -9332,7 +9468,9 @@
       <c r="AQ17" s="2">
         <v>0</v>
       </c>
-      <c r="AR17" s="2"/>
+      <c r="AR17" s="2">
+        <v>0</v>
+      </c>
       <c r="AS17" s="2">
         <v>0</v>
       </c>
@@ -9351,7 +9489,9 @@
       <c r="AX17" s="2">
         <v>0</v>
       </c>
-      <c r="AY17" s="2"/>
+      <c r="AY17" s="2">
+        <v>0</v>
+      </c>
       <c r="AZ17" s="2">
         <v>0</v>
       </c>
@@ -9367,8 +9507,12 @@
       <c r="BD17" s="2">
         <v>0</v>
       </c>
-      <c r="BE17" s="2"/>
-      <c r="BF17" s="2"/>
+      <c r="BE17" s="2">
+        <v>0</v>
+      </c>
+      <c r="BF17" s="2">
+        <v>0</v>
+      </c>
       <c r="BG17" s="2">
         <v>0</v>
       </c>
@@ -9387,7 +9531,9 @@
       <c r="BL17" s="2">
         <v>0</v>
       </c>
-      <c r="BM17" s="2"/>
+      <c r="BM17" s="2">
+        <v>0</v>
+      </c>
       <c r="BN17" s="2">
         <v>0</v>
       </c>
@@ -9406,7 +9552,9 @@
       <c r="BS17" s="2">
         <v>0</v>
       </c>
-      <c r="BT17" s="2"/>
+      <c r="BT17" s="2">
+        <v>0</v>
+      </c>
       <c r="BU17" s="2">
         <v>1</v>
       </c>
@@ -9428,11 +9576,15 @@
       <c r="CA17" s="2">
         <v>1</v>
       </c>
-      <c r="CB17" s="2"/>
+      <c r="CB17" s="2">
+        <v>0</v>
+      </c>
       <c r="CC17" s="2">
         <v>0</v>
       </c>
-      <c r="CD17" s="2"/>
+      <c r="CD17" s="2">
+        <v>0</v>
+      </c>
       <c r="CE17" s="2">
         <v>1</v>
       </c>
@@ -9442,30 +9594,42 @@
       <c r="CG17" s="2">
         <v>0</v>
       </c>
-      <c r="CH17" s="2"/>
+      <c r="CH17" s="2">
+        <v>0</v>
+      </c>
       <c r="CI17" s="2">
         <v>0</v>
       </c>
-      <c r="CJ17" s="2"/>
+      <c r="CJ17" s="2">
+        <v>0</v>
+      </c>
       <c r="CK17" s="2">
-        <v>1</v>
-      </c>
-      <c r="CL17" s="2"/>
+        <v>0</v>
+      </c>
+      <c r="CL17" s="2">
+        <v>1</v>
+      </c>
       <c r="CM17" s="2">
         <v>0</v>
       </c>
-      <c r="CN17" s="2"/>
+      <c r="CN17" s="2">
+        <v>0</v>
+      </c>
       <c r="CO17" s="2">
         <v>1</v>
       </c>
-      <c r="CP17" s="2"/>
+      <c r="CP17" s="2">
+        <v>0</v>
+      </c>
       <c r="CQ17" s="2">
         <v>1</v>
       </c>
       <c r="CR17" s="2">
         <v>0</v>
       </c>
-      <c r="CS17" s="2"/>
+      <c r="CS17" s="2">
+        <v>0</v>
+      </c>
       <c r="CT17" s="2">
         <v>0</v>
       </c>
@@ -9481,7 +9645,9 @@
       <c r="CX17" s="2">
         <v>0</v>
       </c>
-      <c r="CY17" s="2"/>
+      <c r="CY17" s="2">
+        <v>0</v>
+      </c>
       <c r="CZ17" s="2">
         <v>0</v>
       </c>
@@ -9497,7 +9663,9 @@
       <c r="DD17" s="2">
         <v>0</v>
       </c>
-      <c r="DE17" s="2"/>
+      <c r="DE17" s="2">
+        <v>0</v>
+      </c>
       <c r="DF17" s="2">
         <v>0</v>
       </c>
@@ -9532,7 +9700,7 @@
         <v>0</v>
       </c>
       <c r="DQ17" s="2">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="DR17" s="2">
         <v>301</v>
@@ -9637,77 +9805,69 @@
         <v>290</v>
       </c>
       <c r="EZ17" t="s">
-        <v>292</v>
+        <v>2</v>
       </c>
       <c r="FA17" t="s">
-        <v>294</v>
+        <v>2</v>
       </c>
       <c r="FB17" t="s">
-        <v>303</v>
+        <v>2</v>
       </c>
       <c r="FC17" t="s">
-        <v>312</v>
-      </c>
-      <c r="FD17" s="2">
-        <v>301</v>
-      </c>
-      <c r="FE17" s="2">
-        <v>216</v>
-      </c>
-      <c r="FF17" s="2">
-        <v>2024</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="FD17" s="2"/>
+      <c r="FE17" s="2"/>
+      <c r="FF17" s="2"/>
       <c r="FG17" t="s">
-        <v>318</v>
+        <v>2</v>
       </c>
       <c r="FH17" t="s">
-        <v>272</v>
+        <v>2</v>
       </c>
       <c r="FI17" t="s">
         <v>2</v>
       </c>
       <c r="FJ17" t="s">
-        <v>322</v>
+        <v>2</v>
       </c>
       <c r="FK17" t="s">
         <v>2</v>
       </c>
       <c r="FL17" t="s">
-        <v>329</v>
-      </c>
-      <c r="FM17" s="1">
-        <v>45847</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="FM17" s="1"/>
       <c r="FN17" t="s">
-        <v>338</v>
+        <v>2</v>
       </c>
       <c r="FO17" t="s">
-        <v>346</v>
+        <v>2</v>
       </c>
       <c r="FP17" t="s">
-        <v>355</v>
+        <v>2</v>
       </c>
       <c r="FQ17" t="s">
-        <v>357</v>
+        <v>2</v>
       </c>
       <c r="FR17" t="s">
-        <v>190</v>
+        <v>2</v>
       </c>
       <c r="FS17" t="s">
-        <v>360</v>
+        <v>2</v>
       </c>
       <c r="FT17" t="s">
-        <v>202</v>
+        <v>2</v>
       </c>
       <c r="FU17" t="s">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="FV17" s="2"/>
       <c r="FW17" t="s">
-        <v>248</v>
+        <v>2</v>
       </c>
       <c r="FX17" t="s">
-        <v>366</v>
+        <v>2</v>
       </c>
       <c r="FY17" s="2">
         <v>1</v>

--- a/test_data.xlsx
+++ b/test_data.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="2378" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="3567" uniqueCount="369">
   <si>
     <t>publication_date_2025</t>
   </si>
@@ -1154,6 +1154,9 @@
   </si>
   <si>
     <t>a</t>
+  </si>
+  <si>
+    <t>f399c9ab-8c28-403e-b623-61b7ffcb75b1</t>
   </si>
 </sst>
 </file>
@@ -4684,7 +4687,7 @@
         <v>239</v>
       </c>
       <c r="EK7" t="s">
-        <v>243</v>
+        <v>368</v>
       </c>
       <c r="EL7" t="s">
         <v>250</v>

--- a/test_data.xlsx
+++ b/test_data.xlsx
@@ -1,19 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\agrosko\Dropbox\Coding\srn\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF972988-37DA-4DBD-9DFE-2704CEEA93F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView xWindow="-28920" yWindow="-765" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="125725" fullCalcOnLoad="true"/>
+  <calcPr calcId="0" fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="3567" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="2378" uniqueCount="370">
   <si>
     <t>publication_date_2025</t>
   </si>
@@ -82,9 +89,6 @@
   </si>
   <si>
     <t>Demant</t>
-  </si>
-  <si>
-    <t>Ringkj√∏bing Landbobank</t>
   </si>
   <si>
     <t>Ringkjøbing Landbobank</t>
@@ -1157,6 +1161,12 @@
   </si>
   <si>
     <t>f399c9ab-8c28-403e-b623-61b7ffcb75b1</t>
+  </si>
+  <si>
+    <t>Ringkj√∏bing Landbobank</t>
+  </si>
+  <si>
+    <t>2025</t>
   </si>
 </sst>
 </file>
@@ -1185,27 +1195,364 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border/>
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyBorder="true"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyBorder="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="true">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="false"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="true">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="false"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="false">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="true">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="false"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:FY17"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -1221,535 +1568,535 @@
         <v>16</v>
       </c>
       <c r="E1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" t="s">
         <v>27</v>
       </c>
-      <c r="F1" t="s">
-        <v>28</v>
-      </c>
       <c r="G1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1" t="s">
         <v>33</v>
       </c>
-      <c r="H1" t="s">
-        <v>34</v>
-      </c>
       <c r="I1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J1" t="s">
         <v>36</v>
       </c>
-      <c r="J1" t="s">
-        <v>37</v>
-      </c>
       <c r="K1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q1" t="s">
+        <v>51</v>
+      </c>
+      <c r="R1" t="s">
+        <v>36</v>
+      </c>
+      <c r="S1" t="s">
         <v>52</v>
       </c>
-      <c r="R1" t="s">
-        <v>37</v>
-      </c>
-      <c r="S1" t="s">
-        <v>53</v>
-      </c>
       <c r="T1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="U1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="V1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="W1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="X1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="Z1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AA1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AB1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AC1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AD1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AE1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AF1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AG1" t="s">
+        <v>77</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AI1" t="s">
         <v>78</v>
       </c>
-      <c r="AH1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>79</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AK1" t="s">
         <v>80</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AL1" t="s">
         <v>81</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AM1" t="s">
         <v>82</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AN1" t="s">
         <v>83</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>84</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>85</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AQ1" t="s">
         <v>86</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AR1" t="s">
         <v>87</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AS1" t="s">
         <v>88</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AT1" t="s">
         <v>89</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AU1" t="s">
         <v>90</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AV1" t="s">
         <v>91</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AW1" t="s">
         <v>92</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AX1" t="s">
         <v>93</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AY1" t="s">
         <v>94</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AZ1" t="s">
         <v>95</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BA1" t="s">
         <v>96</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BB1" t="s">
         <v>97</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BC1" t="s">
         <v>98</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BD1" t="s">
         <v>99</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BE1" t="s">
         <v>100</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BF1" t="s">
         <v>101</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BG1" t="s">
         <v>102</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BH1" t="s">
         <v>103</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BI1" t="s">
         <v>104</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BJ1" t="s">
         <v>105</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BK1" t="s">
         <v>106</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BL1" t="s">
         <v>107</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BM1" t="s">
         <v>108</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BN1" t="s">
         <v>109</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BO1" t="s">
         <v>110</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BP1" t="s">
         <v>111</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BQ1" t="s">
         <v>112</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BR1" t="s">
         <v>113</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BS1" t="s">
         <v>114</v>
       </c>
-      <c r="BS1" t="s">
+      <c r="BT1" t="s">
         <v>115</v>
       </c>
-      <c r="BT1" t="s">
+      <c r="BU1" t="s">
         <v>116</v>
       </c>
-      <c r="BU1" t="s">
+      <c r="BV1" t="s">
         <v>117</v>
       </c>
-      <c r="BV1" t="s">
+      <c r="BW1" t="s">
         <v>118</v>
       </c>
-      <c r="BW1" t="s">
+      <c r="BX1" t="s">
         <v>119</v>
       </c>
-      <c r="BX1" t="s">
+      <c r="BY1" t="s">
         <v>120</v>
       </c>
-      <c r="BY1" t="s">
+      <c r="BZ1" t="s">
         <v>121</v>
       </c>
-      <c r="BZ1" t="s">
+      <c r="CA1" t="s">
         <v>122</v>
       </c>
-      <c r="CA1" t="s">
+      <c r="CB1" t="s">
         <v>123</v>
       </c>
-      <c r="CB1" t="s">
+      <c r="CC1" t="s">
         <v>124</v>
       </c>
-      <c r="CC1" t="s">
+      <c r="CD1" t="s">
         <v>125</v>
       </c>
-      <c r="CD1" t="s">
+      <c r="CE1" t="s">
         <v>126</v>
       </c>
-      <c r="CE1" t="s">
+      <c r="CF1" t="s">
         <v>127</v>
       </c>
-      <c r="CF1" t="s">
+      <c r="CG1" t="s">
         <v>128</v>
       </c>
-      <c r="CG1" t="s">
+      <c r="CH1" t="s">
         <v>129</v>
       </c>
-      <c r="CH1" t="s">
+      <c r="CI1" t="s">
         <v>130</v>
       </c>
-      <c r="CI1" t="s">
+      <c r="CJ1" t="s">
         <v>131</v>
       </c>
-      <c r="CJ1" t="s">
+      <c r="CK1" t="s">
         <v>132</v>
       </c>
-      <c r="CK1" t="s">
+      <c r="CL1" t="s">
         <v>133</v>
       </c>
-      <c r="CL1" t="s">
+      <c r="CM1" t="s">
         <v>134</v>
       </c>
-      <c r="CM1" t="s">
+      <c r="CN1" t="s">
         <v>135</v>
       </c>
-      <c r="CN1" t="s">
+      <c r="CO1" t="s">
         <v>136</v>
       </c>
-      <c r="CO1" t="s">
+      <c r="CP1" t="s">
         <v>137</v>
       </c>
-      <c r="CP1" t="s">
+      <c r="CQ1" t="s">
         <v>138</v>
       </c>
-      <c r="CQ1" t="s">
+      <c r="CR1" t="s">
         <v>139</v>
       </c>
-      <c r="CR1" t="s">
+      <c r="CS1" t="s">
         <v>140</v>
       </c>
-      <c r="CS1" t="s">
+      <c r="CT1" t="s">
         <v>141</v>
       </c>
-      <c r="CT1" t="s">
+      <c r="CU1" t="s">
         <v>142</v>
       </c>
-      <c r="CU1" t="s">
+      <c r="CV1" t="s">
         <v>143</v>
       </c>
-      <c r="CV1" t="s">
+      <c r="CW1" t="s">
         <v>144</v>
       </c>
-      <c r="CW1" t="s">
+      <c r="CX1" t="s">
         <v>145</v>
       </c>
-      <c r="CX1" t="s">
+      <c r="CY1" t="s">
         <v>146</v>
       </c>
-      <c r="CY1" t="s">
+      <c r="CZ1" t="s">
         <v>147</v>
       </c>
-      <c r="CZ1" t="s">
+      <c r="DA1" t="s">
         <v>148</v>
       </c>
-      <c r="DA1" t="s">
+      <c r="DB1" t="s">
         <v>149</v>
       </c>
-      <c r="DB1" t="s">
+      <c r="DC1" t="s">
         <v>150</v>
       </c>
-      <c r="DC1" t="s">
+      <c r="DD1" t="s">
         <v>151</v>
       </c>
-      <c r="DD1" t="s">
+      <c r="DE1" t="s">
         <v>152</v>
       </c>
-      <c r="DE1" t="s">
+      <c r="DF1" t="s">
         <v>153</v>
       </c>
-      <c r="DF1" t="s">
+      <c r="DG1" t="s">
         <v>154</v>
       </c>
-      <c r="DG1" t="s">
+      <c r="DH1" t="s">
         <v>155</v>
       </c>
-      <c r="DH1" t="s">
+      <c r="DI1" t="s">
         <v>156</v>
       </c>
-      <c r="DI1" t="s">
+      <c r="DJ1" t="s">
         <v>157</v>
       </c>
-      <c r="DJ1" t="s">
+      <c r="DK1" t="s">
         <v>158</v>
       </c>
-      <c r="DK1" t="s">
+      <c r="DL1" t="s">
         <v>159</v>
       </c>
-      <c r="DL1" t="s">
+      <c r="DM1" t="s">
         <v>160</v>
       </c>
-      <c r="DM1" t="s">
+      <c r="DN1" t="s">
         <v>161</v>
       </c>
-      <c r="DN1" t="s">
+      <c r="DO1" t="s">
         <v>162</v>
       </c>
-      <c r="DO1" t="s">
+      <c r="DP1" t="s">
         <v>163</v>
       </c>
-      <c r="DP1" t="s">
+      <c r="DQ1" t="s">
         <v>164</v>
       </c>
-      <c r="DQ1" t="s">
+      <c r="DR1" t="s">
+        <v>164</v>
+      </c>
+      <c r="DS1" t="s">
         <v>165</v>
       </c>
-      <c r="DR1" t="s">
+      <c r="DT1" t="s">
         <v>166</v>
       </c>
-      <c r="DS1" t="s">
+      <c r="DU1" t="s">
         <v>167</v>
       </c>
-      <c r="DT1" t="s">
+      <c r="DV1" t="s">
         <v>168</v>
       </c>
-      <c r="DU1" t="s">
+      <c r="DW1" t="s">
         <v>169</v>
       </c>
-      <c r="DV1" t="s">
+      <c r="DX1" t="s">
         <v>170</v>
       </c>
-      <c r="DW1" t="s">
+      <c r="DY1" t="s">
         <v>171</v>
       </c>
-      <c r="DX1" t="s">
+      <c r="DZ1" t="s">
         <v>172</v>
       </c>
-      <c r="DY1" t="s">
-        <v>173</v>
-      </c>
-      <c r="DZ1" t="s">
-        <v>182</v>
-      </c>
       <c r="EA1" t="s">
+        <v>181</v>
+      </c>
+      <c r="EB1" t="s">
+        <v>190</v>
+      </c>
+      <c r="EC1" t="s">
         <v>191</v>
       </c>
-      <c r="EB1" t="s">
-        <v>192</v>
-      </c>
-      <c r="EC1" t="s">
-        <v>194</v>
-      </c>
       <c r="ED1" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="EE1" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="EF1" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="EG1" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="EH1" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="EI1" t="s">
+        <v>227</v>
+      </c>
+      <c r="EJ1" t="s">
+        <v>236</v>
+      </c>
+      <c r="EK1" t="s">
         <v>237</v>
       </c>
-      <c r="EJ1" t="s">
-        <v>238</v>
-      </c>
-      <c r="EK1" t="s">
-        <v>240</v>
-      </c>
       <c r="EL1" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="EM1" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="EN1" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="EO1" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="EP1" t="s">
+        <v>257</v>
+      </c>
+      <c r="EQ1" t="s">
+        <v>261</v>
+      </c>
+      <c r="ER1" t="s">
         <v>262</v>
       </c>
-      <c r="EQ1" t="s">
+      <c r="ES1" t="s">
         <v>263</v>
       </c>
-      <c r="ER1" t="s">
-        <v>264</v>
-      </c>
-      <c r="ES1" t="s">
-        <v>273</v>
-      </c>
       <c r="ET1" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="EU1" t="s">
+        <v>274</v>
+      </c>
+      <c r="EV1" t="s">
+        <v>276</v>
+      </c>
+      <c r="EW1" t="s">
         <v>277</v>
       </c>
-      <c r="EV1" t="s">
+      <c r="EX1" t="s">
         <v>278</v>
       </c>
-      <c r="EW1" t="s">
-        <v>279</v>
-      </c>
-      <c r="EX1" t="s">
+      <c r="EY1" t="s">
+        <v>280</v>
+      </c>
+      <c r="EZ1" t="s">
         <v>281</v>
       </c>
-      <c r="EY1" t="s">
-        <v>282</v>
-      </c>
-      <c r="EZ1" t="s">
-        <v>291</v>
-      </c>
       <c r="FA1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="FB1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="FC1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="FD1" t="s">
+        <v>312</v>
+      </c>
+      <c r="FE1" t="s">
         <v>313</v>
       </c>
-      <c r="FE1" t="s">
+      <c r="FF1" t="s">
         <v>314</v>
       </c>
-      <c r="FF1" t="s">
+      <c r="FG1" t="s">
         <v>315</v>
       </c>
-      <c r="FG1" t="s">
-        <v>316</v>
-      </c>
       <c r="FH1" t="s">
+        <v>318</v>
+      </c>
+      <c r="FI1" t="s">
         <v>319</v>
       </c>
-      <c r="FI1" t="s">
+      <c r="FJ1" t="s">
         <v>320</v>
       </c>
-      <c r="FJ1" t="s">
-        <v>321</v>
-      </c>
       <c r="FK1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="FL1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="FM1" t="s">
+        <v>329</v>
+      </c>
+      <c r="FN1" t="s">
         <v>330</v>
       </c>
-      <c r="FN1" t="s">
-        <v>331</v>
-      </c>
       <c r="FO1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="FP1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="FQ1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="FR1" t="s">
+        <v>357</v>
+      </c>
+      <c r="FS1" t="s">
         <v>358</v>
       </c>
-      <c r="FS1" t="s">
-        <v>359</v>
-      </c>
       <c r="FT1" t="s">
+        <v>360</v>
+      </c>
+      <c r="FU1" t="s">
         <v>361</v>
       </c>
-      <c r="FU1" t="s">
+      <c r="FV1" t="s">
         <v>362</v>
       </c>
-      <c r="FV1" t="s">
+      <c r="FW1" t="s">
         <v>363</v>
       </c>
-      <c r="FW1" t="s">
+      <c r="FX1" t="s">
         <v>364</v>
       </c>
-      <c r="FX1" t="s">
-        <v>365</v>
-      </c>
       <c r="FY1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="2">
@@ -2054,119 +2401,119 @@
       <c r="DQ2" s="2">
         <v>2024</v>
       </c>
-      <c r="DR2" s="2">
+      <c r="DR2" t="s">
+        <v>291</v>
+      </c>
+      <c r="DS2" s="2">
         <v>315</v>
       </c>
-      <c r="DS2" s="2">
+      <c r="DT2" s="2">
         <v>369</v>
       </c>
-      <c r="DT2" s="2">
+      <c r="DU2" s="2">
         <v>37116</v>
       </c>
-      <c r="DU2" s="2">
+      <c r="DV2" s="2">
         <v>22.288833618164063</v>
       </c>
-      <c r="DV2" s="2">
+      <c r="DW2" s="2">
         <v>1140</v>
       </c>
-      <c r="DW2" s="2">
+      <c r="DX2" s="2">
         <v>0.051753658801317215</v>
       </c>
-      <c r="DX2" s="2">
+      <c r="DY2" s="2">
         <v>49</v>
       </c>
-      <c r="DY2" t="s">
-        <v>174</v>
-      </c>
       <c r="DZ2" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="EA2" t="s">
+        <v>182</v>
+      </c>
+      <c r="EB2" t="s">
         <v>17</v>
       </c>
-      <c r="EB2" t="s">
-        <v>193</v>
-      </c>
       <c r="EC2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="ED2" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="EE2" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="EF2" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="EG2" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="EH2" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="EI2" t="s">
+        <v>228</v>
+      </c>
+      <c r="EJ2" t="s">
         <v>17</v>
       </c>
-      <c r="EJ2" t="s">
-        <v>239</v>
-      </c>
       <c r="EK2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="EL2" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="EM2" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="EN2" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="EO2" t="s">
-        <v>259</v>
-      </c>
-      <c r="EP2" s="2">
+        <v>253</v>
+      </c>
+      <c r="EP2" t="s">
+        <v>258</v>
+      </c>
+      <c r="EQ2" s="2">
         <v>52</v>
       </c>
-      <c r="EQ2" s="2">
+      <c r="ER2" s="2">
         <v>111</v>
       </c>
-      <c r="ER2" t="s">
-        <v>265</v>
-      </c>
       <c r="ES2" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="ET2" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="EU2" t="s">
-        <v>239</v>
+        <v>275</v>
       </c>
       <c r="EV2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="EW2" t="s">
-        <v>280</v>
-      </c>
-      <c r="EX2" s="2">
+        <v>238</v>
+      </c>
+      <c r="EX2" t="s">
+        <v>279</v>
+      </c>
+      <c r="EY2" s="2">
         <v>60</v>
       </c>
-      <c r="EY2" t="s">
-        <v>283</v>
-      </c>
       <c r="EZ2" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="FA2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="FB2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="FC2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="FD2" s="2">
         <v>315</v>
@@ -2178,56 +2525,56 @@
         <v>2024</v>
       </c>
       <c r="FG2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="FH2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="FI2" t="s">
         <v>2</v>
       </c>
       <c r="FJ2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="FK2" t="s">
         <v>2</v>
       </c>
       <c r="FL2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="FM2" s="1">
         <v>45840</v>
       </c>
       <c r="FN2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="FO2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="FP2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="FQ2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="FR2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="FS2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="FT2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="FU2" t="s">
         <v>17</v>
       </c>
       <c r="FV2" s="2"/>
       <c r="FW2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="FX2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="FY2" s="2">
         <v>1</v>
@@ -2250,7 +2597,7 @@
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G3" s="1">
         <v>46057</v>
@@ -2262,79 +2609,79 @@
         <v>1</v>
       </c>
       <c r="J3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K3" s="2">
+        <v>0</v>
+      </c>
+      <c r="L3" t="s">
         <v>38</v>
       </c>
-      <c r="K3" s="2">
-        <v>0</v>
-      </c>
-      <c r="L3" t="s">
-        <v>39</v>
-      </c>
       <c r="M3" s="2">
         <v>0</v>
       </c>
       <c r="N3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O3" s="2">
         <v>0</v>
       </c>
       <c r="P3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q3" s="2">
         <v>0</v>
       </c>
       <c r="R3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S3" s="2">
         <v>0</v>
       </c>
       <c r="T3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="U3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="V3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W3" s="2">
         <v>0</v>
       </c>
       <c r="X3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Y3" s="2">
         <v>0</v>
       </c>
       <c r="Z3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AA3" s="2">
         <v>0</v>
       </c>
       <c r="AB3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AC3" s="2">
         <v>1</v>
       </c>
       <c r="AD3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AE3" s="2">
         <v>0</v>
       </c>
       <c r="AF3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AG3" s="2">
         <v>0</v>
       </c>
       <c r="AH3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AI3" s="2">
         <v>1</v>
@@ -2597,110 +2944,110 @@
       <c r="DQ3" s="2">
         <v>2025</v>
       </c>
-      <c r="DR3" s="2">
+      <c r="DR3" t="s">
+        <v>369</v>
+      </c>
+      <c r="DS3" s="2">
         <v>315</v>
       </c>
-      <c r="DS3" s="2">
+      <c r="DT3" s="2">
         <v>369</v>
       </c>
-      <c r="DT3" s="2">
+      <c r="DU3" s="2">
         <v>37116</v>
       </c>
-      <c r="DU3" s="2">
+      <c r="DV3" s="2">
         <v>22.288833618164063</v>
       </c>
-      <c r="DV3" s="2">
+      <c r="DW3" s="2">
         <v>1140</v>
       </c>
-      <c r="DW3" s="2">
+      <c r="DX3" s="2">
         <v>0.051753658801317215</v>
       </c>
-      <c r="DX3" s="2">
+      <c r="DY3" s="2">
         <v>49</v>
       </c>
-      <c r="DY3" t="s">
-        <v>174</v>
-      </c>
       <c r="DZ3" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="EA3" t="s">
+        <v>182</v>
+      </c>
+      <c r="EB3" t="s">
         <v>17</v>
       </c>
-      <c r="EB3" t="s">
-        <v>193</v>
-      </c>
       <c r="EC3" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="ED3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="EE3" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="EF3" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="EG3" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="EH3" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="EI3" t="s">
+        <v>228</v>
+      </c>
+      <c r="EJ3" t="s">
         <v>17</v>
       </c>
-      <c r="EJ3" t="s">
-        <v>239</v>
-      </c>
       <c r="EK3" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="EL3" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="EM3" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="EN3" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="EO3" t="s">
-        <v>259</v>
-      </c>
-      <c r="EP3" s="2">
+        <v>253</v>
+      </c>
+      <c r="EP3" t="s">
+        <v>258</v>
+      </c>
+      <c r="EQ3" s="2">
         <v>52</v>
       </c>
-      <c r="EQ3" s="2">
+      <c r="ER3" s="2">
         <v>111</v>
       </c>
-      <c r="ER3" t="s">
-        <v>265</v>
-      </c>
       <c r="ES3" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="ET3" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="EU3" t="s">
-        <v>239</v>
+        <v>275</v>
       </c>
       <c r="EV3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="EW3" t="s">
-        <v>280</v>
-      </c>
-      <c r="EX3" s="2">
+        <v>238</v>
+      </c>
+      <c r="EX3" t="s">
+        <v>279</v>
+      </c>
+      <c r="EY3" s="2">
         <v>60</v>
       </c>
-      <c r="EY3" t="s">
-        <v>283</v>
-      </c>
       <c r="EZ3" t="s">
-        <v>2</v>
+        <v>282</v>
       </c>
       <c r="FA3" t="s">
         <v>2</v>
@@ -3070,119 +3417,119 @@
       <c r="DQ4" s="2">
         <v>2024</v>
       </c>
-      <c r="DR4" s="2">
+      <c r="DR4" t="s">
+        <v>291</v>
+      </c>
+      <c r="DS4" s="2">
         <v>254</v>
       </c>
-      <c r="DS4" s="2">
+      <c r="DT4" s="2">
         <v>357</v>
       </c>
-      <c r="DT4" s="2">
+      <c r="DU4" s="2">
         <v>27483</v>
       </c>
-      <c r="DU4" s="2">
+      <c r="DV4" s="2">
         <v>16.569766998291016</v>
       </c>
-      <c r="DV4" s="2">
+      <c r="DW4" s="2">
         <v>1055</v>
       </c>
-      <c r="DW4" s="2">
+      <c r="DX4" s="2">
         <v>0.048195261508226395</v>
       </c>
-      <c r="DX4" s="2">
+      <c r="DY4" s="2">
         <v>46</v>
       </c>
-      <c r="DY4" t="s">
-        <v>175</v>
-      </c>
       <c r="DZ4" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="EA4" t="s">
+        <v>183</v>
+      </c>
+      <c r="EB4" t="s">
         <v>19</v>
       </c>
-      <c r="EB4" t="s">
-        <v>193</v>
-      </c>
       <c r="EC4" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="ED4" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="EE4" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="EF4" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="EG4" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="EH4" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="EI4" t="s">
+        <v>229</v>
+      </c>
+      <c r="EJ4" t="s">
         <v>19</v>
       </c>
-      <c r="EJ4" t="s">
-        <v>239</v>
-      </c>
       <c r="EK4" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="EL4" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="EM4" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="EN4" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="EO4" t="s">
-        <v>260</v>
-      </c>
-      <c r="EP4" s="2">
+        <v>254</v>
+      </c>
+      <c r="EP4" t="s">
+        <v>259</v>
+      </c>
+      <c r="EQ4" s="2">
         <v>42</v>
       </c>
-      <c r="EQ4" s="2">
+      <c r="ER4" s="2">
         <v>84</v>
       </c>
-      <c r="ER4" t="s">
-        <v>266</v>
-      </c>
       <c r="ES4" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="ET4" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="EU4" t="s">
-        <v>239</v>
+        <v>275</v>
       </c>
       <c r="EV4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="EW4" t="s">
-        <v>280</v>
-      </c>
-      <c r="EX4" s="2">
+        <v>238</v>
+      </c>
+      <c r="EX4" t="s">
+        <v>279</v>
+      </c>
+      <c r="EY4" s="2">
         <v>43</v>
       </c>
-      <c r="EY4" t="s">
-        <v>284</v>
-      </c>
       <c r="EZ4" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="FA4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="FB4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="FC4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="FD4" s="2">
         <v>254</v>
@@ -3194,56 +3541,56 @@
         <v>2024</v>
       </c>
       <c r="FG4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="FH4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="FI4" t="s">
         <v>2</v>
       </c>
       <c r="FJ4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="FK4" t="s">
         <v>2</v>
       </c>
       <c r="FL4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="FM4" s="1">
         <v>45840</v>
       </c>
       <c r="FN4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="FO4" t="s">
         <v>18</v>
       </c>
       <c r="FP4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="FQ4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="FR4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="FS4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="FT4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="FU4" t="s">
         <v>19</v>
       </c>
       <c r="FV4" s="2"/>
       <c r="FW4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="FX4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="FY4" s="2">
         <v>1</v>
@@ -3266,7 +3613,7 @@
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G5" s="1">
         <v>46057</v>
@@ -3278,79 +3625,79 @@
         <v>0</v>
       </c>
       <c r="J5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K5" s="2">
         <v>0</v>
       </c>
       <c r="L5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M5" s="2">
         <v>0</v>
       </c>
       <c r="N5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O5" s="2">
         <v>0</v>
       </c>
       <c r="P5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q5" s="2">
         <v>0</v>
       </c>
       <c r="R5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S5" s="2">
         <v>0</v>
       </c>
       <c r="T5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="V5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="W5" s="2">
         <v>0</v>
       </c>
       <c r="X5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Y5" s="2">
         <v>0</v>
       </c>
       <c r="Z5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AA5" s="2">
         <v>1</v>
       </c>
       <c r="AB5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AC5" s="2">
         <v>1</v>
       </c>
       <c r="AD5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AE5" s="2">
         <v>1</v>
       </c>
       <c r="AF5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AG5" s="2">
         <v>0</v>
       </c>
       <c r="AH5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AI5" s="2">
         <v>1</v>
@@ -3613,110 +3960,110 @@
       <c r="DQ5" s="2">
         <v>2025</v>
       </c>
-      <c r="DR5" s="2">
+      <c r="DR5" t="s">
+        <v>369</v>
+      </c>
+      <c r="DS5" s="2">
         <v>254</v>
       </c>
-      <c r="DS5" s="2">
+      <c r="DT5" s="2">
         <v>357</v>
       </c>
-      <c r="DT5" s="2">
+      <c r="DU5" s="2">
         <v>27483</v>
       </c>
-      <c r="DU5" s="2">
+      <c r="DV5" s="2">
         <v>16.569766998291016</v>
       </c>
-      <c r="DV5" s="2">
+      <c r="DW5" s="2">
         <v>1055</v>
       </c>
-      <c r="DW5" s="2">
+      <c r="DX5" s="2">
         <v>0.048195261508226395</v>
       </c>
-      <c r="DX5" s="2">
+      <c r="DY5" s="2">
         <v>46</v>
       </c>
-      <c r="DY5" t="s">
-        <v>175</v>
-      </c>
       <c r="DZ5" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="EA5" t="s">
+        <v>183</v>
+      </c>
+      <c r="EB5" t="s">
         <v>19</v>
       </c>
-      <c r="EB5" t="s">
-        <v>193</v>
-      </c>
       <c r="EC5" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="ED5" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="EE5" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="EF5" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="EG5" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="EH5" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="EI5" t="s">
+        <v>229</v>
+      </c>
+      <c r="EJ5" t="s">
         <v>19</v>
       </c>
-      <c r="EJ5" t="s">
-        <v>239</v>
-      </c>
       <c r="EK5" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="EL5" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="EM5" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="EN5" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="EO5" t="s">
-        <v>260</v>
-      </c>
-      <c r="EP5" s="2">
+        <v>254</v>
+      </c>
+      <c r="EP5" t="s">
+        <v>259</v>
+      </c>
+      <c r="EQ5" s="2">
         <v>42</v>
       </c>
-      <c r="EQ5" s="2">
+      <c r="ER5" s="2">
         <v>84</v>
       </c>
-      <c r="ER5" t="s">
-        <v>266</v>
-      </c>
       <c r="ES5" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="ET5" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="EU5" t="s">
-        <v>239</v>
+        <v>275</v>
       </c>
       <c r="EV5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="EW5" t="s">
-        <v>280</v>
-      </c>
-      <c r="EX5" s="2">
+        <v>238</v>
+      </c>
+      <c r="EX5" t="s">
+        <v>279</v>
+      </c>
+      <c r="EY5" s="2">
         <v>43</v>
       </c>
-      <c r="EY5" t="s">
-        <v>284</v>
-      </c>
       <c r="EZ5" t="s">
-        <v>2</v>
+        <v>283</v>
       </c>
       <c r="FA5" t="s">
         <v>2</v>
@@ -4086,119 +4433,119 @@
       <c r="DQ6" s="2">
         <v>2024</v>
       </c>
-      <c r="DR6" s="2">
+      <c r="DR6" t="s">
+        <v>291</v>
+      </c>
+      <c r="DS6" s="2">
         <v>246</v>
       </c>
-      <c r="DS6" s="2">
+      <c r="DT6" s="2">
         <v>258</v>
       </c>
-      <c r="DT6" s="2">
+      <c r="DU6" s="2">
         <v>22534</v>
       </c>
-      <c r="DU6" s="2">
+      <c r="DV6" s="2">
         <v>30.837818145751953</v>
       </c>
-      <c r="DV6" s="2">
+      <c r="DW6" s="2">
         <v>916</v>
       </c>
-      <c r="DW6" s="2">
+      <c r="DX6" s="2">
         <v>0.12325027585029602</v>
       </c>
-      <c r="DX6" s="2">
+      <c r="DY6" s="2">
         <v>44</v>
       </c>
-      <c r="DY6" t="s">
-        <v>176</v>
-      </c>
       <c r="DZ6" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="EA6" t="s">
+        <v>184</v>
+      </c>
+      <c r="EB6" t="s">
         <v>20</v>
       </c>
-      <c r="EB6" t="s">
-        <v>193</v>
-      </c>
       <c r="EC6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="ED6" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="EE6" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="EF6" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="EG6" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="EH6" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="EI6" t="s">
+        <v>230</v>
+      </c>
+      <c r="EJ6" t="s">
         <v>20</v>
       </c>
-      <c r="EJ6" t="s">
-        <v>239</v>
-      </c>
       <c r="EK6" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="EL6" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="EM6" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="EN6" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="EO6" t="s">
-        <v>261</v>
-      </c>
-      <c r="EP6" s="2">
+        <v>253</v>
+      </c>
+      <c r="EP6" t="s">
+        <v>260</v>
+      </c>
+      <c r="EQ6" s="2">
         <v>47</v>
       </c>
-      <c r="EQ6" s="2">
+      <c r="ER6" s="2">
         <v>101</v>
       </c>
-      <c r="ER6" t="s">
-        <v>267</v>
-      </c>
       <c r="ES6" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="ET6" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="EU6" t="s">
-        <v>239</v>
+        <v>275</v>
       </c>
       <c r="EV6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="EW6" t="s">
-        <v>280</v>
-      </c>
-      <c r="EX6" s="2">
+        <v>238</v>
+      </c>
+      <c r="EX6" t="s">
+        <v>279</v>
+      </c>
+      <c r="EY6" s="2">
         <v>55</v>
       </c>
-      <c r="EY6" t="s">
-        <v>285</v>
-      </c>
       <c r="EZ6" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="FA6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="FB6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="FC6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="FD6" s="2">
         <v>246</v>
@@ -4210,56 +4557,56 @@
         <v>2024</v>
       </c>
       <c r="FG6" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="FH6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="FI6" t="s">
         <v>2</v>
       </c>
       <c r="FJ6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="FK6" t="s">
         <v>2</v>
       </c>
       <c r="FL6" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="FM6" s="1">
         <v>45835</v>
       </c>
       <c r="FN6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="FO6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="FP6" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="FQ6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="FR6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="FS6" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="FT6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="FU6" t="s">
         <v>20</v>
       </c>
       <c r="FV6" s="2"/>
       <c r="FW6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="FX6" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="FY6" s="2">
         <v>1</v>
@@ -4282,91 +4629,91 @@
         <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G7" s="1">
         <v>46058</v>
       </c>
       <c r="H7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I7" s="2">
         <v>1</v>
       </c>
       <c r="J7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K7" s="2">
         <v>0</v>
       </c>
       <c r="L7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M7" s="2">
         <v>1</v>
       </c>
       <c r="N7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O7" s="2">
         <v>0</v>
       </c>
       <c r="P7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q7" s="2">
         <v>0</v>
       </c>
       <c r="R7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S7" s="2">
         <v>0</v>
       </c>
       <c r="T7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="U7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="V7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="W7" s="2">
         <v>0</v>
       </c>
       <c r="X7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Y7" s="2">
         <v>0</v>
       </c>
       <c r="Z7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AA7" s="2">
         <v>1</v>
       </c>
       <c r="AB7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AC7" s="2">
         <v>0</v>
       </c>
       <c r="AD7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AE7" s="2">
         <v>0</v>
       </c>
       <c r="AF7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AG7" s="2">
         <v>0</v>
       </c>
       <c r="AH7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AI7" s="2">
         <v>1</v>
@@ -4629,110 +4976,110 @@
       <c r="DQ7" s="2">
         <v>2025</v>
       </c>
-      <c r="DR7" s="2">
+      <c r="DR7" t="s">
+        <v>369</v>
+      </c>
+      <c r="DS7" s="2">
         <v>246</v>
       </c>
-      <c r="DS7" s="2">
+      <c r="DT7" s="2">
         <v>258</v>
       </c>
-      <c r="DT7" s="2">
+      <c r="DU7" s="2">
         <v>22534</v>
       </c>
-      <c r="DU7" s="2">
+      <c r="DV7" s="2">
         <v>30.837818145751953</v>
       </c>
-      <c r="DV7" s="2">
+      <c r="DW7" s="2">
         <v>916</v>
       </c>
-      <c r="DW7" s="2">
+      <c r="DX7" s="2">
         <v>0.12325027585029602</v>
       </c>
-      <c r="DX7" s="2">
+      <c r="DY7" s="2">
         <v>44</v>
       </c>
-      <c r="DY7" t="s">
-        <v>176</v>
-      </c>
       <c r="DZ7" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="EA7" t="s">
+        <v>184</v>
+      </c>
+      <c r="EB7" t="s">
         <v>20</v>
       </c>
-      <c r="EB7" t="s">
-        <v>193</v>
-      </c>
       <c r="EC7" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="ED7" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="EE7" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="EF7" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="EG7" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="EH7" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="EI7" t="s">
+        <v>230</v>
+      </c>
+      <c r="EJ7" t="s">
         <v>20</v>
       </c>
-      <c r="EJ7" t="s">
-        <v>239</v>
-      </c>
       <c r="EK7" t="s">
-        <v>368</v>
+        <v>238</v>
       </c>
       <c r="EL7" t="s">
-        <v>250</v>
+        <v>367</v>
       </c>
       <c r="EM7" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="EN7" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="EO7" t="s">
-        <v>261</v>
-      </c>
-      <c r="EP7" s="2">
+        <v>253</v>
+      </c>
+      <c r="EP7" t="s">
+        <v>260</v>
+      </c>
+      <c r="EQ7" s="2">
         <v>47</v>
       </c>
-      <c r="EQ7" s="2">
+      <c r="ER7" s="2">
         <v>101</v>
       </c>
-      <c r="ER7" t="s">
-        <v>267</v>
-      </c>
       <c r="ES7" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="ET7" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="EU7" t="s">
-        <v>239</v>
+        <v>275</v>
       </c>
       <c r="EV7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="EW7" t="s">
-        <v>280</v>
-      </c>
-      <c r="EX7" s="2">
+        <v>238</v>
+      </c>
+      <c r="EX7" t="s">
+        <v>279</v>
+      </c>
+      <c r="EY7" s="2">
         <v>55</v>
       </c>
-      <c r="EY7" t="s">
-        <v>285</v>
-      </c>
       <c r="EZ7" t="s">
-        <v>2</v>
+        <v>284</v>
       </c>
       <c r="FA7" t="s">
         <v>2</v>
@@ -5102,119 +5449,119 @@
       <c r="DQ8" s="2">
         <v>2024</v>
       </c>
-      <c r="DR8" s="2">
+      <c r="DR8" t="s">
+        <v>291</v>
+      </c>
+      <c r="DS8" s="2">
         <v>387</v>
       </c>
-      <c r="DS8" s="2">
+      <c r="DT8" s="2">
         <v>725</v>
       </c>
-      <c r="DT8" s="2">
+      <c r="DU8" s="2">
         <v>36918</v>
       </c>
-      <c r="DU8" s="2">
+      <c r="DV8" s="2">
         <v>20.384178161621094</v>
       </c>
-      <c r="DV8" s="2">
+      <c r="DW8" s="2">
         <v>1182</v>
       </c>
-      <c r="DW8" s="2">
+      <c r="DX8" s="2">
         <v>0.25176948308944702</v>
       </c>
-      <c r="DX8" s="2">
+      <c r="DY8" s="2">
         <v>56</v>
       </c>
-      <c r="DY8" t="s">
-        <v>177</v>
-      </c>
       <c r="DZ8" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="EA8" t="s">
+        <v>185</v>
+      </c>
+      <c r="EB8" t="s">
         <v>21</v>
       </c>
-      <c r="EB8" t="s">
-        <v>193</v>
-      </c>
       <c r="EC8" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="ED8" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="EE8" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="EF8" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="EG8" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="EH8" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="EI8" t="s">
+        <v>231</v>
+      </c>
+      <c r="EJ8" t="s">
         <v>21</v>
       </c>
-      <c r="EJ8" t="s">
-        <v>239</v>
-      </c>
       <c r="EK8" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="EL8" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="EM8" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="EN8" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="EO8" t="s">
-        <v>260</v>
-      </c>
-      <c r="EP8" s="2">
+        <v>255</v>
+      </c>
+      <c r="EP8" t="s">
+        <v>259</v>
+      </c>
+      <c r="EQ8" s="2">
         <v>53</v>
       </c>
-      <c r="EQ8" s="2">
+      <c r="ER8" s="2">
         <v>131</v>
       </c>
-      <c r="ER8" t="s">
-        <v>268</v>
-      </c>
       <c r="ES8" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="ET8" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="EU8" t="s">
-        <v>239</v>
+        <v>275</v>
       </c>
       <c r="EV8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="EW8" t="s">
-        <v>280</v>
-      </c>
-      <c r="EX8" s="2">
+        <v>238</v>
+      </c>
+      <c r="EX8" t="s">
+        <v>279</v>
+      </c>
+      <c r="EY8" s="2">
         <v>79</v>
       </c>
-      <c r="EY8" t="s">
-        <v>286</v>
-      </c>
       <c r="EZ8" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="FA8" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="FB8" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="FC8" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="FD8" s="2">
         <v>387</v>
@@ -5226,56 +5573,56 @@
         <v>2024</v>
       </c>
       <c r="FG8" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="FH8" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="FI8" t="s">
         <v>2</v>
       </c>
       <c r="FJ8" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="FK8" t="s">
         <v>2</v>
       </c>
       <c r="FL8" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="FM8" s="1">
         <v>45840</v>
       </c>
       <c r="FN8" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="FO8" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="FP8" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="FQ8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="FR8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="FS8" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="FT8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="FU8" t="s">
         <v>21</v>
       </c>
       <c r="FV8" s="2"/>
       <c r="FW8" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="FX8" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="FY8" s="2">
         <v>1</v>
@@ -5298,7 +5645,7 @@
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G9" s="1">
         <v>46055</v>
@@ -5310,67 +5657,67 @@
         <v>1</v>
       </c>
       <c r="J9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K9" s="2">
         <v>0</v>
       </c>
       <c r="L9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M9" s="2">
         <v>0</v>
       </c>
       <c r="N9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O9" s="2">
         <v>0</v>
       </c>
       <c r="P9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q9" s="2">
         <v>0</v>
       </c>
       <c r="R9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S9" s="2">
         <v>0</v>
       </c>
       <c r="T9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="U9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="V9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="W9" s="2">
         <v>0</v>
       </c>
       <c r="X9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Y9" s="2">
         <v>0</v>
       </c>
       <c r="Z9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AA9" s="2">
         <v>1</v>
       </c>
       <c r="AB9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AC9" s="2">
         <v>1</v>
       </c>
       <c r="AD9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AE9" s="2">
         <v>0</v>
@@ -5643,110 +5990,110 @@
       <c r="DQ9" s="2">
         <v>2025</v>
       </c>
-      <c r="DR9" s="2">
+      <c r="DR9" t="s">
+        <v>369</v>
+      </c>
+      <c r="DS9" s="2">
         <v>387</v>
       </c>
-      <c r="DS9" s="2">
+      <c r="DT9" s="2">
         <v>725</v>
       </c>
-      <c r="DT9" s="2">
+      <c r="DU9" s="2">
         <v>36918</v>
       </c>
-      <c r="DU9" s="2">
+      <c r="DV9" s="2">
         <v>20.384178161621094</v>
       </c>
-      <c r="DV9" s="2">
+      <c r="DW9" s="2">
         <v>1182</v>
       </c>
-      <c r="DW9" s="2">
+      <c r="DX9" s="2">
         <v>0.25176948308944702</v>
       </c>
-      <c r="DX9" s="2">
+      <c r="DY9" s="2">
         <v>56</v>
       </c>
-      <c r="DY9" t="s">
-        <v>177</v>
-      </c>
       <c r="DZ9" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="EA9" t="s">
+        <v>185</v>
+      </c>
+      <c r="EB9" t="s">
         <v>21</v>
       </c>
-      <c r="EB9" t="s">
-        <v>193</v>
-      </c>
       <c r="EC9" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="ED9" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="EE9" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="EF9" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="EG9" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="EH9" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="EI9" t="s">
+        <v>231</v>
+      </c>
+      <c r="EJ9" t="s">
         <v>21</v>
       </c>
-      <c r="EJ9" t="s">
-        <v>239</v>
-      </c>
       <c r="EK9" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="EL9" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="EM9" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="EN9" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="EO9" t="s">
-        <v>260</v>
-      </c>
-      <c r="EP9" s="2">
+        <v>255</v>
+      </c>
+      <c r="EP9" t="s">
+        <v>259</v>
+      </c>
+      <c r="EQ9" s="2">
         <v>53</v>
       </c>
-      <c r="EQ9" s="2">
+      <c r="ER9" s="2">
         <v>131</v>
       </c>
-      <c r="ER9" t="s">
-        <v>268</v>
-      </c>
       <c r="ES9" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="ET9" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="EU9" t="s">
-        <v>239</v>
+        <v>275</v>
       </c>
       <c r="EV9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="EW9" t="s">
-        <v>280</v>
-      </c>
-      <c r="EX9" s="2">
+        <v>238</v>
+      </c>
+      <c r="EX9" t="s">
+        <v>279</v>
+      </c>
+      <c r="EY9" s="2">
         <v>79</v>
       </c>
-      <c r="EY9" t="s">
-        <v>286</v>
-      </c>
       <c r="EZ9" t="s">
-        <v>2</v>
+        <v>285</v>
       </c>
       <c r="FA9" t="s">
         <v>2</v>
@@ -6116,119 +6463,119 @@
       <c r="DQ10" s="2">
         <v>2024</v>
       </c>
-      <c r="DR10" s="2">
+      <c r="DR10" t="s">
+        <v>291</v>
+      </c>
+      <c r="DS10" s="2">
         <v>375</v>
       </c>
-      <c r="DS10" s="2">
+      <c r="DT10" s="2">
         <v>348</v>
       </c>
-      <c r="DT10" s="2">
+      <c r="DU10" s="2">
         <v>28335</v>
       </c>
-      <c r="DU10" s="2">
+      <c r="DV10" s="2">
         <v>29.764091491699219</v>
       </c>
-      <c r="DV10" s="2">
+      <c r="DW10" s="2">
         <v>1250</v>
       </c>
-      <c r="DW10" s="2">
+      <c r="DX10" s="2">
         <v>0.12238007038831711</v>
       </c>
-      <c r="DX10" s="2">
+      <c r="DY10" s="2">
         <v>78</v>
       </c>
-      <c r="DY10" t="s">
-        <v>178</v>
-      </c>
       <c r="DZ10" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="EA10" t="s">
+        <v>186</v>
+      </c>
+      <c r="EB10" t="s">
         <v>22</v>
       </c>
-      <c r="EB10" t="s">
-        <v>193</v>
-      </c>
       <c r="EC10" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="ED10" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="EE10" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="EF10" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="EG10" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="EH10" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="EI10" t="s">
+        <v>232</v>
+      </c>
+      <c r="EJ10" t="s">
         <v>22</v>
       </c>
-      <c r="EJ10" t="s">
-        <v>239</v>
-      </c>
       <c r="EK10" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="EL10" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="EM10" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="EN10" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="EO10" t="s">
-        <v>260</v>
-      </c>
-      <c r="EP10" s="2">
+        <v>253</v>
+      </c>
+      <c r="EP10" t="s">
+        <v>259</v>
+      </c>
+      <c r="EQ10" s="2">
         <v>52</v>
       </c>
-      <c r="EQ10" s="2">
+      <c r="ER10" s="2">
         <v>117</v>
       </c>
-      <c r="ER10" t="s">
-        <v>269</v>
-      </c>
       <c r="ES10" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="ET10" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="EU10" t="s">
-        <v>239</v>
+        <v>275</v>
       </c>
       <c r="EV10" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="EW10" t="s">
-        <v>280</v>
-      </c>
-      <c r="EX10" s="2">
+        <v>238</v>
+      </c>
+      <c r="EX10" t="s">
+        <v>279</v>
+      </c>
+      <c r="EY10" s="2">
         <v>66</v>
       </c>
-      <c r="EY10" t="s">
-        <v>287</v>
-      </c>
       <c r="EZ10" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="FA10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="FB10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="FC10" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="FD10" s="2">
         <v>375</v>
@@ -6240,56 +6587,56 @@
         <v>2024</v>
       </c>
       <c r="FG10" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="FH10" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="FI10" t="s">
         <v>2</v>
       </c>
       <c r="FJ10" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="FK10" t="s">
         <v>2</v>
       </c>
       <c r="FL10" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="FM10" s="1">
         <v>45840</v>
       </c>
       <c r="FN10" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="FO10" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="FP10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="FQ10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="FR10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="FS10" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="FT10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="FU10" t="s">
         <v>22</v>
       </c>
       <c r="FV10" s="2"/>
       <c r="FW10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="FX10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="FY10" s="2">
         <v>1</v>
@@ -6312,7 +6659,7 @@
         <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G11" s="1">
         <v>46056</v>
@@ -6330,34 +6677,34 @@
         <v>0</v>
       </c>
       <c r="L11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M11" s="2">
         <v>0</v>
       </c>
       <c r="N11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O11" s="2">
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Q11" s="2">
         <v>0</v>
       </c>
       <c r="R11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S11" s="2">
         <v>0</v>
       </c>
       <c r="T11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="U11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="V11" t="s">
         <v>2</v>
@@ -6384,7 +6731,7 @@
         <v>1</v>
       </c>
       <c r="AD11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AE11" s="2">
         <v>0</v>
@@ -6659,110 +7006,110 @@
       <c r="DQ11" s="2">
         <v>2025</v>
       </c>
-      <c r="DR11" s="2">
+      <c r="DR11" t="s">
+        <v>369</v>
+      </c>
+      <c r="DS11" s="2">
         <v>375</v>
       </c>
-      <c r="DS11" s="2">
+      <c r="DT11" s="2">
         <v>348</v>
       </c>
-      <c r="DT11" s="2">
+      <c r="DU11" s="2">
         <v>28335</v>
       </c>
-      <c r="DU11" s="2">
+      <c r="DV11" s="2">
         <v>29.764091491699219</v>
       </c>
-      <c r="DV11" s="2">
+      <c r="DW11" s="2">
         <v>1250</v>
       </c>
-      <c r="DW11" s="2">
+      <c r="DX11" s="2">
         <v>0.12238007038831711</v>
       </c>
-      <c r="DX11" s="2">
+      <c r="DY11" s="2">
         <v>78</v>
       </c>
-      <c r="DY11" t="s">
-        <v>178</v>
-      </c>
       <c r="DZ11" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="EA11" t="s">
+        <v>186</v>
+      </c>
+      <c r="EB11" t="s">
         <v>22</v>
       </c>
-      <c r="EB11" t="s">
-        <v>193</v>
-      </c>
       <c r="EC11" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="ED11" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="EE11" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="EF11" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="EG11" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="EH11" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="EI11" t="s">
+        <v>232</v>
+      </c>
+      <c r="EJ11" t="s">
         <v>22</v>
       </c>
-      <c r="EJ11" t="s">
-        <v>239</v>
-      </c>
       <c r="EK11" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="EL11" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="EM11" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="EN11" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="EO11" t="s">
-        <v>260</v>
-      </c>
-      <c r="EP11" s="2">
+        <v>253</v>
+      </c>
+      <c r="EP11" t="s">
+        <v>259</v>
+      </c>
+      <c r="EQ11" s="2">
         <v>52</v>
       </c>
-      <c r="EQ11" s="2">
+      <c r="ER11" s="2">
         <v>117</v>
       </c>
-      <c r="ER11" t="s">
-        <v>269</v>
-      </c>
       <c r="ES11" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="ET11" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="EU11" t="s">
-        <v>239</v>
+        <v>275</v>
       </c>
       <c r="EV11" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="EW11" t="s">
-        <v>280</v>
-      </c>
-      <c r="EX11" s="2">
+        <v>238</v>
+      </c>
+      <c r="EX11" t="s">
+        <v>279</v>
+      </c>
+      <c r="EY11" s="2">
         <v>66</v>
       </c>
-      <c r="EY11" t="s">
-        <v>287</v>
-      </c>
       <c r="EZ11" t="s">
-        <v>2</v>
+        <v>286</v>
       </c>
       <c r="FA11" t="s">
         <v>2</v>
@@ -6839,7 +7186,7 @@
         <v>13</v>
       </c>
       <c r="D12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s">
@@ -7132,119 +7479,119 @@
       <c r="DQ12" s="2">
         <v>2024</v>
       </c>
-      <c r="DR12" s="2">
+      <c r="DR12" t="s">
+        <v>291</v>
+      </c>
+      <c r="DS12" s="2">
         <v>462</v>
       </c>
-      <c r="DS12" s="2">
+      <c r="DT12" s="2">
         <v>417</v>
       </c>
-      <c r="DT12" s="2">
+      <c r="DU12" s="2">
         <v>55359</v>
       </c>
-      <c r="DU12" s="2">
+      <c r="DV12" s="2">
         <v>24.911413192749024</v>
       </c>
-      <c r="DV12" s="2">
+      <c r="DW12" s="2">
         <v>10925</v>
       </c>
-      <c r="DW12" s="2">
+      <c r="DX12" s="2">
         <v>0.009950634092092514</v>
       </c>
-      <c r="DX12" s="2">
+      <c r="DY12" s="2">
         <v>140</v>
       </c>
-      <c r="DY12" t="s">
-        <v>179</v>
-      </c>
       <c r="DZ12" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="EA12" t="s">
-        <v>24</v>
+        <v>187</v>
       </c>
       <c r="EB12" t="s">
-        <v>193</v>
+        <v>23</v>
       </c>
       <c r="EC12" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="ED12" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="EE12" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="EF12" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="EG12" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="EH12" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="EI12" t="s">
-        <v>24</v>
+        <v>233</v>
       </c>
       <c r="EJ12" t="s">
-        <v>239</v>
+        <v>23</v>
       </c>
       <c r="EK12" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="EL12" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="EM12" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="EN12" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="EO12" t="s">
-        <v>260</v>
-      </c>
-      <c r="EP12" s="2">
+        <v>253</v>
+      </c>
+      <c r="EP12" t="s">
+        <v>259</v>
+      </c>
+      <c r="EQ12" s="2">
         <v>53</v>
       </c>
-      <c r="EQ12" s="2">
+      <c r="ER12" s="2">
         <v>151</v>
       </c>
-      <c r="ER12" t="s">
-        <v>270</v>
-      </c>
       <c r="ES12" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="ET12" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="EU12" t="s">
-        <v>239</v>
+        <v>275</v>
       </c>
       <c r="EV12" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="EW12" t="s">
-        <v>280</v>
-      </c>
-      <c r="EX12" s="2">
+        <v>238</v>
+      </c>
+      <c r="EX12" t="s">
+        <v>279</v>
+      </c>
+      <c r="EY12" s="2">
         <v>99</v>
       </c>
-      <c r="EY12" t="s">
-        <v>288</v>
-      </c>
       <c r="EZ12" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="FA12" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="FB12" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="FC12" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="FD12" s="2">
         <v>462</v>
@@ -7256,56 +7603,56 @@
         <v>2024</v>
       </c>
       <c r="FG12" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="FH12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="FI12" t="s">
         <v>2</v>
       </c>
       <c r="FJ12" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="FK12" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="FL12" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="FM12" s="1">
         <v>45840</v>
       </c>
       <c r="FN12" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="FO12" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="FP12" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="FQ12" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="FR12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="FS12" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="FT12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="FU12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="FV12" s="2"/>
       <c r="FW12" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="FX12" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="FY12" s="2">
         <v>1</v>
@@ -7322,13 +7669,13 @@
         <v>13</v>
       </c>
       <c r="D13" t="s">
-        <v>23</v>
+        <v>368</v>
       </c>
       <c r="E13" s="2">
         <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G13" s="1">
         <v>46057</v>
@@ -7340,38 +7687,38 @@
         <v>0</v>
       </c>
       <c r="J13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K13" s="2"/>
       <c r="L13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M13" s="2">
         <v>0</v>
       </c>
       <c r="N13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O13" s="2">
         <v>0</v>
       </c>
       <c r="P13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q13" s="2">
         <v>0</v>
       </c>
       <c r="R13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S13" s="2">
         <v>1</v>
       </c>
       <c r="T13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="U13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="V13" t="s">
         <v>2</v>
@@ -7380,7 +7727,7 @@
         <v>4</v>
       </c>
       <c r="X13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y13" s="2">
         <v>0</v>
@@ -7398,19 +7745,19 @@
         <v>0</v>
       </c>
       <c r="AD13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AE13" s="2">
         <v>0</v>
       </c>
       <c r="AF13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AG13" s="2">
         <v>0</v>
       </c>
       <c r="AH13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AI13" s="2">
         <v>1</v>
@@ -7673,110 +8020,110 @@
       <c r="DQ13" s="2">
         <v>2025</v>
       </c>
-      <c r="DR13" s="2">
+      <c r="DR13" t="s">
+        <v>369</v>
+      </c>
+      <c r="DS13" s="2">
         <v>462</v>
       </c>
-      <c r="DS13" s="2">
+      <c r="DT13" s="2">
         <v>417</v>
       </c>
-      <c r="DT13" s="2">
+      <c r="DU13" s="2">
         <v>55359</v>
       </c>
-      <c r="DU13" s="2">
+      <c r="DV13" s="2">
         <v>24.911413192749024</v>
       </c>
-      <c r="DV13" s="2">
+      <c r="DW13" s="2">
         <v>10925</v>
       </c>
-      <c r="DW13" s="2">
+      <c r="DX13" s="2">
         <v>0.009950634092092514</v>
       </c>
-      <c r="DX13" s="2">
+      <c r="DY13" s="2">
         <v>140</v>
       </c>
-      <c r="DY13" t="s">
-        <v>179</v>
-      </c>
       <c r="DZ13" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="EA13" t="s">
-        <v>24</v>
+        <v>187</v>
       </c>
       <c r="EB13" t="s">
-        <v>193</v>
+        <v>23</v>
       </c>
       <c r="EC13" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="ED13" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="EE13" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="EF13" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="EG13" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="EH13" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="EI13" t="s">
-        <v>24</v>
+        <v>233</v>
       </c>
       <c r="EJ13" t="s">
-        <v>239</v>
+        <v>23</v>
       </c>
       <c r="EK13" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="EL13" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="EM13" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="EN13" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="EO13" t="s">
-        <v>260</v>
-      </c>
-      <c r="EP13" s="2">
+        <v>253</v>
+      </c>
+      <c r="EP13" t="s">
+        <v>259</v>
+      </c>
+      <c r="EQ13" s="2">
         <v>53</v>
       </c>
-      <c r="EQ13" s="2">
+      <c r="ER13" s="2">
         <v>151</v>
       </c>
-      <c r="ER13" t="s">
-        <v>270</v>
-      </c>
       <c r="ES13" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="ET13" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="EU13" t="s">
-        <v>239</v>
+        <v>275</v>
       </c>
       <c r="EV13" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="EW13" t="s">
-        <v>280</v>
-      </c>
-      <c r="EX13" s="2">
+        <v>238</v>
+      </c>
+      <c r="EX13" t="s">
+        <v>279</v>
+      </c>
+      <c r="EY13" s="2">
         <v>99</v>
       </c>
-      <c r="EY13" t="s">
-        <v>288</v>
-      </c>
       <c r="EZ13" t="s">
-        <v>2</v>
+        <v>287</v>
       </c>
       <c r="FA13" t="s">
         <v>2</v>
@@ -7853,7 +8200,7 @@
         <v>14</v>
       </c>
       <c r="D14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s">
@@ -8146,119 +8493,119 @@
       <c r="DQ14" s="2">
         <v>2024</v>
       </c>
-      <c r="DR14" s="2">
+      <c r="DR14" t="s">
+        <v>291</v>
+      </c>
+      <c r="DS14" s="2">
         <v>273</v>
       </c>
-      <c r="DS14" s="2">
+      <c r="DT14" s="2">
         <v>594</v>
       </c>
-      <c r="DT14" s="2">
+      <c r="DU14" s="2">
         <v>35853</v>
       </c>
-      <c r="DU14" s="2">
+      <c r="DV14" s="2">
         <v>29.621505737304688</v>
       </c>
-      <c r="DV14" s="2">
+      <c r="DW14" s="2">
         <v>1173</v>
       </c>
-      <c r="DW14" s="2">
+      <c r="DX14" s="2">
         <v>0.1259913295507431</v>
       </c>
-      <c r="DX14" s="2">
+      <c r="DY14" s="2">
         <v>98</v>
       </c>
-      <c r="DY14" t="s">
-        <v>180</v>
-      </c>
       <c r="DZ14" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="EA14" t="s">
-        <v>25</v>
+        <v>188</v>
       </c>
       <c r="EB14" t="s">
-        <v>193</v>
+        <v>24</v>
       </c>
       <c r="EC14" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="ED14" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="EE14" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="EF14" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="EG14" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="EH14" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="EI14" t="s">
-        <v>25</v>
+        <v>234</v>
       </c>
       <c r="EJ14" t="s">
-        <v>239</v>
+        <v>24</v>
       </c>
       <c r="EK14" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="EL14" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="EM14" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="EN14" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="EO14" t="s">
-        <v>261</v>
-      </c>
-      <c r="EP14" s="2">
+        <v>256</v>
+      </c>
+      <c r="EP14" t="s">
+        <v>260</v>
+      </c>
+      <c r="EQ14" s="2">
         <v>62</v>
       </c>
-      <c r="EQ14" s="2">
+      <c r="ER14" s="2">
         <v>154</v>
       </c>
-      <c r="ER14" t="s">
-        <v>271</v>
-      </c>
       <c r="ES14" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="ET14" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="EU14" t="s">
-        <v>239</v>
+        <v>275</v>
       </c>
       <c r="EV14" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="EW14" t="s">
-        <v>280</v>
-      </c>
-      <c r="EX14" s="2">
+        <v>238</v>
+      </c>
+      <c r="EX14" t="s">
+        <v>279</v>
+      </c>
+      <c r="EY14" s="2">
         <v>93</v>
       </c>
-      <c r="EY14" t="s">
-        <v>289</v>
-      </c>
       <c r="EZ14" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="FA14" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="FB14" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="FC14" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="FD14" s="2">
         <v>273</v>
@@ -8270,56 +8617,56 @@
         <v>2024</v>
       </c>
       <c r="FG14" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="FH14" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="FI14" t="s">
         <v>2</v>
       </c>
       <c r="FJ14" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="FK14" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="FL14" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="FM14" s="1">
         <v>45840</v>
       </c>
       <c r="FN14" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="FO14" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="FP14" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="FQ14" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="FR14" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="FS14" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="FT14" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="FU14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="FV14" s="2"/>
       <c r="FW14" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="FX14" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="FY14" s="2">
         <v>1</v>
@@ -8336,13 +8683,13 @@
         <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E15" s="2">
         <v>1</v>
       </c>
       <c r="F15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G15" s="1">
         <v>46056</v>
@@ -8354,73 +8701,73 @@
         <v>0</v>
       </c>
       <c r="J15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K15" s="2">
         <v>0</v>
       </c>
       <c r="L15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M15" s="2">
         <v>1</v>
       </c>
       <c r="N15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O15" s="2">
         <v>0</v>
       </c>
       <c r="P15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q15" s="2">
         <v>0</v>
       </c>
       <c r="R15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S15" s="2">
         <v>0</v>
       </c>
       <c r="T15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="U15" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="V15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="W15" s="2">
         <v>0</v>
       </c>
       <c r="X15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Y15" s="2">
         <v>0</v>
       </c>
       <c r="Z15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AA15" s="2">
         <v>0</v>
       </c>
       <c r="AB15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AC15" s="2">
         <v>1</v>
       </c>
       <c r="AD15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AE15" s="2">
         <v>1</v>
       </c>
       <c r="AF15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AG15" s="2">
         <v>0</v>
@@ -8689,110 +9036,110 @@
       <c r="DQ15" s="2">
         <v>2025</v>
       </c>
-      <c r="DR15" s="2">
+      <c r="DR15" t="s">
+        <v>369</v>
+      </c>
+      <c r="DS15" s="2">
         <v>273</v>
       </c>
-      <c r="DS15" s="2">
+      <c r="DT15" s="2">
         <v>594</v>
       </c>
-      <c r="DT15" s="2">
+      <c r="DU15" s="2">
         <v>35853</v>
       </c>
-      <c r="DU15" s="2">
+      <c r="DV15" s="2">
         <v>29.621505737304688</v>
       </c>
-      <c r="DV15" s="2">
+      <c r="DW15" s="2">
         <v>1173</v>
       </c>
-      <c r="DW15" s="2">
+      <c r="DX15" s="2">
         <v>0.1259913295507431</v>
       </c>
-      <c r="DX15" s="2">
+      <c r="DY15" s="2">
         <v>98</v>
       </c>
-      <c r="DY15" t="s">
-        <v>180</v>
-      </c>
       <c r="DZ15" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="EA15" t="s">
-        <v>25</v>
+        <v>188</v>
       </c>
       <c r="EB15" t="s">
-        <v>193</v>
+        <v>24</v>
       </c>
       <c r="EC15" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="ED15" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="EE15" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="EF15" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="EG15" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="EH15" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="EI15" t="s">
-        <v>25</v>
+        <v>234</v>
       </c>
       <c r="EJ15" t="s">
-        <v>239</v>
+        <v>24</v>
       </c>
       <c r="EK15" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="EL15" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="EM15" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="EN15" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="EO15" t="s">
-        <v>261</v>
-      </c>
-      <c r="EP15" s="2">
+        <v>256</v>
+      </c>
+      <c r="EP15" t="s">
+        <v>260</v>
+      </c>
+      <c r="EQ15" s="2">
         <v>62</v>
       </c>
-      <c r="EQ15" s="2">
+      <c r="ER15" s="2">
         <v>154</v>
       </c>
-      <c r="ER15" t="s">
-        <v>271</v>
-      </c>
       <c r="ES15" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="ET15" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="EU15" t="s">
-        <v>239</v>
+        <v>275</v>
       </c>
       <c r="EV15" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="EW15" t="s">
-        <v>280</v>
-      </c>
-      <c r="EX15" s="2">
+        <v>238</v>
+      </c>
+      <c r="EX15" t="s">
+        <v>279</v>
+      </c>
+      <c r="EY15" s="2">
         <v>93</v>
       </c>
-      <c r="EY15" t="s">
-        <v>289</v>
-      </c>
       <c r="EZ15" t="s">
-        <v>2</v>
+        <v>288</v>
       </c>
       <c r="FA15" t="s">
         <v>2</v>
@@ -8869,7 +9216,7 @@
         <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s">
@@ -9162,119 +9509,119 @@
       <c r="DQ16" s="2">
         <v>2024</v>
       </c>
-      <c r="DR16" s="2">
+      <c r="DR16" t="s">
+        <v>291</v>
+      </c>
+      <c r="DS16" s="2">
         <v>301</v>
       </c>
-      <c r="DS16" s="2">
+      <c r="DT16" s="2">
         <v>216</v>
       </c>
-      <c r="DT16" s="2">
+      <c r="DU16" s="2">
         <v>21648</v>
       </c>
-      <c r="DU16" s="2">
+      <c r="DV16" s="2">
         <v>19.887435913085938</v>
       </c>
-      <c r="DV16" s="2">
+      <c r="DW16" s="2">
         <v>881</v>
       </c>
-      <c r="DW16" s="2">
+      <c r="DX16" s="2">
         <v>0.033100180327892303</v>
       </c>
-      <c r="DX16" s="2">
+      <c r="DY16" s="2">
         <v>40</v>
       </c>
-      <c r="DY16" t="s">
-        <v>181</v>
-      </c>
       <c r="DZ16" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="EA16" t="s">
-        <v>26</v>
+        <v>189</v>
       </c>
       <c r="EB16" t="s">
-        <v>193</v>
+        <v>25</v>
       </c>
       <c r="EC16" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="ED16" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="EE16" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="EF16" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="EG16" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="EH16" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="EI16" t="s">
-        <v>26</v>
+        <v>235</v>
       </c>
       <c r="EJ16" t="s">
-        <v>239</v>
+        <v>25</v>
       </c>
       <c r="EK16" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="EL16" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="EM16" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="EN16" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="EO16" t="s">
-        <v>260</v>
-      </c>
-      <c r="EP16" s="2">
+        <v>253</v>
+      </c>
+      <c r="EP16" t="s">
+        <v>259</v>
+      </c>
+      <c r="EQ16" s="2">
         <v>62</v>
       </c>
-      <c r="EQ16" s="2">
+      <c r="ER16" s="2">
         <v>100</v>
       </c>
-      <c r="ER16" t="s">
-        <v>272</v>
-      </c>
       <c r="ES16" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="ET16" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="EU16" t="s">
-        <v>239</v>
+        <v>275</v>
       </c>
       <c r="EV16" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="EW16" t="s">
-        <v>280</v>
-      </c>
-      <c r="EX16" s="2">
+        <v>238</v>
+      </c>
+      <c r="EX16" t="s">
+        <v>279</v>
+      </c>
+      <c r="EY16" s="2">
         <v>39</v>
       </c>
-      <c r="EY16" t="s">
-        <v>290</v>
-      </c>
       <c r="EZ16" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="FA16" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="FB16" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="FC16" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="FD16" s="2">
         <v>301</v>
@@ -9286,56 +9633,56 @@
         <v>2024</v>
       </c>
       <c r="FG16" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="FH16" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="FI16" t="s">
         <v>2</v>
       </c>
       <c r="FJ16" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="FK16" t="s">
         <v>2</v>
       </c>
       <c r="FL16" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="FM16" s="1">
         <v>45847</v>
       </c>
       <c r="FN16" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="FO16" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="FP16" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="FQ16" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="FR16" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="FS16" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="FT16" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="FU16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="FV16" s="2"/>
       <c r="FW16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="FX16" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="FY16" s="2">
         <v>1</v>
@@ -9352,13 +9699,13 @@
         <v>15</v>
       </c>
       <c r="D17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E17" s="2">
         <v>1</v>
       </c>
       <c r="F17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G17" s="1">
         <v>46057</v>
@@ -9370,79 +9717,79 @@
         <v>0</v>
       </c>
       <c r="J17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K17" s="2">
         <v>0</v>
       </c>
       <c r="L17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M17" s="2">
         <v>0</v>
       </c>
       <c r="N17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O17" s="2">
         <v>0</v>
       </c>
       <c r="P17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q17" s="2">
         <v>0</v>
       </c>
       <c r="R17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S17" s="2">
         <v>0</v>
       </c>
       <c r="T17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="U17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="V17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="W17" s="2">
         <v>0</v>
       </c>
       <c r="X17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Y17" s="2">
         <v>1</v>
       </c>
       <c r="Z17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AA17" s="2">
         <v>1</v>
       </c>
       <c r="AB17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AC17" s="2">
         <v>0</v>
       </c>
       <c r="AD17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AE17" s="2">
         <v>0</v>
       </c>
       <c r="AF17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AG17" s="2">
         <v>0</v>
       </c>
       <c r="AH17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AI17" s="2">
         <v>1</v>
@@ -9705,110 +10052,110 @@
       <c r="DQ17" s="2">
         <v>2025</v>
       </c>
-      <c r="DR17" s="2">
+      <c r="DR17" t="s">
+        <v>369</v>
+      </c>
+      <c r="DS17" s="2">
         <v>301</v>
       </c>
-      <c r="DS17" s="2">
+      <c r="DT17" s="2">
         <v>216</v>
       </c>
-      <c r="DT17" s="2">
+      <c r="DU17" s="2">
         <v>21648</v>
       </c>
-      <c r="DU17" s="2">
+      <c r="DV17" s="2">
         <v>19.887435913085938</v>
       </c>
-      <c r="DV17" s="2">
+      <c r="DW17" s="2">
         <v>881</v>
       </c>
-      <c r="DW17" s="2">
+      <c r="DX17" s="2">
         <v>0.033100180327892303</v>
       </c>
-      <c r="DX17" s="2">
+      <c r="DY17" s="2">
         <v>40</v>
       </c>
-      <c r="DY17" t="s">
-        <v>181</v>
-      </c>
       <c r="DZ17" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="EA17" t="s">
-        <v>26</v>
+        <v>189</v>
       </c>
       <c r="EB17" t="s">
-        <v>193</v>
+        <v>25</v>
       </c>
       <c r="EC17" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="ED17" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="EE17" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="EF17" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="EG17" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="EH17" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="EI17" t="s">
-        <v>26</v>
+        <v>235</v>
       </c>
       <c r="EJ17" t="s">
-        <v>239</v>
+        <v>25</v>
       </c>
       <c r="EK17" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="EL17" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="EM17" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="EN17" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="EO17" t="s">
-        <v>260</v>
-      </c>
-      <c r="EP17" s="2">
+        <v>253</v>
+      </c>
+      <c r="EP17" t="s">
+        <v>259</v>
+      </c>
+      <c r="EQ17" s="2">
         <v>62</v>
       </c>
-      <c r="EQ17" s="2">
+      <c r="ER17" s="2">
         <v>100</v>
       </c>
-      <c r="ER17" t="s">
-        <v>272</v>
-      </c>
       <c r="ES17" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="ET17" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="EU17" t="s">
-        <v>239</v>
+        <v>275</v>
       </c>
       <c r="EV17" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="EW17" t="s">
-        <v>280</v>
-      </c>
-      <c r="EX17" s="2">
+        <v>238</v>
+      </c>
+      <c r="EX17" t="s">
+        <v>279</v>
+      </c>
+      <c r="EY17" s="2">
         <v>39</v>
       </c>
-      <c r="EY17" t="s">
-        <v>290</v>
-      </c>
       <c r="EZ17" t="s">
-        <v>2</v>
+        <v>289</v>
       </c>
       <c r="FA17" t="s">
         <v>2</v>
@@ -9877,5 +10224,6 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/test_data.xlsx
+++ b/test_data.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="2378" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="3567" uniqueCount="370">
   <si>
     <t>publication_date_2025</t>
   </si>
@@ -3093,7 +3093,7 @@
         <v>2</v>
       </c>
       <c r="FR3" t="s">
-        <v>2</v>
+        <v>182</v>
       </c>
       <c r="FS3" t="s">
         <v>2</v>
@@ -4109,7 +4109,7 @@
         <v>2</v>
       </c>
       <c r="FR5" t="s">
-        <v>2</v>
+        <v>183</v>
       </c>
       <c r="FS5" t="s">
         <v>2</v>
@@ -5125,7 +5125,7 @@
         <v>2</v>
       </c>
       <c r="FR7" t="s">
-        <v>2</v>
+        <v>184</v>
       </c>
       <c r="FS7" t="s">
         <v>2</v>
@@ -6139,7 +6139,7 @@
         <v>2</v>
       </c>
       <c r="FR9" t="s">
-        <v>2</v>
+        <v>185</v>
       </c>
       <c r="FS9" t="s">
         <v>2</v>
@@ -7155,7 +7155,7 @@
         <v>2</v>
       </c>
       <c r="FR11" t="s">
-        <v>2</v>
+        <v>186</v>
       </c>
       <c r="FS11" t="s">
         <v>2</v>
@@ -8169,7 +8169,7 @@
         <v>2</v>
       </c>
       <c r="FR13" t="s">
-        <v>2</v>
+        <v>187</v>
       </c>
       <c r="FS13" t="s">
         <v>2</v>
@@ -9185,7 +9185,7 @@
         <v>2</v>
       </c>
       <c r="FR15" t="s">
-        <v>2</v>
+        <v>188</v>
       </c>
       <c r="FS15" t="s">
         <v>2</v>
@@ -10201,7 +10201,7 @@
         <v>2</v>
       </c>
       <c r="FR17" t="s">
-        <v>2</v>
+        <v>189</v>
       </c>
       <c r="FS17" t="s">
         <v>2</v>
